--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1820,6 +1820,1254 @@
         <v>0.0041</v>
       </c>
     </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C50">
+        <v>7</v>
+      </c>
+      <c r="D50">
+        <v>5.5514</v>
+      </c>
+      <c r="E50">
+        <v>0.151496</v>
+      </c>
+      <c r="F50">
+        <v>15.1496</v>
+      </c>
+      <c r="G50">
+        <v>0.162635</v>
+      </c>
+      <c r="H50">
+        <v>16.2635</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C51">
+        <v>7</v>
+      </c>
+      <c r="D51">
+        <v>5.6286</v>
+      </c>
+      <c r="E51">
+        <v>0.14942</v>
+      </c>
+      <c r="F51">
+        <v>14.942</v>
+      </c>
+      <c r="G51">
+        <v>0.160365</v>
+      </c>
+      <c r="H51">
+        <v>16.0365</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C52">
+        <v>7</v>
+      </c>
+      <c r="D52">
+        <v>8.4186</v>
+      </c>
+      <c r="E52">
+        <v>0.099901</v>
+      </c>
+      <c r="F52">
+        <v>9.9901</v>
+      </c>
+      <c r="G52">
+        <v>0.106215</v>
+      </c>
+      <c r="H52">
+        <v>10.6215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C53">
+        <v>7</v>
+      </c>
+      <c r="D53">
+        <v>8.7043</v>
+      </c>
+      <c r="E53">
+        <v>0.096621</v>
+      </c>
+      <c r="F53">
+        <v>9.662100000000001</v>
+      </c>
+      <c r="G53">
+        <v>0.10263</v>
+      </c>
+      <c r="H53">
+        <v>10.263</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C54">
+        <v>7</v>
+      </c>
+      <c r="D54">
+        <v>10.1143</v>
+      </c>
+      <c r="E54">
+        <v>0.083152</v>
+      </c>
+      <c r="F54">
+        <v>8.315200000000001</v>
+      </c>
+      <c r="G54">
+        <v>0.087904</v>
+      </c>
+      <c r="H54">
+        <v>8.7904</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C55">
+        <v>7</v>
+      </c>
+      <c r="D55">
+        <v>10.3286</v>
+      </c>
+      <c r="E55">
+        <v>0.081427</v>
+      </c>
+      <c r="F55">
+        <v>8.1427</v>
+      </c>
+      <c r="G55">
+        <v>0.086018</v>
+      </c>
+      <c r="H55">
+        <v>8.601800000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C56">
+        <v>7</v>
+      </c>
+      <c r="D56">
+        <v>15.6714</v>
+      </c>
+      <c r="E56">
+        <v>0.053666</v>
+      </c>
+      <c r="F56">
+        <v>5.3666</v>
+      </c>
+      <c r="G56">
+        <v>0.055681</v>
+      </c>
+      <c r="H56">
+        <v>5.5681</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C57">
+        <v>7</v>
+      </c>
+      <c r="D57">
+        <v>20.2857</v>
+      </c>
+      <c r="E57">
+        <v>0.041459</v>
+      </c>
+      <c r="F57">
+        <v>4.1459</v>
+      </c>
+      <c r="G57">
+        <v>0.042353</v>
+      </c>
+      <c r="H57">
+        <v>4.2353</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C58">
+        <v>7</v>
+      </c>
+      <c r="D58">
+        <v>33</v>
+      </c>
+      <c r="E58">
+        <v>0.025485</v>
+      </c>
+      <c r="F58">
+        <v>2.5485</v>
+      </c>
+      <c r="G58">
+        <v>0.024947</v>
+      </c>
+      <c r="H58">
+        <v>2.4947</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C59">
+        <v>7</v>
+      </c>
+      <c r="D59">
+        <v>37.7143</v>
+      </c>
+      <c r="E59">
+        <v>0.0223</v>
+      </c>
+      <c r="F59">
+        <v>2.23</v>
+      </c>
+      <c r="G59">
+        <v>0.021487</v>
+      </c>
+      <c r="H59">
+        <v>2.1487</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C60">
+        <v>7</v>
+      </c>
+      <c r="D60">
+        <v>44.5714</v>
+      </c>
+      <c r="E60">
+        <v>0.018869</v>
+      </c>
+      <c r="F60">
+        <v>1.8869</v>
+      </c>
+      <c r="G60">
+        <v>0.01777</v>
+      </c>
+      <c r="H60">
+        <v>1.777</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
+      <c r="D61">
+        <v>45.5714</v>
+      </c>
+      <c r="E61">
+        <v>0.018455</v>
+      </c>
+      <c r="F61">
+        <v>1.8455</v>
+      </c>
+      <c r="G61">
+        <v>0.017322</v>
+      </c>
+      <c r="H61">
+        <v>1.7322</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C62">
+        <v>7</v>
+      </c>
+      <c r="D62">
+        <v>50.5714</v>
+      </c>
+      <c r="E62">
+        <v>0.01663</v>
+      </c>
+      <c r="F62">
+        <v>1.663</v>
+      </c>
+      <c r="G62">
+        <v>0.015352</v>
+      </c>
+      <c r="H62">
+        <v>1.5352</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C63">
+        <v>7</v>
+      </c>
+      <c r="D63">
+        <v>52.7143</v>
+      </c>
+      <c r="E63">
+        <v>0.015954</v>
+      </c>
+      <c r="F63">
+        <v>1.5954</v>
+      </c>
+      <c r="G63">
+        <v>0.014623</v>
+      </c>
+      <c r="H63">
+        <v>1.4623</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C64">
+        <v>7</v>
+      </c>
+      <c r="D64">
+        <v>53.4286</v>
+      </c>
+      <c r="E64">
+        <v>0.015741</v>
+      </c>
+      <c r="F64">
+        <v>1.5741</v>
+      </c>
+      <c r="G64">
+        <v>0.014394</v>
+      </c>
+      <c r="H64">
+        <v>1.4394</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C65">
+        <v>7</v>
+      </c>
+      <c r="D65">
+        <v>75.1429</v>
+      </c>
+      <c r="E65">
+        <v>0.011192</v>
+      </c>
+      <c r="F65">
+        <v>1.1192</v>
+      </c>
+      <c r="G65">
+        <v>0.009528</v>
+      </c>
+      <c r="H65">
+        <v>0.9528</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>23</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C66">
+        <v>7</v>
+      </c>
+      <c r="D66">
+        <v>75.28570000000001</v>
+      </c>
+      <c r="E66">
+        <v>0.011171</v>
+      </c>
+      <c r="F66">
+        <v>1.1171</v>
+      </c>
+      <c r="G66">
+        <v>0.009505</v>
+      </c>
+      <c r="H66">
+        <v>0.9505</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C67">
+        <v>7</v>
+      </c>
+      <c r="D67">
+        <v>80</v>
+      </c>
+      <c r="E67">
+        <v>0.010513</v>
+      </c>
+      <c r="F67">
+        <v>1.0513</v>
+      </c>
+      <c r="G67">
+        <v>0.008809000000000001</v>
+      </c>
+      <c r="H67">
+        <v>0.8809</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>27</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C68">
+        <v>7</v>
+      </c>
+      <c r="D68">
+        <v>90.4286</v>
+      </c>
+      <c r="E68">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="F68">
+        <v>0.93</v>
+      </c>
+      <c r="G68">
+        <v>0.007534</v>
+      </c>
+      <c r="H68">
+        <v>0.7534</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>26</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C69">
+        <v>7</v>
+      </c>
+      <c r="D69">
+        <v>91.71429999999999</v>
+      </c>
+      <c r="E69">
+        <v>0.009169999999999999</v>
+      </c>
+      <c r="F69">
+        <v>0.917</v>
+      </c>
+      <c r="G69">
+        <v>0.007398</v>
+      </c>
+      <c r="H69">
+        <v>0.7398</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C70">
+        <v>7</v>
+      </c>
+      <c r="D70">
+        <v>106.1429</v>
+      </c>
+      <c r="E70">
+        <v>0.007922999999999999</v>
+      </c>
+      <c r="F70">
+        <v>0.7923</v>
+      </c>
+      <c r="G70">
+        <v>0.006104</v>
+      </c>
+      <c r="H70">
+        <v>0.6104000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>29</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C71">
+        <v>7</v>
+      </c>
+      <c r="D71">
+        <v>145.5714</v>
+      </c>
+      <c r="E71">
+        <v>0.005777</v>
+      </c>
+      <c r="F71">
+        <v>0.5777</v>
+      </c>
+      <c r="G71">
+        <v>0.003938</v>
+      </c>
+      <c r="H71">
+        <v>0.3938</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>30</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C72">
+        <v>7</v>
+      </c>
+      <c r="D72">
+        <v>158.5714</v>
+      </c>
+      <c r="E72">
+        <v>0.005304</v>
+      </c>
+      <c r="F72">
+        <v>0.5304</v>
+      </c>
+      <c r="G72">
+        <v>0.003477</v>
+      </c>
+      <c r="H72">
+        <v>0.3477</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>31</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C73">
+        <v>7</v>
+      </c>
+      <c r="D73">
+        <v>222.7143</v>
+      </c>
+      <c r="E73">
+        <v>0.003776</v>
+      </c>
+      <c r="F73">
+        <v>0.3776</v>
+      </c>
+      <c r="G73">
+        <v>0.002064</v>
+      </c>
+      <c r="H73">
+        <v>0.2064</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C74">
+        <v>7</v>
+      </c>
+      <c r="D74">
+        <v>241</v>
+      </c>
+      <c r="E74">
+        <v>0.00349</v>
+      </c>
+      <c r="F74">
+        <v>0.349</v>
+      </c>
+      <c r="G74">
+        <v>0.001817</v>
+      </c>
+      <c r="H74">
+        <v>0.1817</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C75">
+        <v>7</v>
+      </c>
+      <c r="D75">
+        <v>242.5714</v>
+      </c>
+      <c r="E75">
+        <v>0.003467</v>
+      </c>
+      <c r="F75">
+        <v>0.3467</v>
+      </c>
+      <c r="G75">
+        <v>0.001798</v>
+      </c>
+      <c r="H75">
+        <v>0.1798</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>34</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C76">
+        <v>7</v>
+      </c>
+      <c r="D76">
+        <v>259.8571</v>
+      </c>
+      <c r="E76">
+        <v>0.003236</v>
+      </c>
+      <c r="F76">
+        <v>0.3236</v>
+      </c>
+      <c r="G76">
+        <v>0.001605</v>
+      </c>
+      <c r="H76">
+        <v>0.1605</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C77">
+        <v>7</v>
+      </c>
+      <c r="D77">
+        <v>351.5714</v>
+      </c>
+      <c r="E77">
+        <v>0.002392</v>
+      </c>
+      <c r="F77">
+        <v>0.2392</v>
+      </c>
+      <c r="G77">
+        <v>0.000956</v>
+      </c>
+      <c r="H77">
+        <v>0.0956</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C78">
+        <v>7</v>
+      </c>
+      <c r="D78">
+        <v>376.7143</v>
+      </c>
+      <c r="E78">
+        <v>0.002233</v>
+      </c>
+      <c r="F78">
+        <v>0.2233</v>
+      </c>
+      <c r="G78">
+        <v>0.000846</v>
+      </c>
+      <c r="H78">
+        <v>0.08459999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>37</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C79">
+        <v>7</v>
+      </c>
+      <c r="D79">
+        <v>383</v>
+      </c>
+      <c r="E79">
+        <v>0.002196</v>
+      </c>
+      <c r="F79">
+        <v>0.2196</v>
+      </c>
+      <c r="G79">
+        <v>0.000821</v>
+      </c>
+      <c r="H79">
+        <v>0.08210000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C80">
+        <v>7</v>
+      </c>
+      <c r="D80">
+        <v>455.5714</v>
+      </c>
+      <c r="E80">
+        <v>0.001846</v>
+      </c>
+      <c r="F80">
+        <v>0.1846</v>
+      </c>
+      <c r="G80">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H80">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C81">
+        <v>7</v>
+      </c>
+      <c r="D81">
+        <v>462.2857</v>
+      </c>
+      <c r="E81">
+        <v>0.001819</v>
+      </c>
+      <c r="F81">
+        <v>0.1819</v>
+      </c>
+      <c r="G81">
+        <v>0.000584</v>
+      </c>
+      <c r="H81">
+        <v>0.0584</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>35</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C82">
+        <v>7</v>
+      </c>
+      <c r="D82">
+        <v>497.8571</v>
+      </c>
+      <c r="E82">
+        <v>0.001689</v>
+      </c>
+      <c r="F82">
+        <v>0.1689</v>
+      </c>
+      <c r="G82">
+        <v>0.000509</v>
+      </c>
+      <c r="H82">
+        <v>0.0509</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>41</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C83">
+        <v>7</v>
+      </c>
+      <c r="D83">
+        <v>505.2857</v>
+      </c>
+      <c r="E83">
+        <v>0.001664</v>
+      </c>
+      <c r="F83">
+        <v>0.1664</v>
+      </c>
+      <c r="G83">
+        <v>0.000495</v>
+      </c>
+      <c r="H83">
+        <v>0.0495</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>42</v>
+      </c>
+      <c r="B84" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C84">
+        <v>7</v>
+      </c>
+      <c r="D84">
+        <v>576.4286</v>
+      </c>
+      <c r="E84">
+        <v>0.001459</v>
+      </c>
+      <c r="F84">
+        <v>0.1459</v>
+      </c>
+      <c r="G84">
+        <v>0.000387</v>
+      </c>
+      <c r="H84">
+        <v>0.0387</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>43</v>
+      </c>
+      <c r="B85" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C85">
+        <v>7</v>
+      </c>
+      <c r="D85">
+        <v>640.7143</v>
+      </c>
+      <c r="E85">
+        <v>0.001313</v>
+      </c>
+      <c r="F85">
+        <v>0.1313</v>
+      </c>
+      <c r="G85">
+        <v>0.000316</v>
+      </c>
+      <c r="H85">
+        <v>0.0316</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>44</v>
+      </c>
+      <c r="B86" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C86">
+        <v>7</v>
+      </c>
+      <c r="D86">
+        <v>747.8570999999999</v>
+      </c>
+      <c r="E86">
+        <v>0.001125</v>
+      </c>
+      <c r="F86">
+        <v>0.1125</v>
+      </c>
+      <c r="G86">
+        <v>0.000235</v>
+      </c>
+      <c r="H86">
+        <v>0.0235</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C87">
+        <v>7</v>
+      </c>
+      <c r="D87">
+        <v>890.7143</v>
+      </c>
+      <c r="E87">
+        <v>0.000944</v>
+      </c>
+      <c r="F87">
+        <v>0.0944</v>
+      </c>
+      <c r="G87">
+        <v>0.000167</v>
+      </c>
+      <c r="H87">
+        <v>0.0167</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>47</v>
+      </c>
+      <c r="B88" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C88">
+        <v>7</v>
+      </c>
+      <c r="D88">
+        <v>1069.2857</v>
+      </c>
+      <c r="E88">
+        <v>0.000787</v>
+      </c>
+      <c r="F88">
+        <v>0.07870000000000001</v>
+      </c>
+      <c r="G88">
+        <v>0.000117</v>
+      </c>
+      <c r="H88">
+        <v>0.0117</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>48</v>
+      </c>
+      <c r="B89" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C89">
+        <v>7</v>
+      </c>
+      <c r="D89">
+        <v>1126.4286</v>
+      </c>
+      <c r="E89">
+        <v>0.0007470000000000001</v>
+      </c>
+      <c r="F89">
+        <v>0.0747</v>
+      </c>
+      <c r="G89">
+        <v>0.000106</v>
+      </c>
+      <c r="H89">
+        <v>0.0106</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>46</v>
+      </c>
+      <c r="B90" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C90">
+        <v>7</v>
+      </c>
+      <c r="D90">
+        <v>1176.4286</v>
+      </c>
+      <c r="E90">
+        <v>0.000715</v>
+      </c>
+      <c r="F90">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="G90">
+        <v>9.7E-05</v>
+      </c>
+      <c r="H90">
+        <v>0.0097</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>49</v>
+      </c>
+      <c r="B91" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C91">
+        <v>7</v>
+      </c>
+      <c r="D91">
+        <v>1197.8571</v>
+      </c>
+      <c r="E91">
+        <v>0.000702</v>
+      </c>
+      <c r="F91">
+        <v>0.0702</v>
+      </c>
+      <c r="G91">
+        <v>9.399999999999999E-05</v>
+      </c>
+      <c r="H91">
+        <v>0.0094</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>50</v>
+      </c>
+      <c r="B92" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C92">
+        <v>7</v>
+      </c>
+      <c r="D92">
+        <v>1197.8571</v>
+      </c>
+      <c r="E92">
+        <v>0.000702</v>
+      </c>
+      <c r="F92">
+        <v>0.0702</v>
+      </c>
+      <c r="G92">
+        <v>9.399999999999999E-05</v>
+      </c>
+      <c r="H92">
+        <v>0.0094</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>51</v>
+      </c>
+      <c r="B93" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C93">
+        <v>7</v>
+      </c>
+      <c r="D93">
+        <v>1197.8571</v>
+      </c>
+      <c r="E93">
+        <v>0.000702</v>
+      </c>
+      <c r="F93">
+        <v>0.0702</v>
+      </c>
+      <c r="G93">
+        <v>9.399999999999999E-05</v>
+      </c>
+      <c r="H93">
+        <v>0.0094</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>52</v>
+      </c>
+      <c r="B94" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C94">
+        <v>7</v>
+      </c>
+      <c r="D94">
+        <v>1326.4286</v>
+      </c>
+      <c r="E94">
+        <v>0.000634</v>
+      </c>
+      <c r="F94">
+        <v>0.0634</v>
+      </c>
+      <c r="G94">
+        <v>7.7E-05</v>
+      </c>
+      <c r="H94">
+        <v>0.0077</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>53</v>
+      </c>
+      <c r="B95" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C95">
+        <v>7</v>
+      </c>
+      <c r="D95">
+        <v>1497.8571</v>
+      </c>
+      <c r="E95">
+        <v>0.000561</v>
+      </c>
+      <c r="F95">
+        <v>0.0561</v>
+      </c>
+      <c r="G95">
+        <v>6E-05</v>
+      </c>
+      <c r="H95">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>54</v>
+      </c>
+      <c r="B96" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C96">
+        <v>7</v>
+      </c>
+      <c r="D96">
+        <v>1926.4286</v>
+      </c>
+      <c r="E96">
+        <v>0.000437</v>
+      </c>
+      <c r="F96">
+        <v>0.0437</v>
+      </c>
+      <c r="G96">
+        <v>3.7E-05</v>
+      </c>
+      <c r="H96">
+        <v>0.0037</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>55</v>
+      </c>
+      <c r="B97" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C97">
+        <v>7</v>
+      </c>
+      <c r="D97">
+        <v>1926.4286</v>
+      </c>
+      <c r="E97">
+        <v>0.000437</v>
+      </c>
+      <c r="F97">
+        <v>0.0437</v>
+      </c>
+      <c r="G97">
+        <v>3.7E-05</v>
+      </c>
+      <c r="H97">
+        <v>0.0037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3068,6 +3068,1254 @@
         <v>0.0037</v>
       </c>
     </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C98">
+        <v>7</v>
+      </c>
+      <c r="D98">
+        <v>5.5514</v>
+      </c>
+      <c r="E98">
+        <v>0.151973</v>
+      </c>
+      <c r="F98">
+        <v>15.1973</v>
+      </c>
+      <c r="G98">
+        <v>0.162992</v>
+      </c>
+      <c r="H98">
+        <v>16.2992</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C99">
+        <v>7</v>
+      </c>
+      <c r="D99">
+        <v>5.6286</v>
+      </c>
+      <c r="E99">
+        <v>0.14989</v>
+      </c>
+      <c r="F99">
+        <v>14.989</v>
+      </c>
+      <c r="G99">
+        <v>0.160718</v>
+      </c>
+      <c r="H99">
+        <v>16.0718</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>10</v>
+      </c>
+      <c r="B100" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C100">
+        <v>7</v>
+      </c>
+      <c r="D100">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E100">
+        <v>0.100556</v>
+      </c>
+      <c r="F100">
+        <v>10.0556</v>
+      </c>
+      <c r="G100">
+        <v>0.10686</v>
+      </c>
+      <c r="H100">
+        <v>10.686</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C101">
+        <v>7</v>
+      </c>
+      <c r="D101">
+        <v>8.632899999999999</v>
+      </c>
+      <c r="E101">
+        <v>0.097728</v>
+      </c>
+      <c r="F101">
+        <v>9.7728</v>
+      </c>
+      <c r="G101">
+        <v>0.103773</v>
+      </c>
+      <c r="H101">
+        <v>10.3773</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C102">
+        <v>7</v>
+      </c>
+      <c r="D102">
+        <v>10.6143</v>
+      </c>
+      <c r="E102">
+        <v>0.079484</v>
+      </c>
+      <c r="F102">
+        <v>7.9484</v>
+      </c>
+      <c r="G102">
+        <v>0.083861</v>
+      </c>
+      <c r="H102">
+        <v>8.386100000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C103">
+        <v>7</v>
+      </c>
+      <c r="D103">
+        <v>11.0429</v>
+      </c>
+      <c r="E103">
+        <v>0.07639899999999999</v>
+      </c>
+      <c r="F103">
+        <v>7.6399</v>
+      </c>
+      <c r="G103">
+        <v>0.080495</v>
+      </c>
+      <c r="H103">
+        <v>8.0495</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>14</v>
+      </c>
+      <c r="B104" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C104">
+        <v>7</v>
+      </c>
+      <c r="D104">
+        <v>15.3857</v>
+      </c>
+      <c r="E104">
+        <v>0.054834</v>
+      </c>
+      <c r="F104">
+        <v>5.4834</v>
+      </c>
+      <c r="G104">
+        <v>0.056968</v>
+      </c>
+      <c r="H104">
+        <v>5.6968</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C105">
+        <v>7</v>
+      </c>
+      <c r="D105">
+        <v>19.7143</v>
+      </c>
+      <c r="E105">
+        <v>0.042795</v>
+      </c>
+      <c r="F105">
+        <v>4.2795</v>
+      </c>
+      <c r="G105">
+        <v>0.043842</v>
+      </c>
+      <c r="H105">
+        <v>4.3842</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>16</v>
+      </c>
+      <c r="B106" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C106">
+        <v>7</v>
+      </c>
+      <c r="D106">
+        <v>34.1429</v>
+      </c>
+      <c r="E106">
+        <v>0.02471</v>
+      </c>
+      <c r="F106">
+        <v>2.471</v>
+      </c>
+      <c r="G106">
+        <v>0.024163</v>
+      </c>
+      <c r="H106">
+        <v>2.4163</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C107">
+        <v>7</v>
+      </c>
+      <c r="D107">
+        <v>38.7143</v>
+      </c>
+      <c r="E107">
+        <v>0.021792</v>
+      </c>
+      <c r="F107">
+        <v>2.1792</v>
+      </c>
+      <c r="G107">
+        <v>0.020999</v>
+      </c>
+      <c r="H107">
+        <v>2.0999</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>17</v>
+      </c>
+      <c r="B108" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C108">
+        <v>7</v>
+      </c>
+      <c r="D108">
+        <v>39.4286</v>
+      </c>
+      <c r="E108">
+        <v>0.021397</v>
+      </c>
+      <c r="F108">
+        <v>2.1397</v>
+      </c>
+      <c r="G108">
+        <v>0.020571</v>
+      </c>
+      <c r="H108">
+        <v>2.0571</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>21</v>
+      </c>
+      <c r="B109" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C109">
+        <v>7</v>
+      </c>
+      <c r="D109">
+        <v>43.8571</v>
+      </c>
+      <c r="E109">
+        <v>0.019237</v>
+      </c>
+      <c r="F109">
+        <v>1.9237</v>
+      </c>
+      <c r="G109">
+        <v>0.018233</v>
+      </c>
+      <c r="H109">
+        <v>1.8233</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>18</v>
+      </c>
+      <c r="B110" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C110">
+        <v>7</v>
+      </c>
+      <c r="D110">
+        <v>47</v>
+      </c>
+      <c r="E110">
+        <v>0.01795</v>
+      </c>
+      <c r="F110">
+        <v>1.795</v>
+      </c>
+      <c r="G110">
+        <v>0.016843</v>
+      </c>
+      <c r="H110">
+        <v>1.6843</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>20</v>
+      </c>
+      <c r="B111" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C111">
+        <v>7</v>
+      </c>
+      <c r="D111">
+        <v>51.2857</v>
+      </c>
+      <c r="E111">
+        <v>0.01645</v>
+      </c>
+      <c r="F111">
+        <v>1.645</v>
+      </c>
+      <c r="G111">
+        <v>0.015226</v>
+      </c>
+      <c r="H111">
+        <v>1.5226</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>22</v>
+      </c>
+      <c r="B112" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C112">
+        <v>7</v>
+      </c>
+      <c r="D112">
+        <v>52.7143</v>
+      </c>
+      <c r="E112">
+        <v>0.016005</v>
+      </c>
+      <c r="F112">
+        <v>1.6005</v>
+      </c>
+      <c r="G112">
+        <v>0.014746</v>
+      </c>
+      <c r="H112">
+        <v>1.4746</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B113" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C113">
+        <v>7</v>
+      </c>
+      <c r="D113">
+        <v>75.28570000000001</v>
+      </c>
+      <c r="E113">
+        <v>0.011206</v>
+      </c>
+      <c r="F113">
+        <v>1.1206</v>
+      </c>
+      <c r="G113">
+        <v>0.009612000000000001</v>
+      </c>
+      <c r="H113">
+        <v>0.9612000000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>24</v>
+      </c>
+      <c r="B114" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C114">
+        <v>7</v>
+      </c>
+      <c r="D114">
+        <v>83.5714</v>
+      </c>
+      <c r="E114">
+        <v>0.010095</v>
+      </c>
+      <c r="F114">
+        <v>1.0095</v>
+      </c>
+      <c r="G114">
+        <v>0.008437</v>
+      </c>
+      <c r="H114">
+        <v>0.8437</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>26</v>
+      </c>
+      <c r="B115" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C115">
+        <v>7</v>
+      </c>
+      <c r="D115">
+        <v>91.71429999999999</v>
+      </c>
+      <c r="E115">
+        <v>0.009199000000000001</v>
+      </c>
+      <c r="F115">
+        <v>0.9199000000000001</v>
+      </c>
+      <c r="G115">
+        <v>0.007495</v>
+      </c>
+      <c r="H115">
+        <v>0.7495000000000001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>28</v>
+      </c>
+      <c r="B116" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C116">
+        <v>7</v>
+      </c>
+      <c r="D116">
+        <v>107.5714</v>
+      </c>
+      <c r="E116">
+        <v>0.007842999999999999</v>
+      </c>
+      <c r="F116">
+        <v>0.7843</v>
+      </c>
+      <c r="G116">
+        <v>0.006085</v>
+      </c>
+      <c r="H116">
+        <v>0.6085</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>29</v>
+      </c>
+      <c r="B117" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C117">
+        <v>7</v>
+      </c>
+      <c r="D117">
+        <v>110.1429</v>
+      </c>
+      <c r="E117">
+        <v>0.00766</v>
+      </c>
+      <c r="F117">
+        <v>0.766</v>
+      </c>
+      <c r="G117">
+        <v>0.005897</v>
+      </c>
+      <c r="H117">
+        <v>0.5897</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>25</v>
+      </c>
+      <c r="B118" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C118">
+        <v>7</v>
+      </c>
+      <c r="D118">
+        <v>133.1429</v>
+      </c>
+      <c r="E118">
+        <v>0.006337</v>
+      </c>
+      <c r="F118">
+        <v>0.6337</v>
+      </c>
+      <c r="G118">
+        <v>0.004552</v>
+      </c>
+      <c r="H118">
+        <v>0.4552</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>27</v>
+      </c>
+      <c r="B119" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C119">
+        <v>7</v>
+      </c>
+      <c r="D119">
+        <v>133.7143</v>
+      </c>
+      <c r="E119">
+        <v>0.006309</v>
+      </c>
+      <c r="F119">
+        <v>0.6309</v>
+      </c>
+      <c r="G119">
+        <v>0.004524</v>
+      </c>
+      <c r="H119">
+        <v>0.4524</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>34</v>
+      </c>
+      <c r="B120" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C120">
+        <v>7</v>
+      </c>
+      <c r="D120">
+        <v>153</v>
+      </c>
+      <c r="E120">
+        <v>0.005514</v>
+      </c>
+      <c r="F120">
+        <v>0.5514</v>
+      </c>
+      <c r="G120">
+        <v>0.003736</v>
+      </c>
+      <c r="H120">
+        <v>0.3736</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>30</v>
+      </c>
+      <c r="B121" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C121">
+        <v>7</v>
+      </c>
+      <c r="D121">
+        <v>157.1429</v>
+      </c>
+      <c r="E121">
+        <v>0.005369</v>
+      </c>
+      <c r="F121">
+        <v>0.5369</v>
+      </c>
+      <c r="G121">
+        <v>0.003594</v>
+      </c>
+      <c r="H121">
+        <v>0.3594</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>40</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C122">
+        <v>7</v>
+      </c>
+      <c r="D122">
+        <v>186</v>
+      </c>
+      <c r="E122">
+        <v>0.004536</v>
+      </c>
+      <c r="F122">
+        <v>0.4536</v>
+      </c>
+      <c r="G122">
+        <v>0.002799</v>
+      </c>
+      <c r="H122">
+        <v>0.2799</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>31</v>
+      </c>
+      <c r="B123" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C123">
+        <v>7</v>
+      </c>
+      <c r="D123">
+        <v>193.2857</v>
+      </c>
+      <c r="E123">
+        <v>0.004365</v>
+      </c>
+      <c r="F123">
+        <v>0.4365</v>
+      </c>
+      <c r="G123">
+        <v>0.00264</v>
+      </c>
+      <c r="H123">
+        <v>0.264</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>39</v>
+      </c>
+      <c r="B124" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C124">
+        <v>7</v>
+      </c>
+      <c r="D124">
+        <v>224.2857</v>
+      </c>
+      <c r="E124">
+        <v>0.003762</v>
+      </c>
+      <c r="F124">
+        <v>0.3762</v>
+      </c>
+      <c r="G124">
+        <v>0.002093</v>
+      </c>
+      <c r="H124">
+        <v>0.2093</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>33</v>
+      </c>
+      <c r="B125" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C125">
+        <v>7</v>
+      </c>
+      <c r="D125">
+        <v>228.1429</v>
+      </c>
+      <c r="E125">
+        <v>0.003698</v>
+      </c>
+      <c r="F125">
+        <v>0.3698</v>
+      </c>
+      <c r="G125">
+        <v>0.002037</v>
+      </c>
+      <c r="H125">
+        <v>0.2037</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>36</v>
+      </c>
+      <c r="B126" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C126">
+        <v>7</v>
+      </c>
+      <c r="D126">
+        <v>341.7143</v>
+      </c>
+      <c r="E126">
+        <v>0.002469</v>
+      </c>
+      <c r="F126">
+        <v>0.2469</v>
+      </c>
+      <c r="G126">
+        <v>0.001038</v>
+      </c>
+      <c r="H126">
+        <v>0.1038</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>37</v>
+      </c>
+      <c r="B127" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C127">
+        <v>7</v>
+      </c>
+      <c r="D127">
+        <v>378.8571</v>
+      </c>
+      <c r="E127">
+        <v>0.002227</v>
+      </c>
+      <c r="F127">
+        <v>0.2227</v>
+      </c>
+      <c r="G127">
+        <v>0.000865</v>
+      </c>
+      <c r="H127">
+        <v>0.08649999999999999</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>38</v>
+      </c>
+      <c r="B128" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C128">
+        <v>7</v>
+      </c>
+      <c r="D128">
+        <v>383.7143</v>
+      </c>
+      <c r="E128">
+        <v>0.002199</v>
+      </c>
+      <c r="F128">
+        <v>0.2199</v>
+      </c>
+      <c r="G128">
+        <v>0.000846</v>
+      </c>
+      <c r="H128">
+        <v>0.08459999999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>32</v>
+      </c>
+      <c r="B129" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C129">
+        <v>7</v>
+      </c>
+      <c r="D129">
+        <v>483.5714</v>
+      </c>
+      <c r="E129">
+        <v>0.001745</v>
+      </c>
+      <c r="F129">
+        <v>0.1745</v>
+      </c>
+      <c r="G129">
+        <v>0.000556</v>
+      </c>
+      <c r="H129">
+        <v>0.0556</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>35</v>
+      </c>
+      <c r="B130" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C130">
+        <v>7</v>
+      </c>
+      <c r="D130">
+        <v>486.7143</v>
+      </c>
+      <c r="E130">
+        <v>0.001733</v>
+      </c>
+      <c r="F130">
+        <v>0.1733</v>
+      </c>
+      <c r="G130">
+        <v>0.00055</v>
+      </c>
+      <c r="H130">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>41</v>
+      </c>
+      <c r="B131" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C131">
+        <v>7</v>
+      </c>
+      <c r="D131">
+        <v>494.1429</v>
+      </c>
+      <c r="E131">
+        <v>0.001707</v>
+      </c>
+      <c r="F131">
+        <v>0.1707</v>
+      </c>
+      <c r="G131">
+        <v>0.000535</v>
+      </c>
+      <c r="H131">
+        <v>0.0535</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>42</v>
+      </c>
+      <c r="B132" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C132">
+        <v>7</v>
+      </c>
+      <c r="D132">
+        <v>576.4286</v>
+      </c>
+      <c r="E132">
+        <v>0.001464</v>
+      </c>
+      <c r="F132">
+        <v>0.1464</v>
+      </c>
+      <c r="G132">
+        <v>0.000401</v>
+      </c>
+      <c r="H132">
+        <v>0.0401</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B133" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C133">
+        <v>7</v>
+      </c>
+      <c r="D133">
+        <v>747.8570999999999</v>
+      </c>
+      <c r="E133">
+        <v>0.001128</v>
+      </c>
+      <c r="F133">
+        <v>0.1128</v>
+      </c>
+      <c r="G133">
+        <v>0.000244</v>
+      </c>
+      <c r="H133">
+        <v>0.0244</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>45</v>
+      </c>
+      <c r="B134" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C134">
+        <v>7</v>
+      </c>
+      <c r="D134">
+        <v>890.7143</v>
+      </c>
+      <c r="E134">
+        <v>0.000947</v>
+      </c>
+      <c r="F134">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="G134">
+        <v>0.000174</v>
+      </c>
+      <c r="H134">
+        <v>0.0174</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>43</v>
+      </c>
+      <c r="B135" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C135">
+        <v>7</v>
+      </c>
+      <c r="D135">
+        <v>890.7143</v>
+      </c>
+      <c r="E135">
+        <v>0.000947</v>
+      </c>
+      <c r="F135">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="G135">
+        <v>0.000174</v>
+      </c>
+      <c r="H135">
+        <v>0.0174</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>47</v>
+      </c>
+      <c r="B136" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C136">
+        <v>7</v>
+      </c>
+      <c r="D136">
+        <v>1069.2857</v>
+      </c>
+      <c r="E136">
+        <v>0.000789</v>
+      </c>
+      <c r="F136">
+        <v>0.0789</v>
+      </c>
+      <c r="G136">
+        <v>0.000122</v>
+      </c>
+      <c r="H136">
+        <v>0.0122</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>48</v>
+      </c>
+      <c r="B137" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C137">
+        <v>7</v>
+      </c>
+      <c r="D137">
+        <v>1126.4286</v>
+      </c>
+      <c r="E137">
+        <v>0.000749</v>
+      </c>
+      <c r="F137">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="G137">
+        <v>0.00011</v>
+      </c>
+      <c r="H137">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>46</v>
+      </c>
+      <c r="B138" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C138">
+        <v>7</v>
+      </c>
+      <c r="D138">
+        <v>1176.4286</v>
+      </c>
+      <c r="E138">
+        <v>0.000717</v>
+      </c>
+      <c r="F138">
+        <v>0.0717</v>
+      </c>
+      <c r="G138">
+        <v>0.000101</v>
+      </c>
+      <c r="H138">
+        <v>0.0101</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>49</v>
+      </c>
+      <c r="B139" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C139">
+        <v>7</v>
+      </c>
+      <c r="D139">
+        <v>1197.8571</v>
+      </c>
+      <c r="E139">
+        <v>0.000704</v>
+      </c>
+      <c r="F139">
+        <v>0.0704</v>
+      </c>
+      <c r="G139">
+        <v>9.8E-05</v>
+      </c>
+      <c r="H139">
+        <v>0.0098</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>50</v>
+      </c>
+      <c r="B140" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C140">
+        <v>7</v>
+      </c>
+      <c r="D140">
+        <v>1197.8571</v>
+      </c>
+      <c r="E140">
+        <v>0.000704</v>
+      </c>
+      <c r="F140">
+        <v>0.0704</v>
+      </c>
+      <c r="G140">
+        <v>9.8E-05</v>
+      </c>
+      <c r="H140">
+        <v>0.0098</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>51</v>
+      </c>
+      <c r="B141" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C141">
+        <v>7</v>
+      </c>
+      <c r="D141">
+        <v>1197.8571</v>
+      </c>
+      <c r="E141">
+        <v>0.000704</v>
+      </c>
+      <c r="F141">
+        <v>0.0704</v>
+      </c>
+      <c r="G141">
+        <v>9.8E-05</v>
+      </c>
+      <c r="H141">
+        <v>0.0098</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>52</v>
+      </c>
+      <c r="B142" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C142">
+        <v>7</v>
+      </c>
+      <c r="D142">
+        <v>1326.4286</v>
+      </c>
+      <c r="E142">
+        <v>0.000636</v>
+      </c>
+      <c r="F142">
+        <v>0.0636</v>
+      </c>
+      <c r="G142">
+        <v>8.000000000000001E-05</v>
+      </c>
+      <c r="H142">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
+        <v>53</v>
+      </c>
+      <c r="B143" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C143">
+        <v>7</v>
+      </c>
+      <c r="D143">
+        <v>1497.8571</v>
+      </c>
+      <c r="E143">
+        <v>0.000563</v>
+      </c>
+      <c r="F143">
+        <v>0.0563</v>
+      </c>
+      <c r="G143">
+        <v>6.3E-05</v>
+      </c>
+      <c r="H143">
+        <v>0.0063</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
+        <v>55</v>
+      </c>
+      <c r="B144" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C144">
+        <v>7</v>
+      </c>
+      <c r="D144">
+        <v>2033.5714</v>
+      </c>
+      <c r="E144">
+        <v>0.000415</v>
+      </c>
+      <c r="F144">
+        <v>0.0415</v>
+      </c>
+      <c r="G144">
+        <v>3.4E-05</v>
+      </c>
+      <c r="H144">
+        <v>0.0034</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
+        <v>54</v>
+      </c>
+      <c r="B145" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C145">
+        <v>7</v>
+      </c>
+      <c r="D145">
+        <v>2355</v>
+      </c>
+      <c r="E145">
+        <v>0.000358</v>
+      </c>
+      <c r="F145">
+        <v>0.0358</v>
+      </c>
+      <c r="G145">
+        <v>2.6E-05</v>
+      </c>
+      <c r="H145">
+        <v>0.0026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4316,6 +4316,1254 @@
         <v>0.0026</v>
       </c>
     </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C146">
+        <v>7</v>
+      </c>
+      <c r="D146">
+        <v>4.9671</v>
+      </c>
+      <c r="E146">
+        <v>0.168128</v>
+      </c>
+      <c r="F146">
+        <v>16.8128</v>
+      </c>
+      <c r="G146">
+        <v>0.181375</v>
+      </c>
+      <c r="H146">
+        <v>18.1375</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C147">
+        <v>7</v>
+      </c>
+      <c r="D147">
+        <v>6.5114</v>
+      </c>
+      <c r="E147">
+        <v>0.128254</v>
+      </c>
+      <c r="F147">
+        <v>12.8254</v>
+      </c>
+      <c r="G147">
+        <v>0.13761</v>
+      </c>
+      <c r="H147">
+        <v>13.761</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>10</v>
+      </c>
+      <c r="B148" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C148">
+        <v>7</v>
+      </c>
+      <c r="D148">
+        <v>8.334300000000001</v>
+      </c>
+      <c r="E148">
+        <v>0.100202</v>
+      </c>
+      <c r="F148">
+        <v>10.0202</v>
+      </c>
+      <c r="G148">
+        <v>0.106826</v>
+      </c>
+      <c r="H148">
+        <v>10.6826</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>11</v>
+      </c>
+      <c r="B149" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C149">
+        <v>7</v>
+      </c>
+      <c r="D149">
+        <v>8.617100000000001</v>
+      </c>
+      <c r="E149">
+        <v>0.096913</v>
+      </c>
+      <c r="F149">
+        <v>9.6913</v>
+      </c>
+      <c r="G149">
+        <v>0.103217</v>
+      </c>
+      <c r="H149">
+        <v>10.3217</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>13</v>
+      </c>
+      <c r="B150" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C150">
+        <v>7</v>
+      </c>
+      <c r="D150">
+        <v>9.4</v>
+      </c>
+      <c r="E150">
+        <v>0.088842</v>
+      </c>
+      <c r="F150">
+        <v>8.8842</v>
+      </c>
+      <c r="G150">
+        <v>0.094361</v>
+      </c>
+      <c r="H150">
+        <v>9.4361</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>12</v>
+      </c>
+      <c r="B151" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C151">
+        <v>7</v>
+      </c>
+      <c r="D151">
+        <v>11.3857</v>
+      </c>
+      <c r="E151">
+        <v>0.073348</v>
+      </c>
+      <c r="F151">
+        <v>7.3348</v>
+      </c>
+      <c r="G151">
+        <v>0.077362</v>
+      </c>
+      <c r="H151">
+        <v>7.7362</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>14</v>
+      </c>
+      <c r="B152" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C152">
+        <v>7</v>
+      </c>
+      <c r="D152">
+        <v>14.6714</v>
+      </c>
+      <c r="E152">
+        <v>0.056921</v>
+      </c>
+      <c r="F152">
+        <v>5.6921</v>
+      </c>
+      <c r="G152">
+        <v>0.059348</v>
+      </c>
+      <c r="H152">
+        <v>5.9348</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C153">
+        <v>7</v>
+      </c>
+      <c r="D153">
+        <v>20.1429</v>
+      </c>
+      <c r="E153">
+        <v>0.04146</v>
+      </c>
+      <c r="F153">
+        <v>4.146</v>
+      </c>
+      <c r="G153">
+        <v>0.042405</v>
+      </c>
+      <c r="H153">
+        <v>4.2405</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>16</v>
+      </c>
+      <c r="B154" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
+      </c>
+      <c r="D154">
+        <v>30.4286</v>
+      </c>
+      <c r="E154">
+        <v>0.027445</v>
+      </c>
+      <c r="F154">
+        <v>2.7445</v>
+      </c>
+      <c r="G154">
+        <v>0.027078</v>
+      </c>
+      <c r="H154">
+        <v>2.7078</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>19</v>
+      </c>
+      <c r="B155" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C155">
+        <v>7</v>
+      </c>
+      <c r="D155">
+        <v>37.7143</v>
+      </c>
+      <c r="E155">
+        <v>0.022143</v>
+      </c>
+      <c r="F155">
+        <v>2.2143</v>
+      </c>
+      <c r="G155">
+        <v>0.021298</v>
+      </c>
+      <c r="H155">
+        <v>2.1298</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>21</v>
+      </c>
+      <c r="B156" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C156">
+        <v>7</v>
+      </c>
+      <c r="D156">
+        <v>41.1429</v>
+      </c>
+      <c r="E156">
+        <v>0.020298</v>
+      </c>
+      <c r="F156">
+        <v>2.0298</v>
+      </c>
+      <c r="G156">
+        <v>0.019292</v>
+      </c>
+      <c r="H156">
+        <v>1.9292</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" t="s">
+        <v>17</v>
+      </c>
+      <c r="B157" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C157">
+        <v>7</v>
+      </c>
+      <c r="D157">
+        <v>42</v>
+      </c>
+      <c r="E157">
+        <v>0.019884</v>
+      </c>
+      <c r="F157">
+        <v>1.9884</v>
+      </c>
+      <c r="G157">
+        <v>0.018842</v>
+      </c>
+      <c r="H157">
+        <v>1.8842</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" t="s">
+        <v>18</v>
+      </c>
+      <c r="B158" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C158">
+        <v>7</v>
+      </c>
+      <c r="D158">
+        <v>50.4286</v>
+      </c>
+      <c r="E158">
+        <v>0.01656</v>
+      </c>
+      <c r="F158">
+        <v>1.656</v>
+      </c>
+      <c r="G158">
+        <v>0.01524</v>
+      </c>
+      <c r="H158">
+        <v>1.524</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" t="s">
+        <v>20</v>
+      </c>
+      <c r="B159" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C159">
+        <v>7</v>
+      </c>
+      <c r="D159">
+        <v>51.2857</v>
+      </c>
+      <c r="E159">
+        <v>0.016284</v>
+      </c>
+      <c r="F159">
+        <v>1.6284</v>
+      </c>
+      <c r="G159">
+        <v>0.014941</v>
+      </c>
+      <c r="H159">
+        <v>1.4941</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" t="s">
+        <v>22</v>
+      </c>
+      <c r="B160" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C160">
+        <v>7</v>
+      </c>
+      <c r="D160">
+        <v>57.8571</v>
+      </c>
+      <c r="E160">
+        <v>0.014434</v>
+      </c>
+      <c r="F160">
+        <v>1.4434</v>
+      </c>
+      <c r="G160">
+        <v>0.012947</v>
+      </c>
+      <c r="H160">
+        <v>1.2947</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" t="s">
+        <v>23</v>
+      </c>
+      <c r="B161" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C161">
+        <v>7</v>
+      </c>
+      <c r="D161">
+        <v>83</v>
+      </c>
+      <c r="E161">
+        <v>0.010062</v>
+      </c>
+      <c r="F161">
+        <v>1.0062</v>
+      </c>
+      <c r="G161">
+        <v>0.008283</v>
+      </c>
+      <c r="H161">
+        <v>0.8283</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" t="s">
+        <v>24</v>
+      </c>
+      <c r="B162" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C162">
+        <v>7</v>
+      </c>
+      <c r="D162">
+        <v>87.71429999999999</v>
+      </c>
+      <c r="E162">
+        <v>0.009521</v>
+      </c>
+      <c r="F162">
+        <v>0.9520999999999999</v>
+      </c>
+      <c r="G162">
+        <v>0.007715</v>
+      </c>
+      <c r="H162">
+        <v>0.7715</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" t="s">
+        <v>26</v>
+      </c>
+      <c r="B163" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C163">
+        <v>7</v>
+      </c>
+      <c r="D163">
+        <v>92.4286</v>
+      </c>
+      <c r="E163">
+        <v>0.009035</v>
+      </c>
+      <c r="F163">
+        <v>0.9035</v>
+      </c>
+      <c r="G163">
+        <v>0.007206</v>
+      </c>
+      <c r="H163">
+        <v>0.7206</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" t="s">
+        <v>29</v>
+      </c>
+      <c r="B164" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C164">
+        <v>7</v>
+      </c>
+      <c r="D164">
+        <v>105.8571</v>
+      </c>
+      <c r="E164">
+        <v>0.007889</v>
+      </c>
+      <c r="F164">
+        <v>0.7889</v>
+      </c>
+      <c r="G164">
+        <v>0.006018</v>
+      </c>
+      <c r="H164">
+        <v>0.6018</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" t="s">
+        <v>28</v>
+      </c>
+      <c r="B165" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C165">
+        <v>7</v>
+      </c>
+      <c r="D165">
+        <v>119.5714</v>
+      </c>
+      <c r="E165">
+        <v>0.006984</v>
+      </c>
+      <c r="F165">
+        <v>0.6984</v>
+      </c>
+      <c r="G165">
+        <v>0.005094</v>
+      </c>
+      <c r="H165">
+        <v>0.5094</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" t="s">
+        <v>40</v>
+      </c>
+      <c r="B166" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C166">
+        <v>7</v>
+      </c>
+      <c r="D166">
+        <v>123.1429</v>
+      </c>
+      <c r="E166">
+        <v>0.006782</v>
+      </c>
+      <c r="F166">
+        <v>0.6782</v>
+      </c>
+      <c r="G166">
+        <v>0.00489</v>
+      </c>
+      <c r="H166">
+        <v>0.489</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" t="s">
+        <v>27</v>
+      </c>
+      <c r="B167" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C167">
+        <v>7</v>
+      </c>
+      <c r="D167">
+        <v>135.1429</v>
+      </c>
+      <c r="E167">
+        <v>0.006179</v>
+      </c>
+      <c r="F167">
+        <v>0.6179</v>
+      </c>
+      <c r="G167">
+        <v>0.004287</v>
+      </c>
+      <c r="H167">
+        <v>0.4287</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" t="s">
+        <v>30</v>
+      </c>
+      <c r="B168" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C168">
+        <v>7</v>
+      </c>
+      <c r="D168">
+        <v>135.1429</v>
+      </c>
+      <c r="E168">
+        <v>0.006179</v>
+      </c>
+      <c r="F168">
+        <v>0.6179</v>
+      </c>
+      <c r="G168">
+        <v>0.004287</v>
+      </c>
+      <c r="H168">
+        <v>0.4287</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" t="s">
+        <v>34</v>
+      </c>
+      <c r="B169" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C169">
+        <v>7</v>
+      </c>
+      <c r="D169">
+        <v>143</v>
+      </c>
+      <c r="E169">
+        <v>0.00584</v>
+      </c>
+      <c r="F169">
+        <v>0.584</v>
+      </c>
+      <c r="G169">
+        <v>0.003953</v>
+      </c>
+      <c r="H169">
+        <v>0.3953</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" t="s">
+        <v>25</v>
+      </c>
+      <c r="B170" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C170">
+        <v>7</v>
+      </c>
+      <c r="D170">
+        <v>145.8571</v>
+      </c>
+      <c r="E170">
+        <v>0.005726</v>
+      </c>
+      <c r="F170">
+        <v>0.5726</v>
+      </c>
+      <c r="G170">
+        <v>0.003841</v>
+      </c>
+      <c r="H170">
+        <v>0.3841</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" t="s">
+        <v>31</v>
+      </c>
+      <c r="B171" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C171">
+        <v>7</v>
+      </c>
+      <c r="D171">
+        <v>197.4286</v>
+      </c>
+      <c r="E171">
+        <v>0.00423</v>
+      </c>
+      <c r="F171">
+        <v>0.423</v>
+      </c>
+      <c r="G171">
+        <v>0.002429</v>
+      </c>
+      <c r="H171">
+        <v>0.2429</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" t="s">
+        <v>33</v>
+      </c>
+      <c r="B172" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C172">
+        <v>7</v>
+      </c>
+      <c r="D172">
+        <v>216.7143</v>
+      </c>
+      <c r="E172">
+        <v>0.003854</v>
+      </c>
+      <c r="F172">
+        <v>0.3854</v>
+      </c>
+      <c r="G172">
+        <v>0.002095</v>
+      </c>
+      <c r="H172">
+        <v>0.2095</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" t="s">
+        <v>39</v>
+      </c>
+      <c r="B173" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C173">
+        <v>7</v>
+      </c>
+      <c r="D173">
+        <v>234</v>
+      </c>
+      <c r="E173">
+        <v>0.003569</v>
+      </c>
+      <c r="F173">
+        <v>0.3569</v>
+      </c>
+      <c r="G173">
+        <v>0.00185</v>
+      </c>
+      <c r="H173">
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" t="s">
+        <v>36</v>
+      </c>
+      <c r="B174" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C174">
+        <v>7</v>
+      </c>
+      <c r="D174">
+        <v>283.7143</v>
+      </c>
+      <c r="E174">
+        <v>0.002944</v>
+      </c>
+      <c r="F174">
+        <v>0.2944</v>
+      </c>
+      <c r="G174">
+        <v>0.001341</v>
+      </c>
+      <c r="H174">
+        <v>0.1341</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" t="s">
+        <v>38</v>
+      </c>
+      <c r="B175" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C175">
+        <v>7</v>
+      </c>
+      <c r="D175">
+        <v>390.7143</v>
+      </c>
+      <c r="E175">
+        <v>0.002137</v>
+      </c>
+      <c r="F175">
+        <v>0.2137</v>
+      </c>
+      <c r="G175">
+        <v>0.000764</v>
+      </c>
+      <c r="H175">
+        <v>0.0764</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" t="s">
+        <v>37</v>
+      </c>
+      <c r="B176" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C176">
+        <v>7</v>
+      </c>
+      <c r="D176">
+        <v>474.5714</v>
+      </c>
+      <c r="E176">
+        <v>0.00176</v>
+      </c>
+      <c r="F176">
+        <v>0.176</v>
+      </c>
+      <c r="G176">
+        <v>0.000535</v>
+      </c>
+      <c r="H176">
+        <v>0.0535</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" t="s">
+        <v>32</v>
+      </c>
+      <c r="B177" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C177">
+        <v>7</v>
+      </c>
+      <c r="D177">
+        <v>490.7143</v>
+      </c>
+      <c r="E177">
+        <v>0.001702</v>
+      </c>
+      <c r="F177">
+        <v>0.1702</v>
+      </c>
+      <c r="G177">
+        <v>0.000502</v>
+      </c>
+      <c r="H177">
+        <v>0.0502</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" t="s">
+        <v>35</v>
+      </c>
+      <c r="B178" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C178">
+        <v>7</v>
+      </c>
+      <c r="D178">
+        <v>497.8571</v>
+      </c>
+      <c r="E178">
+        <v>0.001677</v>
+      </c>
+      <c r="F178">
+        <v>0.1677</v>
+      </c>
+      <c r="G178">
+        <v>0.000489</v>
+      </c>
+      <c r="H178">
+        <v>0.0489</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" t="s">
+        <v>41</v>
+      </c>
+      <c r="B179" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C179">
+        <v>7</v>
+      </c>
+      <c r="D179">
+        <v>502.4286</v>
+      </c>
+      <c r="E179">
+        <v>0.001662</v>
+      </c>
+      <c r="F179">
+        <v>0.1662</v>
+      </c>
+      <c r="G179">
+        <v>0.000481</v>
+      </c>
+      <c r="H179">
+        <v>0.0481</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" t="s">
+        <v>42</v>
+      </c>
+      <c r="B180" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C180">
+        <v>7</v>
+      </c>
+      <c r="D180">
+        <v>612.1429000000001</v>
+      </c>
+      <c r="E180">
+        <v>0.001364</v>
+      </c>
+      <c r="F180">
+        <v>0.1364</v>
+      </c>
+      <c r="G180">
+        <v>0.000331</v>
+      </c>
+      <c r="H180">
+        <v>0.0331</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" t="s">
+        <v>44</v>
+      </c>
+      <c r="B181" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C181">
+        <v>7</v>
+      </c>
+      <c r="D181">
+        <v>747.8570999999999</v>
+      </c>
+      <c r="E181">
+        <v>0.001117</v>
+      </c>
+      <c r="F181">
+        <v>0.1117</v>
+      </c>
+      <c r="G181">
+        <v>0.000225</v>
+      </c>
+      <c r="H181">
+        <v>0.0225</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" t="s">
+        <v>45</v>
+      </c>
+      <c r="B182" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C182">
+        <v>7</v>
+      </c>
+      <c r="D182">
+        <v>783.5714</v>
+      </c>
+      <c r="E182">
+        <v>0.001066</v>
+      </c>
+      <c r="F182">
+        <v>0.1066</v>
+      </c>
+      <c r="G182">
+        <v>0.000206</v>
+      </c>
+      <c r="H182">
+        <v>0.0206</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" t="s">
+        <v>49</v>
+      </c>
+      <c r="B183" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C183">
+        <v>7</v>
+      </c>
+      <c r="D183">
+        <v>819.2857</v>
+      </c>
+      <c r="E183">
+        <v>0.001019</v>
+      </c>
+      <c r="F183">
+        <v>0.1019</v>
+      </c>
+      <c r="G183">
+        <v>0.000189</v>
+      </c>
+      <c r="H183">
+        <v>0.0189</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" t="s">
+        <v>43</v>
+      </c>
+      <c r="B184" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C184">
+        <v>7</v>
+      </c>
+      <c r="D184">
+        <v>926.4286</v>
+      </c>
+      <c r="E184">
+        <v>0.000901</v>
+      </c>
+      <c r="F184">
+        <v>0.0901</v>
+      </c>
+      <c r="G184">
+        <v>0.000148</v>
+      </c>
+      <c r="H184">
+        <v>0.0148</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" t="s">
+        <v>52</v>
+      </c>
+      <c r="B185" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C185">
+        <v>7</v>
+      </c>
+      <c r="D185">
+        <v>1069.2857</v>
+      </c>
+      <c r="E185">
+        <v>0.000781</v>
+      </c>
+      <c r="F185">
+        <v>0.0781</v>
+      </c>
+      <c r="G185">
+        <v>0.000112</v>
+      </c>
+      <c r="H185">
+        <v>0.0112</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" t="s">
+        <v>47</v>
+      </c>
+      <c r="B186" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C186">
+        <v>7</v>
+      </c>
+      <c r="D186">
+        <v>1069.2857</v>
+      </c>
+      <c r="E186">
+        <v>0.000781</v>
+      </c>
+      <c r="F186">
+        <v>0.0781</v>
+      </c>
+      <c r="G186">
+        <v>0.000112</v>
+      </c>
+      <c r="H186">
+        <v>0.0112</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" t="s">
+        <v>46</v>
+      </c>
+      <c r="B187" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C187">
+        <v>7</v>
+      </c>
+      <c r="D187">
+        <v>1176.4286</v>
+      </c>
+      <c r="E187">
+        <v>0.00071</v>
+      </c>
+      <c r="F187">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="G187">
+        <v>9.3E-05</v>
+      </c>
+      <c r="H187">
+        <v>0.009299999999999999</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" t="s">
+        <v>48</v>
+      </c>
+      <c r="B188" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C188">
+        <v>7</v>
+      </c>
+      <c r="D188">
+        <v>1197.8571</v>
+      </c>
+      <c r="E188">
+        <v>0.000697</v>
+      </c>
+      <c r="F188">
+        <v>0.0697</v>
+      </c>
+      <c r="G188">
+        <v>9.000000000000001E-05</v>
+      </c>
+      <c r="H188">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" t="s">
+        <v>50</v>
+      </c>
+      <c r="B189" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C189">
+        <v>7</v>
+      </c>
+      <c r="D189">
+        <v>1197.8571</v>
+      </c>
+      <c r="E189">
+        <v>0.000697</v>
+      </c>
+      <c r="F189">
+        <v>0.0697</v>
+      </c>
+      <c r="G189">
+        <v>9.000000000000001E-05</v>
+      </c>
+      <c r="H189">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" t="s">
+        <v>51</v>
+      </c>
+      <c r="B190" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C190">
+        <v>7</v>
+      </c>
+      <c r="D190">
+        <v>1197.8571</v>
+      </c>
+      <c r="E190">
+        <v>0.000697</v>
+      </c>
+      <c r="F190">
+        <v>0.0697</v>
+      </c>
+      <c r="G190">
+        <v>9.000000000000001E-05</v>
+      </c>
+      <c r="H190">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" t="s">
+        <v>53</v>
+      </c>
+      <c r="B191" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C191">
+        <v>7</v>
+      </c>
+      <c r="D191">
+        <v>1497.8571</v>
+      </c>
+      <c r="E191">
+        <v>0.000558</v>
+      </c>
+      <c r="F191">
+        <v>0.0558</v>
+      </c>
+      <c r="G191">
+        <v>5.8E-05</v>
+      </c>
+      <c r="H191">
+        <v>0.0058</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" t="s">
+        <v>55</v>
+      </c>
+      <c r="B192" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C192">
+        <v>7</v>
+      </c>
+      <c r="D192">
+        <v>2033.5714</v>
+      </c>
+      <c r="E192">
+        <v>0.000411</v>
+      </c>
+      <c r="F192">
+        <v>0.0411</v>
+      </c>
+      <c r="G192">
+        <v>3.1E-05</v>
+      </c>
+      <c r="H192">
+        <v>0.0031</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" t="s">
+        <v>54</v>
+      </c>
+      <c r="B193" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C193">
+        <v>7</v>
+      </c>
+      <c r="D193">
+        <v>2355</v>
+      </c>
+      <c r="E193">
+        <v>0.000355</v>
+      </c>
+      <c r="F193">
+        <v>0.0355</v>
+      </c>
+      <c r="G193">
+        <v>2.3E-05</v>
+      </c>
+      <c r="H193">
+        <v>0.0023</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -5564,6 +5564,1254 @@
         <v>0.0023</v>
       </c>
     </row>
+    <row r="194" spans="1:8">
+      <c r="A194" t="s">
+        <v>9</v>
+      </c>
+      <c r="B194" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C194">
+        <v>6</v>
+      </c>
+      <c r="D194">
+        <v>4.82</v>
+      </c>
+      <c r="E194">
+        <v>0.174802</v>
+      </c>
+      <c r="F194">
+        <v>17.4802</v>
+      </c>
+      <c r="G194">
+        <v>0.188004</v>
+      </c>
+      <c r="H194">
+        <v>18.8004</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" t="s">
+        <v>8</v>
+      </c>
+      <c r="B195" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C195">
+        <v>6</v>
+      </c>
+      <c r="D195">
+        <v>6.8783</v>
+      </c>
+      <c r="E195">
+        <v>0.122493</v>
+      </c>
+      <c r="F195">
+        <v>12.2493</v>
+      </c>
+      <c r="G195">
+        <v>0.130854</v>
+      </c>
+      <c r="H195">
+        <v>13.0854</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" t="s">
+        <v>10</v>
+      </c>
+      <c r="B196" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C196">
+        <v>6</v>
+      </c>
+      <c r="D196">
+        <v>7.045</v>
+      </c>
+      <c r="E196">
+        <v>0.119595</v>
+      </c>
+      <c r="F196">
+        <v>11.9595</v>
+      </c>
+      <c r="G196">
+        <v>0.127688</v>
+      </c>
+      <c r="H196">
+        <v>12.7688</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" t="s">
+        <v>13</v>
+      </c>
+      <c r="B197" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C197">
+        <v>6</v>
+      </c>
+      <c r="D197">
+        <v>9.136699999999999</v>
+      </c>
+      <c r="E197">
+        <v>0.09221600000000001</v>
+      </c>
+      <c r="F197">
+        <v>9.2216</v>
+      </c>
+      <c r="G197">
+        <v>0.09778100000000001</v>
+      </c>
+      <c r="H197">
+        <v>9.7781</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" t="s">
+        <v>11</v>
+      </c>
+      <c r="B198" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C198">
+        <v>6</v>
+      </c>
+      <c r="D198">
+        <v>10.6333</v>
+      </c>
+      <c r="E198">
+        <v>0.079236</v>
+      </c>
+      <c r="F198">
+        <v>7.9236</v>
+      </c>
+      <c r="G198">
+        <v>0.083605</v>
+      </c>
+      <c r="H198">
+        <v>8.3605</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" t="s">
+        <v>12</v>
+      </c>
+      <c r="B199" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199">
+        <v>12.2</v>
+      </c>
+      <c r="E199">
+        <v>0.069061</v>
+      </c>
+      <c r="F199">
+        <v>6.9061</v>
+      </c>
+      <c r="G199">
+        <v>0.072494</v>
+      </c>
+      <c r="H199">
+        <v>7.2494</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" t="s">
+        <v>14</v>
+      </c>
+      <c r="B200" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C200">
+        <v>6</v>
+      </c>
+      <c r="D200">
+        <v>14.8667</v>
+      </c>
+      <c r="E200">
+        <v>0.056674</v>
+      </c>
+      <c r="F200">
+        <v>5.6674</v>
+      </c>
+      <c r="G200">
+        <v>0.058971</v>
+      </c>
+      <c r="H200">
+        <v>5.8971</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C201">
+        <v>6</v>
+      </c>
+      <c r="D201">
+        <v>21</v>
+      </c>
+      <c r="E201">
+        <v>0.040121</v>
+      </c>
+      <c r="F201">
+        <v>4.0121</v>
+      </c>
+      <c r="G201">
+        <v>0.040914</v>
+      </c>
+      <c r="H201">
+        <v>4.0914</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" t="s">
+        <v>16</v>
+      </c>
+      <c r="B202" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C202">
+        <v>6</v>
+      </c>
+      <c r="D202">
+        <v>31.5</v>
+      </c>
+      <c r="E202">
+        <v>0.026748</v>
+      </c>
+      <c r="F202">
+        <v>2.6748</v>
+      </c>
+      <c r="G202">
+        <v>0.026352</v>
+      </c>
+      <c r="H202">
+        <v>2.6352</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" t="s">
+        <v>19</v>
+      </c>
+      <c r="B203" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C203">
+        <v>6</v>
+      </c>
+      <c r="D203">
+        <v>40.6667</v>
+      </c>
+      <c r="E203">
+        <v>0.020718</v>
+      </c>
+      <c r="F203">
+        <v>2.0718</v>
+      </c>
+      <c r="G203">
+        <v>0.019809</v>
+      </c>
+      <c r="H203">
+        <v>1.9809</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" t="s">
+        <v>21</v>
+      </c>
+      <c r="B204" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C204">
+        <v>6</v>
+      </c>
+      <c r="D204">
+        <v>42</v>
+      </c>
+      <c r="E204">
+        <v>0.020061</v>
+      </c>
+      <c r="F204">
+        <v>2.0061</v>
+      </c>
+      <c r="G204">
+        <v>0.019097</v>
+      </c>
+      <c r="H204">
+        <v>1.9097</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" t="s">
+        <v>17</v>
+      </c>
+      <c r="B205" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C205">
+        <v>6</v>
+      </c>
+      <c r="D205">
+        <v>42.1667</v>
+      </c>
+      <c r="E205">
+        <v>0.019981</v>
+      </c>
+      <c r="F205">
+        <v>1.9981</v>
+      </c>
+      <c r="G205">
+        <v>0.019011</v>
+      </c>
+      <c r="H205">
+        <v>1.9011</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" t="s">
+        <v>22</v>
+      </c>
+      <c r="B206" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C206">
+        <v>6</v>
+      </c>
+      <c r="D206">
+        <v>47.1667</v>
+      </c>
+      <c r="E206">
+        <v>0.017863</v>
+      </c>
+      <c r="F206">
+        <v>1.7863</v>
+      </c>
+      <c r="G206">
+        <v>0.016721</v>
+      </c>
+      <c r="H206">
+        <v>1.6721</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" t="s">
+        <v>18</v>
+      </c>
+      <c r="B207" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C207">
+        <v>6</v>
+      </c>
+      <c r="D207">
+        <v>48</v>
+      </c>
+      <c r="E207">
+        <v>0.017553</v>
+      </c>
+      <c r="F207">
+        <v>1.7553</v>
+      </c>
+      <c r="G207">
+        <v>0.016386</v>
+      </c>
+      <c r="H207">
+        <v>1.6386</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" t="s">
+        <v>20</v>
+      </c>
+      <c r="B208" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C208">
+        <v>6</v>
+      </c>
+      <c r="D208">
+        <v>53</v>
+      </c>
+      <c r="E208">
+        <v>0.015897</v>
+      </c>
+      <c r="F208">
+        <v>1.5897</v>
+      </c>
+      <c r="G208">
+        <v>0.014601</v>
+      </c>
+      <c r="H208">
+        <v>1.4601</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" t="s">
+        <v>24</v>
+      </c>
+      <c r="B209" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C209">
+        <v>6</v>
+      </c>
+      <c r="D209">
+        <v>78</v>
+      </c>
+      <c r="E209">
+        <v>0.010802</v>
+      </c>
+      <c r="F209">
+        <v>1.0802</v>
+      </c>
+      <c r="G209">
+        <v>0.009154000000000001</v>
+      </c>
+      <c r="H209">
+        <v>0.9154</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" t="s">
+        <v>23</v>
+      </c>
+      <c r="B210" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C210">
+        <v>6</v>
+      </c>
+      <c r="D210">
+        <v>88.83329999999999</v>
+      </c>
+      <c r="E210">
+        <v>0.009485</v>
+      </c>
+      <c r="F210">
+        <v>0.9485</v>
+      </c>
+      <c r="G210">
+        <v>0.007766</v>
+      </c>
+      <c r="H210">
+        <v>0.7766</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" t="s">
+        <v>29</v>
+      </c>
+      <c r="B211" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C211">
+        <v>6</v>
+      </c>
+      <c r="D211">
+        <v>110</v>
+      </c>
+      <c r="E211">
+        <v>0.00766</v>
+      </c>
+      <c r="F211">
+        <v>0.766</v>
+      </c>
+      <c r="G211">
+        <v>0.005869</v>
+      </c>
+      <c r="H211">
+        <v>0.5869</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" t="s">
+        <v>26</v>
+      </c>
+      <c r="B212" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C212">
+        <v>6</v>
+      </c>
+      <c r="D212">
+        <v>110.8333</v>
+      </c>
+      <c r="E212">
+        <v>0.007602</v>
+      </c>
+      <c r="F212">
+        <v>0.7602</v>
+      </c>
+      <c r="G212">
+        <v>0.00581</v>
+      </c>
+      <c r="H212">
+        <v>0.581</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" t="s">
+        <v>28</v>
+      </c>
+      <c r="B213" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C213">
+        <v>6</v>
+      </c>
+      <c r="D213">
+        <v>115.1667</v>
+      </c>
+      <c r="E213">
+        <v>0.007316</v>
+      </c>
+      <c r="F213">
+        <v>0.7316</v>
+      </c>
+      <c r="G213">
+        <v>0.005517</v>
+      </c>
+      <c r="H213">
+        <v>0.5517</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" t="s">
+        <v>40</v>
+      </c>
+      <c r="B214" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C214">
+        <v>6</v>
+      </c>
+      <c r="D214">
+        <v>128.5</v>
+      </c>
+      <c r="E214">
+        <v>0.006557</v>
+      </c>
+      <c r="F214">
+        <v>0.6556999999999999</v>
+      </c>
+      <c r="G214">
+        <v>0.004747</v>
+      </c>
+      <c r="H214">
+        <v>0.4747</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" t="s">
+        <v>30</v>
+      </c>
+      <c r="B215" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C215">
+        <v>6</v>
+      </c>
+      <c r="D215">
+        <v>144</v>
+      </c>
+      <c r="E215">
+        <v>0.005851</v>
+      </c>
+      <c r="F215">
+        <v>0.5851</v>
+      </c>
+      <c r="G215">
+        <v>0.004044</v>
+      </c>
+      <c r="H215">
+        <v>0.4044</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" t="s">
+        <v>34</v>
+      </c>
+      <c r="B216" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C216">
+        <v>6</v>
+      </c>
+      <c r="D216">
+        <v>144.8333</v>
+      </c>
+      <c r="E216">
+        <v>0.005817</v>
+      </c>
+      <c r="F216">
+        <v>0.5817</v>
+      </c>
+      <c r="G216">
+        <v>0.00401</v>
+      </c>
+      <c r="H216">
+        <v>0.401</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" t="s">
+        <v>31</v>
+      </c>
+      <c r="B217" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C217">
+        <v>6</v>
+      </c>
+      <c r="D217">
+        <v>148.1667</v>
+      </c>
+      <c r="E217">
+        <v>0.005686</v>
+      </c>
+      <c r="F217">
+        <v>0.5686</v>
+      </c>
+      <c r="G217">
+        <v>0.003882</v>
+      </c>
+      <c r="H217">
+        <v>0.3882</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" t="s">
+        <v>27</v>
+      </c>
+      <c r="B218" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C218">
+        <v>6</v>
+      </c>
+      <c r="D218">
+        <v>148.3333</v>
+      </c>
+      <c r="E218">
+        <v>0.00568</v>
+      </c>
+      <c r="F218">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="G218">
+        <v>0.003875</v>
+      </c>
+      <c r="H218">
+        <v>0.3875</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" t="s">
+        <v>25</v>
+      </c>
+      <c r="B219" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C219">
+        <v>6</v>
+      </c>
+      <c r="D219">
+        <v>152.3333</v>
+      </c>
+      <c r="E219">
+        <v>0.005531</v>
+      </c>
+      <c r="F219">
+        <v>0.5531</v>
+      </c>
+      <c r="G219">
+        <v>0.003729</v>
+      </c>
+      <c r="H219">
+        <v>0.3729</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" t="s">
+        <v>33</v>
+      </c>
+      <c r="B220" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C220">
+        <v>6</v>
+      </c>
+      <c r="D220">
+        <v>234.1667</v>
+      </c>
+      <c r="E220">
+        <v>0.003598</v>
+      </c>
+      <c r="F220">
+        <v>0.3598</v>
+      </c>
+      <c r="G220">
+        <v>0.001933</v>
+      </c>
+      <c r="H220">
+        <v>0.1933</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" t="s">
+        <v>39</v>
+      </c>
+      <c r="B221" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C221">
+        <v>6</v>
+      </c>
+      <c r="D221">
+        <v>256.3333</v>
+      </c>
+      <c r="E221">
+        <v>0.003287</v>
+      </c>
+      <c r="F221">
+        <v>0.3287</v>
+      </c>
+      <c r="G221">
+        <v>0.001668</v>
+      </c>
+      <c r="H221">
+        <v>0.1668</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" t="s">
+        <v>36</v>
+      </c>
+      <c r="B222" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C222">
+        <v>6</v>
+      </c>
+      <c r="D222">
+        <v>302.5</v>
+      </c>
+      <c r="E222">
+        <v>0.002785</v>
+      </c>
+      <c r="F222">
+        <v>0.2785</v>
+      </c>
+      <c r="G222">
+        <v>0.001264</v>
+      </c>
+      <c r="H222">
+        <v>0.1264</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" t="s">
+        <v>41</v>
+      </c>
+      <c r="B223" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C223">
+        <v>6</v>
+      </c>
+      <c r="D223">
+        <v>441.3333</v>
+      </c>
+      <c r="E223">
+        <v>0.001909</v>
+      </c>
+      <c r="F223">
+        <v>0.1909</v>
+      </c>
+      <c r="G223">
+        <v>0.000648</v>
+      </c>
+      <c r="H223">
+        <v>0.0648</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" t="s">
+        <v>38</v>
+      </c>
+      <c r="B224" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C224">
+        <v>6</v>
+      </c>
+      <c r="D224">
+        <v>473</v>
+      </c>
+      <c r="E224">
+        <v>0.001781</v>
+      </c>
+      <c r="F224">
+        <v>0.1781</v>
+      </c>
+      <c r="G224">
+        <v>0.000571</v>
+      </c>
+      <c r="H224">
+        <v>0.0571</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" t="s">
+        <v>32</v>
+      </c>
+      <c r="B225" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C225">
+        <v>6</v>
+      </c>
+      <c r="D225">
+        <v>522.3333</v>
+      </c>
+      <c r="E225">
+        <v>0.001613</v>
+      </c>
+      <c r="F225">
+        <v>0.1613</v>
+      </c>
+      <c r="G225">
+        <v>0.000475</v>
+      </c>
+      <c r="H225">
+        <v>0.0475</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" t="s">
+        <v>37</v>
+      </c>
+      <c r="B226" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C226">
+        <v>6</v>
+      </c>
+      <c r="D226">
+        <v>530.6667</v>
+      </c>
+      <c r="E226">
+        <v>0.001588</v>
+      </c>
+      <c r="F226">
+        <v>0.1588</v>
+      </c>
+      <c r="G226">
+        <v>0.000461</v>
+      </c>
+      <c r="H226">
+        <v>0.0461</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" t="s">
+        <v>35</v>
+      </c>
+      <c r="B227" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C227">
+        <v>6</v>
+      </c>
+      <c r="D227">
+        <v>572.3333</v>
+      </c>
+      <c r="E227">
+        <v>0.001472</v>
+      </c>
+      <c r="F227">
+        <v>0.1472</v>
+      </c>
+      <c r="G227">
+        <v>0.0004</v>
+      </c>
+      <c r="H227">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" t="s">
+        <v>44</v>
+      </c>
+      <c r="B228" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C228">
+        <v>6</v>
+      </c>
+      <c r="D228">
+        <v>607.5</v>
+      </c>
+      <c r="E228">
+        <v>0.001387</v>
+      </c>
+      <c r="F228">
+        <v>0.1387</v>
+      </c>
+      <c r="G228">
+        <v>0.000358</v>
+      </c>
+      <c r="H228">
+        <v>0.0358</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" t="s">
+        <v>42</v>
+      </c>
+      <c r="B229" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C229">
+        <v>6</v>
+      </c>
+      <c r="D229">
+        <v>630.6667</v>
+      </c>
+      <c r="E229">
+        <v>0.001336</v>
+      </c>
+      <c r="F229">
+        <v>0.1336</v>
+      </c>
+      <c r="G229">
+        <v>0.000333</v>
+      </c>
+      <c r="H229">
+        <v>0.0333</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" t="s">
+        <v>45</v>
+      </c>
+      <c r="B230" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C230">
+        <v>6</v>
+      </c>
+      <c r="D230">
+        <v>789</v>
+      </c>
+      <c r="E230">
+        <v>0.001068</v>
+      </c>
+      <c r="F230">
+        <v>0.1068</v>
+      </c>
+      <c r="G230">
+        <v>0.000217</v>
+      </c>
+      <c r="H230">
+        <v>0.0217</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231" t="s">
+        <v>49</v>
+      </c>
+      <c r="B231" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C231">
+        <v>6</v>
+      </c>
+      <c r="D231">
+        <v>872.3333</v>
+      </c>
+      <c r="E231">
+        <v>0.000966</v>
+      </c>
+      <c r="F231">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="G231">
+        <v>0.000178</v>
+      </c>
+      <c r="H231">
+        <v>0.0178</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232" t="s">
+        <v>43</v>
+      </c>
+      <c r="B232" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C232">
+        <v>6</v>
+      </c>
+      <c r="D232">
+        <v>955.6667</v>
+      </c>
+      <c r="E232">
+        <v>0.000882</v>
+      </c>
+      <c r="F232">
+        <v>0.0882</v>
+      </c>
+      <c r="G232">
+        <v>0.000149</v>
+      </c>
+      <c r="H232">
+        <v>0.0149</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233" t="s">
+        <v>52</v>
+      </c>
+      <c r="B233" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C233">
+        <v>6</v>
+      </c>
+      <c r="D233">
+        <v>996.6</v>
+      </c>
+      <c r="E233">
+        <v>0.000845</v>
+      </c>
+      <c r="F233">
+        <v>0.08450000000000001</v>
+      </c>
+      <c r="G233">
+        <v>0.000138</v>
+      </c>
+      <c r="H233">
+        <v>0.0138</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" t="s">
+        <v>46</v>
+      </c>
+      <c r="B234" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C234">
+        <v>6</v>
+      </c>
+      <c r="D234">
+        <v>1205.6667</v>
+      </c>
+      <c r="E234">
+        <v>0.000699</v>
+      </c>
+      <c r="F234">
+        <v>0.0699</v>
+      </c>
+      <c r="G234">
+        <v>9.500000000000001E-05</v>
+      </c>
+      <c r="H234">
+        <v>0.0095</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" t="s">
+        <v>50</v>
+      </c>
+      <c r="B235" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C235">
+        <v>6</v>
+      </c>
+      <c r="D235">
+        <v>1247.3333</v>
+      </c>
+      <c r="E235">
+        <v>0.000675</v>
+      </c>
+      <c r="F235">
+        <v>0.0675</v>
+      </c>
+      <c r="G235">
+        <v>8.899999999999999E-05</v>
+      </c>
+      <c r="H235">
+        <v>0.0089</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" t="s">
+        <v>48</v>
+      </c>
+      <c r="B236" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C236">
+        <v>6</v>
+      </c>
+      <c r="D236">
+        <v>1296.6</v>
+      </c>
+      <c r="E236">
+        <v>0.00065</v>
+      </c>
+      <c r="F236">
+        <v>0.065</v>
+      </c>
+      <c r="G236">
+        <v>8.2E-05</v>
+      </c>
+      <c r="H236">
+        <v>0.008200000000000001</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" t="s">
+        <v>51</v>
+      </c>
+      <c r="B237" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C237">
+        <v>6</v>
+      </c>
+      <c r="D237">
+        <v>1296.6</v>
+      </c>
+      <c r="E237">
+        <v>0.00065</v>
+      </c>
+      <c r="F237">
+        <v>0.065</v>
+      </c>
+      <c r="G237">
+        <v>8.2E-05</v>
+      </c>
+      <c r="H237">
+        <v>0.008200000000000001</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238" t="s">
+        <v>47</v>
+      </c>
+      <c r="B238" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C238">
+        <v>6</v>
+      </c>
+      <c r="D238">
+        <v>1372.3333</v>
+      </c>
+      <c r="E238">
+        <v>0.000614</v>
+      </c>
+      <c r="F238">
+        <v>0.0614</v>
+      </c>
+      <c r="G238">
+        <v>7.3E-05</v>
+      </c>
+      <c r="H238">
+        <v>0.0073</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" t="s">
+        <v>53</v>
+      </c>
+      <c r="B239" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C239">
+        <v>6</v>
+      </c>
+      <c r="D239">
+        <v>1696.6</v>
+      </c>
+      <c r="E239">
+        <v>0.000497</v>
+      </c>
+      <c r="F239">
+        <v>0.0497</v>
+      </c>
+      <c r="G239">
+        <v>4.8E-05</v>
+      </c>
+      <c r="H239">
+        <v>0.0048</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" t="s">
+        <v>55</v>
+      </c>
+      <c r="B240" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C240">
+        <v>6</v>
+      </c>
+      <c r="D240">
+        <v>2296.6</v>
+      </c>
+      <c r="E240">
+        <v>0.000367</v>
+      </c>
+      <c r="F240">
+        <v>0.0367</v>
+      </c>
+      <c r="G240">
+        <v>2.6E-05</v>
+      </c>
+      <c r="H240">
+        <v>0.0026</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" t="s">
+        <v>54</v>
+      </c>
+      <c r="B241" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C241">
+        <v>6</v>
+      </c>
+      <c r="D241">
+        <v>2596.6</v>
+      </c>
+      <c r="E241">
+        <v>0.000324</v>
+      </c>
+      <c r="F241">
+        <v>0.0324</v>
+      </c>
+      <c r="G241">
+        <v>2.1E-05</v>
+      </c>
+      <c r="H241">
+        <v>0.0021</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -6812,6 +6812,1176 @@
         <v>0.0021</v>
       </c>
     </row>
+    <row r="242" spans="1:8">
+      <c r="A242" t="s">
+        <v>9</v>
+      </c>
+      <c r="B242" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C242">
+        <v>7</v>
+      </c>
+      <c r="D242">
+        <v>4.8743</v>
+      </c>
+      <c r="E242">
+        <v>0.173239</v>
+      </c>
+      <c r="F242">
+        <v>17.3239</v>
+      </c>
+      <c r="G242">
+        <v>0.185967</v>
+      </c>
+      <c r="H242">
+        <v>18.5967</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" t="s">
+        <v>8</v>
+      </c>
+      <c r="B243" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C243">
+        <v>7</v>
+      </c>
+      <c r="D243">
+        <v>6.34</v>
+      </c>
+      <c r="E243">
+        <v>0.133189</v>
+      </c>
+      <c r="F243">
+        <v>13.3189</v>
+      </c>
+      <c r="G243">
+        <v>0.142253</v>
+      </c>
+      <c r="H243">
+        <v>14.2253</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" t="s">
+        <v>10</v>
+      </c>
+      <c r="B244" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C244">
+        <v>7</v>
+      </c>
+      <c r="D244">
+        <v>7.11</v>
+      </c>
+      <c r="E244">
+        <v>0.118765</v>
+      </c>
+      <c r="F244">
+        <v>11.8765</v>
+      </c>
+      <c r="G244">
+        <v>0.12651</v>
+      </c>
+      <c r="H244">
+        <v>12.651</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" t="s">
+        <v>13</v>
+      </c>
+      <c r="B245" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C245">
+        <v>7</v>
+      </c>
+      <c r="D245">
+        <v>8.707100000000001</v>
+      </c>
+      <c r="E245">
+        <v>0.09698</v>
+      </c>
+      <c r="F245">
+        <v>9.698</v>
+      </c>
+      <c r="G245">
+        <v>0.102737</v>
+      </c>
+      <c r="H245">
+        <v>10.2737</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" t="s">
+        <v>11</v>
+      </c>
+      <c r="B246" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C246">
+        <v>7</v>
+      </c>
+      <c r="D246">
+        <v>11.6714</v>
+      </c>
+      <c r="E246">
+        <v>0.072349</v>
+      </c>
+      <c r="F246">
+        <v>7.2349</v>
+      </c>
+      <c r="G246">
+        <v>0.075864</v>
+      </c>
+      <c r="H246">
+        <v>7.5864</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" t="s">
+        <v>12</v>
+      </c>
+      <c r="B247" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C247">
+        <v>7</v>
+      </c>
+      <c r="D247">
+        <v>13.1714</v>
+      </c>
+      <c r="E247">
+        <v>0.06411</v>
+      </c>
+      <c r="F247">
+        <v>6.411</v>
+      </c>
+      <c r="G247">
+        <v>0.06687700000000001</v>
+      </c>
+      <c r="H247">
+        <v>6.6877</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" t="s">
+        <v>14</v>
+      </c>
+      <c r="B248" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C248">
+        <v>7</v>
+      </c>
+      <c r="D248">
+        <v>14.5286</v>
+      </c>
+      <c r="E248">
+        <v>0.058121</v>
+      </c>
+      <c r="F248">
+        <v>5.8121</v>
+      </c>
+      <c r="G248">
+        <v>0.060347</v>
+      </c>
+      <c r="H248">
+        <v>6.0347</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" t="s">
+        <v>15</v>
+      </c>
+      <c r="B249" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C249">
+        <v>7</v>
+      </c>
+      <c r="D249">
+        <v>17.5286</v>
+      </c>
+      <c r="E249">
+        <v>0.048174</v>
+      </c>
+      <c r="F249">
+        <v>4.8174</v>
+      </c>
+      <c r="G249">
+        <v>0.049504</v>
+      </c>
+      <c r="H249">
+        <v>4.9504</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" t="s">
+        <v>21</v>
+      </c>
+      <c r="B250" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C250">
+        <v>7</v>
+      </c>
+      <c r="D250">
+        <v>31.4286</v>
+      </c>
+      <c r="E250">
+        <v>0.026868</v>
+      </c>
+      <c r="F250">
+        <v>2.6868</v>
+      </c>
+      <c r="G250">
+        <v>0.02632</v>
+      </c>
+      <c r="H250">
+        <v>2.632</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" t="s">
+        <v>19</v>
+      </c>
+      <c r="B251" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C251">
+        <v>7</v>
+      </c>
+      <c r="D251">
+        <v>32.8571</v>
+      </c>
+      <c r="E251">
+        <v>0.0257</v>
+      </c>
+      <c r="F251">
+        <v>2.57</v>
+      </c>
+      <c r="G251">
+        <v>0.025053</v>
+      </c>
+      <c r="H251">
+        <v>2.5053</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" t="s">
+        <v>16</v>
+      </c>
+      <c r="B252" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C252">
+        <v>7</v>
+      </c>
+      <c r="D252">
+        <v>36.5714</v>
+      </c>
+      <c r="E252">
+        <v>0.02309</v>
+      </c>
+      <c r="F252">
+        <v>2.309</v>
+      </c>
+      <c r="G252">
+        <v>0.022224</v>
+      </c>
+      <c r="H252">
+        <v>2.2224</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" t="s">
+        <v>20</v>
+      </c>
+      <c r="B253" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C253">
+        <v>7</v>
+      </c>
+      <c r="D253">
+        <v>42.8571</v>
+      </c>
+      <c r="E253">
+        <v>0.019703</v>
+      </c>
+      <c r="F253">
+        <v>1.9703</v>
+      </c>
+      <c r="G253">
+        <v>0.018561</v>
+      </c>
+      <c r="H253">
+        <v>1.8561</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" t="s">
+        <v>17</v>
+      </c>
+      <c r="B254" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C254">
+        <v>7</v>
+      </c>
+      <c r="D254">
+        <v>47.7143</v>
+      </c>
+      <c r="E254">
+        <v>0.017697</v>
+      </c>
+      <c r="F254">
+        <v>1.7697</v>
+      </c>
+      <c r="G254">
+        <v>0.016397</v>
+      </c>
+      <c r="H254">
+        <v>1.6397</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" t="s">
+        <v>18</v>
+      </c>
+      <c r="B255" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C255">
+        <v>7</v>
+      </c>
+      <c r="D255">
+        <v>49.8571</v>
+      </c>
+      <c r="E255">
+        <v>0.016937</v>
+      </c>
+      <c r="F255">
+        <v>1.6937</v>
+      </c>
+      <c r="G255">
+        <v>0.015579</v>
+      </c>
+      <c r="H255">
+        <v>1.5579</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" t="s">
+        <v>22</v>
+      </c>
+      <c r="B256" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C256">
+        <v>7</v>
+      </c>
+      <c r="D256">
+        <v>51.1429</v>
+      </c>
+      <c r="E256">
+        <v>0.016511</v>
+      </c>
+      <c r="F256">
+        <v>1.6511</v>
+      </c>
+      <c r="G256">
+        <v>0.015121</v>
+      </c>
+      <c r="H256">
+        <v>1.5121</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" t="s">
+        <v>24</v>
+      </c>
+      <c r="B257" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C257">
+        <v>7</v>
+      </c>
+      <c r="D257">
+        <v>81.4286</v>
+      </c>
+      <c r="E257">
+        <v>0.01037</v>
+      </c>
+      <c r="F257">
+        <v>1.037</v>
+      </c>
+      <c r="G257">
+        <v>0.008577</v>
+      </c>
+      <c r="H257">
+        <v>0.8577</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258" t="s">
+        <v>26</v>
+      </c>
+      <c r="B258" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C258">
+        <v>7</v>
+      </c>
+      <c r="D258">
+        <v>123</v>
+      </c>
+      <c r="E258">
+        <v>0.006865</v>
+      </c>
+      <c r="F258">
+        <v>0.6865</v>
+      </c>
+      <c r="G258">
+        <v>0.004959</v>
+      </c>
+      <c r="H258">
+        <v>0.4959</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="A259" t="s">
+        <v>28</v>
+      </c>
+      <c r="B259" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C259">
+        <v>7</v>
+      </c>
+      <c r="D259">
+        <v>125.8571</v>
+      </c>
+      <c r="E259">
+        <v>0.006709</v>
+      </c>
+      <c r="F259">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="G259">
+        <v>0.004803</v>
+      </c>
+      <c r="H259">
+        <v>0.4803</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" t="s">
+        <v>34</v>
+      </c>
+      <c r="B260" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C260">
+        <v>7</v>
+      </c>
+      <c r="D260">
+        <v>133.7143</v>
+      </c>
+      <c r="E260">
+        <v>0.006315</v>
+      </c>
+      <c r="F260">
+        <v>0.6315</v>
+      </c>
+      <c r="G260">
+        <v>0.00441</v>
+      </c>
+      <c r="H260">
+        <v>0.441</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" t="s">
+        <v>30</v>
+      </c>
+      <c r="B261" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C261">
+        <v>7</v>
+      </c>
+      <c r="D261">
+        <v>139.2857</v>
+      </c>
+      <c r="E261">
+        <v>0.006062</v>
+      </c>
+      <c r="F261">
+        <v>0.6062</v>
+      </c>
+      <c r="G261">
+        <v>0.004161</v>
+      </c>
+      <c r="H261">
+        <v>0.4161</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262" t="s">
+        <v>31</v>
+      </c>
+      <c r="B262" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C262">
+        <v>7</v>
+      </c>
+      <c r="D262">
+        <v>140</v>
+      </c>
+      <c r="E262">
+        <v>0.006032</v>
+      </c>
+      <c r="F262">
+        <v>0.6032</v>
+      </c>
+      <c r="G262">
+        <v>0.00413</v>
+      </c>
+      <c r="H262">
+        <v>0.413</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" t="s">
+        <v>23</v>
+      </c>
+      <c r="B263" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C263">
+        <v>7</v>
+      </c>
+      <c r="D263">
+        <v>162.8571</v>
+      </c>
+      <c r="E263">
+        <v>0.005185</v>
+      </c>
+      <c r="F263">
+        <v>0.5185</v>
+      </c>
+      <c r="G263">
+        <v>0.003311</v>
+      </c>
+      <c r="H263">
+        <v>0.3311</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264" t="s">
+        <v>29</v>
+      </c>
+      <c r="B264" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C264">
+        <v>7</v>
+      </c>
+      <c r="D264">
+        <v>171.8571</v>
+      </c>
+      <c r="E264">
+        <v>0.004913</v>
+      </c>
+      <c r="F264">
+        <v>0.4913</v>
+      </c>
+      <c r="G264">
+        <v>0.003054</v>
+      </c>
+      <c r="H264">
+        <v>0.3054</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265" t="s">
+        <v>40</v>
+      </c>
+      <c r="B265" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C265">
+        <v>7</v>
+      </c>
+      <c r="D265">
+        <v>174.4286</v>
+      </c>
+      <c r="E265">
+        <v>0.004841</v>
+      </c>
+      <c r="F265">
+        <v>0.4841</v>
+      </c>
+      <c r="G265">
+        <v>0.002986</v>
+      </c>
+      <c r="H265">
+        <v>0.2986</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" t="s">
+        <v>36</v>
+      </c>
+      <c r="B266" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C266">
+        <v>7</v>
+      </c>
+      <c r="D266">
+        <v>261.1429</v>
+      </c>
+      <c r="E266">
+        <v>0.003234</v>
+      </c>
+      <c r="F266">
+        <v>0.3234</v>
+      </c>
+      <c r="G266">
+        <v>0.00157</v>
+      </c>
+      <c r="H266">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" t="s">
+        <v>27</v>
+      </c>
+      <c r="B267" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C267">
+        <v>7</v>
+      </c>
+      <c r="D267">
+        <v>279.2857</v>
+      </c>
+      <c r="E267">
+        <v>0.003023</v>
+      </c>
+      <c r="F267">
+        <v>0.3023</v>
+      </c>
+      <c r="G267">
+        <v>0.001402</v>
+      </c>
+      <c r="H267">
+        <v>0.1402</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268" t="s">
+        <v>39</v>
+      </c>
+      <c r="B268" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C268">
+        <v>7</v>
+      </c>
+      <c r="D268">
+        <v>293.5714</v>
+      </c>
+      <c r="E268">
+        <v>0.002876</v>
+      </c>
+      <c r="F268">
+        <v>0.2876</v>
+      </c>
+      <c r="G268">
+        <v>0.001288</v>
+      </c>
+      <c r="H268">
+        <v>0.1288</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
+      <c r="A269" t="s">
+        <v>33</v>
+      </c>
+      <c r="B269" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C269">
+        <v>7</v>
+      </c>
+      <c r="D269">
+        <v>305.5714</v>
+      </c>
+      <c r="E269">
+        <v>0.002763</v>
+      </c>
+      <c r="F269">
+        <v>0.2763</v>
+      </c>
+      <c r="G269">
+        <v>0.001202</v>
+      </c>
+      <c r="H269">
+        <v>0.1202</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8">
+      <c r="A270" t="s">
+        <v>32</v>
+      </c>
+      <c r="B270" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C270">
+        <v>7</v>
+      </c>
+      <c r="D270">
+        <v>324.2857</v>
+      </c>
+      <c r="E270">
+        <v>0.002604</v>
+      </c>
+      <c r="F270">
+        <v>0.2604</v>
+      </c>
+      <c r="G270">
+        <v>0.001085</v>
+      </c>
+      <c r="H270">
+        <v>0.1085</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8">
+      <c r="A271" t="s">
+        <v>41</v>
+      </c>
+      <c r="B271" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C271">
+        <v>7</v>
+      </c>
+      <c r="D271">
+        <v>433.8571</v>
+      </c>
+      <c r="E271">
+        <v>0.001946</v>
+      </c>
+      <c r="F271">
+        <v>0.1946</v>
+      </c>
+      <c r="G271">
+        <v>0.000644</v>
+      </c>
+      <c r="H271">
+        <v>0.0644</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
+      <c r="A272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B272" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C272">
+        <v>7</v>
+      </c>
+      <c r="D272">
+        <v>514</v>
+      </c>
+      <c r="E272">
+        <v>0.001643</v>
+      </c>
+      <c r="F272">
+        <v>0.1643</v>
+      </c>
+      <c r="G272">
+        <v>0.00047</v>
+      </c>
+      <c r="H272">
+        <v>0.047</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="A273" t="s">
+        <v>37</v>
+      </c>
+      <c r="B273" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C273">
+        <v>7</v>
+      </c>
+      <c r="D273">
+        <v>518</v>
+      </c>
+      <c r="E273">
+        <v>0.00163</v>
+      </c>
+      <c r="F273">
+        <v>0.163</v>
+      </c>
+      <c r="G273">
+        <v>0.000464</v>
+      </c>
+      <c r="H273">
+        <v>0.0464</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274" t="s">
+        <v>35</v>
+      </c>
+      <c r="B274" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C274">
+        <v>7</v>
+      </c>
+      <c r="D274">
+        <v>547.8570999999999</v>
+      </c>
+      <c r="E274">
+        <v>0.001541</v>
+      </c>
+      <c r="F274">
+        <v>0.1541</v>
+      </c>
+      <c r="G274">
+        <v>0.000417</v>
+      </c>
+      <c r="H274">
+        <v>0.0417</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8">
+      <c r="A275" t="s">
+        <v>44</v>
+      </c>
+      <c r="B275" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C275">
+        <v>7</v>
+      </c>
+      <c r="D275">
+        <v>569.2857</v>
+      </c>
+      <c r="E275">
+        <v>0.001483</v>
+      </c>
+      <c r="F275">
+        <v>0.1483</v>
+      </c>
+      <c r="G275">
+        <v>0.000388</v>
+      </c>
+      <c r="H275">
+        <v>0.0388</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8">
+      <c r="A276" t="s">
+        <v>42</v>
+      </c>
+      <c r="B276" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C276">
+        <v>7</v>
+      </c>
+      <c r="D276">
+        <v>647.8570999999999</v>
+      </c>
+      <c r="E276">
+        <v>0.001303</v>
+      </c>
+      <c r="F276">
+        <v>0.1303</v>
+      </c>
+      <c r="G276">
+        <v>0.000304</v>
+      </c>
+      <c r="H276">
+        <v>0.0304</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="A277" t="s">
+        <v>52</v>
+      </c>
+      <c r="B277" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C277">
+        <v>7</v>
+      </c>
+      <c r="D277">
+        <v>705.6667</v>
+      </c>
+      <c r="E277">
+        <v>0.001197</v>
+      </c>
+      <c r="F277">
+        <v>0.1197</v>
+      </c>
+      <c r="G277">
+        <v>0.000258</v>
+      </c>
+      <c r="H277">
+        <v>0.0258</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8">
+      <c r="A278" t="s">
+        <v>45</v>
+      </c>
+      <c r="B278" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C278">
+        <v>7</v>
+      </c>
+      <c r="D278">
+        <v>855</v>
+      </c>
+      <c r="E278">
+        <v>0.0009879999999999999</v>
+      </c>
+      <c r="F278">
+        <v>0.0988</v>
+      </c>
+      <c r="G278">
+        <v>0.000178</v>
+      </c>
+      <c r="H278">
+        <v>0.0178</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8">
+      <c r="A279" t="s">
+        <v>49</v>
+      </c>
+      <c r="B279" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C279">
+        <v>7</v>
+      </c>
+      <c r="D279">
+        <v>890.7143</v>
+      </c>
+      <c r="E279">
+        <v>0.0009479999999999999</v>
+      </c>
+      <c r="F279">
+        <v>0.0948</v>
+      </c>
+      <c r="G279">
+        <v>0.000164</v>
+      </c>
+      <c r="H279">
+        <v>0.0164</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="A280" t="s">
+        <v>50</v>
+      </c>
+      <c r="B280" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C280">
+        <v>7</v>
+      </c>
+      <c r="D280">
+        <v>1212.1429</v>
+      </c>
+      <c r="E280">
+        <v>0.000697</v>
+      </c>
+      <c r="F280">
+        <v>0.0697</v>
+      </c>
+      <c r="G280">
+        <v>9.000000000000001E-05</v>
+      </c>
+      <c r="H280">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281" t="s">
+        <v>48</v>
+      </c>
+      <c r="B281" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C281">
+        <v>7</v>
+      </c>
+      <c r="D281">
+        <v>1247.3333</v>
+      </c>
+      <c r="E281">
+        <v>0.000677</v>
+      </c>
+      <c r="F281">
+        <v>0.0677</v>
+      </c>
+      <c r="G281">
+        <v>8.500000000000001E-05</v>
+      </c>
+      <c r="H281">
+        <v>0.008500000000000001</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8">
+      <c r="A282" t="s">
+        <v>46</v>
+      </c>
+      <c r="B282" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C282">
+        <v>7</v>
+      </c>
+      <c r="D282">
+        <v>1247.8571</v>
+      </c>
+      <c r="E282">
+        <v>0.000677</v>
+      </c>
+      <c r="F282">
+        <v>0.0677</v>
+      </c>
+      <c r="G282">
+        <v>8.500000000000001E-05</v>
+      </c>
+      <c r="H282">
+        <v>0.008500000000000001</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8">
+      <c r="A283" t="s">
+        <v>51</v>
+      </c>
+      <c r="B283" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C283">
+        <v>7</v>
+      </c>
+      <c r="D283">
+        <v>1247.3333</v>
+      </c>
+      <c r="E283">
+        <v>0.000677</v>
+      </c>
+      <c r="F283">
+        <v>0.0677</v>
+      </c>
+      <c r="G283">
+        <v>8.500000000000001E-05</v>
+      </c>
+      <c r="H283">
+        <v>0.008500000000000001</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8">
+      <c r="A284" t="s">
+        <v>53</v>
+      </c>
+      <c r="B284" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C284">
+        <v>7</v>
+      </c>
+      <c r="D284">
+        <v>1664</v>
+      </c>
+      <c r="E284">
+        <v>0.000507</v>
+      </c>
+      <c r="F284">
+        <v>0.0507</v>
+      </c>
+      <c r="G284">
+        <v>4.8E-05</v>
+      </c>
+      <c r="H284">
+        <v>0.0048</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="A285" t="s">
+        <v>47</v>
+      </c>
+      <c r="B285" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C285">
+        <v>7</v>
+      </c>
+      <c r="D285">
+        <v>1926.4286</v>
+      </c>
+      <c r="E285">
+        <v>0.000438</v>
+      </c>
+      <c r="F285">
+        <v>0.0438</v>
+      </c>
+      <c r="G285">
+        <v>3.6E-05</v>
+      </c>
+      <c r="H285">
+        <v>0.0036</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8">
+      <c r="A286" t="s">
+        <v>54</v>
+      </c>
+      <c r="B286" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C286">
+        <v>7</v>
+      </c>
+      <c r="D286">
+        <v>1997.3333</v>
+      </c>
+      <c r="E286">
+        <v>0.000423</v>
+      </c>
+      <c r="F286">
+        <v>0.0423</v>
+      </c>
+      <c r="G286">
+        <v>3.3E-05</v>
+      </c>
+      <c r="H286">
+        <v>0.0033</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:H330"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -7982,6 +7982,1150 @@
         <v>0.0033</v>
       </c>
     </row>
+    <row r="287" spans="1:8">
+      <c r="A287" t="s">
+        <v>9</v>
+      </c>
+      <c r="B287" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C287">
+        <v>7</v>
+      </c>
+      <c r="D287">
+        <v>4.8743</v>
+      </c>
+      <c r="E287">
+        <v>0.173086</v>
+      </c>
+      <c r="F287">
+        <v>17.3086</v>
+      </c>
+      <c r="G287">
+        <v>0.185811</v>
+      </c>
+      <c r="H287">
+        <v>18.5811</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8">
+      <c r="A288" t="s">
+        <v>8</v>
+      </c>
+      <c r="B288" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C288">
+        <v>7</v>
+      </c>
+      <c r="D288">
+        <v>6.4829</v>
+      </c>
+      <c r="E288">
+        <v>0.130139</v>
+      </c>
+      <c r="F288">
+        <v>13.0139</v>
+      </c>
+      <c r="G288">
+        <v>0.138911</v>
+      </c>
+      <c r="H288">
+        <v>13.8911</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8">
+      <c r="A289" t="s">
+        <v>13</v>
+      </c>
+      <c r="B289" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C289">
+        <v>7</v>
+      </c>
+      <c r="D289">
+        <v>7.4514</v>
+      </c>
+      <c r="E289">
+        <v>0.113223</v>
+      </c>
+      <c r="F289">
+        <v>11.3223</v>
+      </c>
+      <c r="G289">
+        <v>0.120439</v>
+      </c>
+      <c r="H289">
+        <v>12.0439</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8">
+      <c r="A290" t="s">
+        <v>10</v>
+      </c>
+      <c r="B290" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C290">
+        <v>7</v>
+      </c>
+      <c r="D290">
+        <v>7.6071</v>
+      </c>
+      <c r="E290">
+        <v>0.110905</v>
+      </c>
+      <c r="F290">
+        <v>11.0905</v>
+      </c>
+      <c r="G290">
+        <v>0.117909</v>
+      </c>
+      <c r="H290">
+        <v>11.7909</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291" t="s">
+        <v>11</v>
+      </c>
+      <c r="B291" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C291">
+        <v>7</v>
+      </c>
+      <c r="D291">
+        <v>10.8286</v>
+      </c>
+      <c r="E291">
+        <v>0.077912</v>
+      </c>
+      <c r="F291">
+        <v>7.7912</v>
+      </c>
+      <c r="G291">
+        <v>0.081889</v>
+      </c>
+      <c r="H291">
+        <v>8.1889</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8">
+      <c r="A292" t="s">
+        <v>14</v>
+      </c>
+      <c r="B292" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C292">
+        <v>7</v>
+      </c>
+      <c r="D292">
+        <v>14.6</v>
+      </c>
+      <c r="E292">
+        <v>0.057786</v>
+      </c>
+      <c r="F292">
+        <v>5.7786</v>
+      </c>
+      <c r="G292">
+        <v>0.059928</v>
+      </c>
+      <c r="H292">
+        <v>5.9928</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
+      <c r="A293" t="s">
+        <v>12</v>
+      </c>
+      <c r="B293" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C293">
+        <v>7</v>
+      </c>
+      <c r="D293">
+        <v>14.9429</v>
+      </c>
+      <c r="E293">
+        <v>0.05646</v>
+      </c>
+      <c r="F293">
+        <v>5.646</v>
+      </c>
+      <c r="G293">
+        <v>0.058482</v>
+      </c>
+      <c r="H293">
+        <v>5.8482</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
+      <c r="A294" t="s">
+        <v>15</v>
+      </c>
+      <c r="B294" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C294">
+        <v>7</v>
+      </c>
+      <c r="D294">
+        <v>17.2286</v>
+      </c>
+      <c r="E294">
+        <v>0.048969</v>
+      </c>
+      <c r="F294">
+        <v>4.8969</v>
+      </c>
+      <c r="G294">
+        <v>0.050314</v>
+      </c>
+      <c r="H294">
+        <v>5.0314</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
+      <c r="A295" t="s">
+        <v>21</v>
+      </c>
+      <c r="B295" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C295">
+        <v>7</v>
+      </c>
+      <c r="D295">
+        <v>32.1429</v>
+      </c>
+      <c r="E295">
+        <v>0.026248</v>
+      </c>
+      <c r="F295">
+        <v>2.6248</v>
+      </c>
+      <c r="G295">
+        <v>0.025582</v>
+      </c>
+      <c r="H295">
+        <v>2.5582</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
+      <c r="A296" t="s">
+        <v>16</v>
+      </c>
+      <c r="B296" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296">
+        <v>32.4286</v>
+      </c>
+      <c r="E296">
+        <v>0.026016</v>
+      </c>
+      <c r="F296">
+        <v>2.6016</v>
+      </c>
+      <c r="G296">
+        <v>0.025331</v>
+      </c>
+      <c r="H296">
+        <v>2.5331</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297" t="s">
+        <v>19</v>
+      </c>
+      <c r="B297" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C297">
+        <v>7</v>
+      </c>
+      <c r="D297">
+        <v>35.1429</v>
+      </c>
+      <c r="E297">
+        <v>0.024007</v>
+      </c>
+      <c r="F297">
+        <v>2.4007</v>
+      </c>
+      <c r="G297">
+        <v>0.023151</v>
+      </c>
+      <c r="H297">
+        <v>2.3151</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" t="s">
+        <v>20</v>
+      </c>
+      <c r="B298" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C298">
+        <v>7</v>
+      </c>
+      <c r="D298">
+        <v>40</v>
+      </c>
+      <c r="E298">
+        <v>0.021092</v>
+      </c>
+      <c r="F298">
+        <v>2.1092</v>
+      </c>
+      <c r="G298">
+        <v>0.019995</v>
+      </c>
+      <c r="H298">
+        <v>1.9995</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
+      <c r="A299" t="s">
+        <v>18</v>
+      </c>
+      <c r="B299" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C299">
+        <v>7</v>
+      </c>
+      <c r="D299">
+        <v>47</v>
+      </c>
+      <c r="E299">
+        <v>0.01795</v>
+      </c>
+      <c r="F299">
+        <v>1.795</v>
+      </c>
+      <c r="G299">
+        <v>0.016604</v>
+      </c>
+      <c r="H299">
+        <v>1.6604</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300" t="s">
+        <v>22</v>
+      </c>
+      <c r="B300" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C300">
+        <v>7</v>
+      </c>
+      <c r="D300">
+        <v>52.5714</v>
+      </c>
+      <c r="E300">
+        <v>0.016048</v>
+      </c>
+      <c r="F300">
+        <v>1.6048</v>
+      </c>
+      <c r="G300">
+        <v>0.014558</v>
+      </c>
+      <c r="H300">
+        <v>1.4558</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301" t="s">
+        <v>17</v>
+      </c>
+      <c r="B301" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C301">
+        <v>7</v>
+      </c>
+      <c r="D301">
+        <v>52.7143</v>
+      </c>
+      <c r="E301">
+        <v>0.016005</v>
+      </c>
+      <c r="F301">
+        <v>1.6005</v>
+      </c>
+      <c r="G301">
+        <v>0.014511</v>
+      </c>
+      <c r="H301">
+        <v>1.4511</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302" t="s">
+        <v>24</v>
+      </c>
+      <c r="B302" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C302">
+        <v>7</v>
+      </c>
+      <c r="D302">
+        <v>80.1429</v>
+      </c>
+      <c r="E302">
+        <v>0.010527</v>
+      </c>
+      <c r="F302">
+        <v>1.0527</v>
+      </c>
+      <c r="G302">
+        <v>0.008680999999999999</v>
+      </c>
+      <c r="H302">
+        <v>0.8681</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
+      <c r="A303" t="s">
+        <v>26</v>
+      </c>
+      <c r="B303" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C303">
+        <v>7</v>
+      </c>
+      <c r="D303">
+        <v>112.2857</v>
+      </c>
+      <c r="E303">
+        <v>0.007514</v>
+      </c>
+      <c r="F303">
+        <v>0.7514</v>
+      </c>
+      <c r="G303">
+        <v>0.005562</v>
+      </c>
+      <c r="H303">
+        <v>0.5562</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304" t="s">
+        <v>34</v>
+      </c>
+      <c r="B304" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C304">
+        <v>7</v>
+      </c>
+      <c r="D304">
+        <v>137.8571</v>
+      </c>
+      <c r="E304">
+        <v>0.00612</v>
+      </c>
+      <c r="F304">
+        <v>0.612</v>
+      </c>
+      <c r="G304">
+        <v>0.004169</v>
+      </c>
+      <c r="H304">
+        <v>0.4169</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
+      <c r="A305" t="s">
+        <v>31</v>
+      </c>
+      <c r="B305" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C305">
+        <v>7</v>
+      </c>
+      <c r="D305">
+        <v>138.5714</v>
+      </c>
+      <c r="E305">
+        <v>0.006088</v>
+      </c>
+      <c r="F305">
+        <v>0.6088</v>
+      </c>
+      <c r="G305">
+        <v>0.004138</v>
+      </c>
+      <c r="H305">
+        <v>0.4138</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306" t="s">
+        <v>28</v>
+      </c>
+      <c r="B306" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C306">
+        <v>7</v>
+      </c>
+      <c r="D306">
+        <v>153.5714</v>
+      </c>
+      <c r="E306">
+        <v>0.005494</v>
+      </c>
+      <c r="F306">
+        <v>0.5494</v>
+      </c>
+      <c r="G306">
+        <v>0.003561</v>
+      </c>
+      <c r="H306">
+        <v>0.3561</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8">
+      <c r="A307" t="s">
+        <v>30</v>
+      </c>
+      <c r="B307" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C307">
+        <v>7</v>
+      </c>
+      <c r="D307">
+        <v>187.2857</v>
+      </c>
+      <c r="E307">
+        <v>0.004505</v>
+      </c>
+      <c r="F307">
+        <v>0.4505</v>
+      </c>
+      <c r="G307">
+        <v>0.002636</v>
+      </c>
+      <c r="H307">
+        <v>0.2636</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
+      <c r="A308" t="s">
+        <v>29</v>
+      </c>
+      <c r="B308" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C308">
+        <v>7</v>
+      </c>
+      <c r="D308">
+        <v>188.2857</v>
+      </c>
+      <c r="E308">
+        <v>0.004481</v>
+      </c>
+      <c r="F308">
+        <v>0.4481</v>
+      </c>
+      <c r="G308">
+        <v>0.002614</v>
+      </c>
+      <c r="H308">
+        <v>0.2614</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8">
+      <c r="A309" t="s">
+        <v>23</v>
+      </c>
+      <c r="B309" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C309">
+        <v>7</v>
+      </c>
+      <c r="D309">
+        <v>190</v>
+      </c>
+      <c r="E309">
+        <v>0.00444</v>
+      </c>
+      <c r="F309">
+        <v>0.444</v>
+      </c>
+      <c r="G309">
+        <v>0.002578</v>
+      </c>
+      <c r="H309">
+        <v>0.2578</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8">
+      <c r="A310" t="s">
+        <v>40</v>
+      </c>
+      <c r="B310" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C310">
+        <v>7</v>
+      </c>
+      <c r="D310">
+        <v>206.3333</v>
+      </c>
+      <c r="E310">
+        <v>0.004089</v>
+      </c>
+      <c r="F310">
+        <v>0.4089</v>
+      </c>
+      <c r="G310">
+        <v>0.002264</v>
+      </c>
+      <c r="H310">
+        <v>0.2264</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="A311" t="s">
+        <v>36</v>
+      </c>
+      <c r="B311" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C311">
+        <v>7</v>
+      </c>
+      <c r="D311">
+        <v>232.5714</v>
+      </c>
+      <c r="E311">
+        <v>0.003628</v>
+      </c>
+      <c r="F311">
+        <v>0.3628</v>
+      </c>
+      <c r="G311">
+        <v>0.001866</v>
+      </c>
+      <c r="H311">
+        <v>0.1866</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
+      <c r="A312" t="s">
+        <v>39</v>
+      </c>
+      <c r="B312" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C312">
+        <v>7</v>
+      </c>
+      <c r="D312">
+        <v>288</v>
+      </c>
+      <c r="E312">
+        <v>0.002929</v>
+      </c>
+      <c r="F312">
+        <v>0.2929</v>
+      </c>
+      <c r="G312">
+        <v>0.001304</v>
+      </c>
+      <c r="H312">
+        <v>0.1304</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8">
+      <c r="A313" t="s">
+        <v>27</v>
+      </c>
+      <c r="B313" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C313">
+        <v>7</v>
+      </c>
+      <c r="D313">
+        <v>289.2857</v>
+      </c>
+      <c r="E313">
+        <v>0.002916</v>
+      </c>
+      <c r="F313">
+        <v>0.2916</v>
+      </c>
+      <c r="G313">
+        <v>0.001294</v>
+      </c>
+      <c r="H313">
+        <v>0.1294</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8">
+      <c r="A314" t="s">
+        <v>33</v>
+      </c>
+      <c r="B314" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C314">
+        <v>7</v>
+      </c>
+      <c r="D314">
+        <v>314.4286</v>
+      </c>
+      <c r="E314">
+        <v>0.002683</v>
+      </c>
+      <c r="F314">
+        <v>0.2683</v>
+      </c>
+      <c r="G314">
+        <v>0.00112</v>
+      </c>
+      <c r="H314">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8">
+      <c r="A315" t="s">
+        <v>32</v>
+      </c>
+      <c r="B315" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C315">
+        <v>7</v>
+      </c>
+      <c r="D315">
+        <v>320.1429</v>
+      </c>
+      <c r="E315">
+        <v>0.002635</v>
+      </c>
+      <c r="F315">
+        <v>0.2635</v>
+      </c>
+      <c r="G315">
+        <v>0.001085</v>
+      </c>
+      <c r="H315">
+        <v>0.1085</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8">
+      <c r="A316" t="s">
+        <v>41</v>
+      </c>
+      <c r="B316" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C316">
+        <v>7</v>
+      </c>
+      <c r="D316">
+        <v>331</v>
+      </c>
+      <c r="E316">
+        <v>0.002549</v>
+      </c>
+      <c r="F316">
+        <v>0.2549</v>
+      </c>
+      <c r="G316">
+        <v>0.001024</v>
+      </c>
+      <c r="H316">
+        <v>0.1024</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8">
+      <c r="A317" t="s">
+        <v>37</v>
+      </c>
+      <c r="B317" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C317">
+        <v>7</v>
+      </c>
+      <c r="D317">
+        <v>529.5714</v>
+      </c>
+      <c r="E317">
+        <v>0.001593</v>
+      </c>
+      <c r="F317">
+        <v>0.1593</v>
+      </c>
+      <c r="G317">
+        <v>0.000434</v>
+      </c>
+      <c r="H317">
+        <v>0.0434</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
+      <c r="A318" t="s">
+        <v>38</v>
+      </c>
+      <c r="B318" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C318">
+        <v>7</v>
+      </c>
+      <c r="D318">
+        <v>547.8570999999999</v>
+      </c>
+      <c r="E318">
+        <v>0.00154</v>
+      </c>
+      <c r="F318">
+        <v>0.154</v>
+      </c>
+      <c r="G318">
+        <v>0.000407</v>
+      </c>
+      <c r="H318">
+        <v>0.0407</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8">
+      <c r="A319" t="s">
+        <v>35</v>
+      </c>
+      <c r="B319" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C319">
+        <v>7</v>
+      </c>
+      <c r="D319">
+        <v>583.5714</v>
+      </c>
+      <c r="E319">
+        <v>0.001446</v>
+      </c>
+      <c r="F319">
+        <v>0.1446</v>
+      </c>
+      <c r="G319">
+        <v>0.000361</v>
+      </c>
+      <c r="H319">
+        <v>0.0361</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8">
+      <c r="A320" t="s">
+        <v>44</v>
+      </c>
+      <c r="B320" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C320">
+        <v>7</v>
+      </c>
+      <c r="D320">
+        <v>647.8570999999999</v>
+      </c>
+      <c r="E320">
+        <v>0.001302</v>
+      </c>
+      <c r="F320">
+        <v>0.1302</v>
+      </c>
+      <c r="G320">
+        <v>0.000296</v>
+      </c>
+      <c r="H320">
+        <v>0.0296</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="A321" t="s">
+        <v>42</v>
+      </c>
+      <c r="B321" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C321">
+        <v>7</v>
+      </c>
+      <c r="D321">
+        <v>647.8570999999999</v>
+      </c>
+      <c r="E321">
+        <v>0.001302</v>
+      </c>
+      <c r="F321">
+        <v>0.1302</v>
+      </c>
+      <c r="G321">
+        <v>0.000296</v>
+      </c>
+      <c r="H321">
+        <v>0.0296</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="A322" t="s">
+        <v>52</v>
+      </c>
+      <c r="B322" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C322">
+        <v>7</v>
+      </c>
+      <c r="D322">
+        <v>747.8570999999999</v>
+      </c>
+      <c r="E322">
+        <v>0.001128</v>
+      </c>
+      <c r="F322">
+        <v>0.1128</v>
+      </c>
+      <c r="G322">
+        <v>0.000224</v>
+      </c>
+      <c r="H322">
+        <v>0.0224</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="A323" t="s">
+        <v>45</v>
+      </c>
+      <c r="B323" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C323">
+        <v>7</v>
+      </c>
+      <c r="D323">
+        <v>855</v>
+      </c>
+      <c r="E323">
+        <v>0.000987</v>
+      </c>
+      <c r="F323">
+        <v>0.0987</v>
+      </c>
+      <c r="G323">
+        <v>0.000173</v>
+      </c>
+      <c r="H323">
+        <v>0.0173</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="A324" t="s">
+        <v>49</v>
+      </c>
+      <c r="B324" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C324">
+        <v>7</v>
+      </c>
+      <c r="D324">
+        <v>890.7143</v>
+      </c>
+      <c r="E324">
+        <v>0.000947</v>
+      </c>
+      <c r="F324">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="G324">
+        <v>0.00016</v>
+      </c>
+      <c r="H324">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
+      <c r="A325" t="s">
+        <v>51</v>
+      </c>
+      <c r="B325" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C325">
+        <v>7</v>
+      </c>
+      <c r="D325">
+        <v>1212.1429</v>
+      </c>
+      <c r="E325">
+        <v>0.000696</v>
+      </c>
+      <c r="F325">
+        <v>0.0696</v>
+      </c>
+      <c r="G325">
+        <v>8.7E-05</v>
+      </c>
+      <c r="H325">
+        <v>0.008699999999999999</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
+      <c r="A326" t="s">
+        <v>46</v>
+      </c>
+      <c r="B326" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C326">
+        <v>7</v>
+      </c>
+      <c r="D326">
+        <v>1247.8571</v>
+      </c>
+      <c r="E326">
+        <v>0.000676</v>
+      </c>
+      <c r="F326">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="G326">
+        <v>8.2E-05</v>
+      </c>
+      <c r="H326">
+        <v>0.008200000000000001</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8">
+      <c r="A327" t="s">
+        <v>48</v>
+      </c>
+      <c r="B327" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C327">
+        <v>7</v>
+      </c>
+      <c r="D327">
+        <v>1569.2857</v>
+      </c>
+      <c r="E327">
+        <v>0.000538</v>
+      </c>
+      <c r="F327">
+        <v>0.0538</v>
+      </c>
+      <c r="G327">
+        <v>5.2E-05</v>
+      </c>
+      <c r="H327">
+        <v>0.0052</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328" t="s">
+        <v>50</v>
+      </c>
+      <c r="B328" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C328">
+        <v>7</v>
+      </c>
+      <c r="D328">
+        <v>1664</v>
+      </c>
+      <c r="E328">
+        <v>0.000507</v>
+      </c>
+      <c r="F328">
+        <v>0.0507</v>
+      </c>
+      <c r="G328">
+        <v>4.7E-05</v>
+      </c>
+      <c r="H328">
+        <v>0.0047</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" t="s">
+        <v>54</v>
+      </c>
+      <c r="B329" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C329">
+        <v>7</v>
+      </c>
+      <c r="D329">
+        <v>1855</v>
+      </c>
+      <c r="E329">
+        <v>0.000455</v>
+      </c>
+      <c r="F329">
+        <v>0.0455</v>
+      </c>
+      <c r="G329">
+        <v>3.7E-05</v>
+      </c>
+      <c r="H329">
+        <v>0.0037</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330" t="s">
+        <v>47</v>
+      </c>
+      <c r="B330" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C330">
+        <v>7</v>
+      </c>
+      <c r="D330">
+        <v>1926.4286</v>
+      </c>
+      <c r="E330">
+        <v>0.000438</v>
+      </c>
+      <c r="F330">
+        <v>0.0438</v>
+      </c>
+      <c r="G330">
+        <v>3.5E-05</v>
+      </c>
+      <c r="H330">
+        <v>0.0035</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H330"/>
+  <dimension ref="A1:H385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -7984,85 +7984,31 @@
     </row>
     <row r="287" spans="1:8">
       <c r="A287" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="B287" s="2">
-        <v>46197</v>
-      </c>
-      <c r="C287">
-        <v>7</v>
-      </c>
-      <c r="D287">
-        <v>4.8743</v>
-      </c>
-      <c r="E287">
-        <v>0.173086</v>
-      </c>
-      <c r="F287">
-        <v>17.3086</v>
-      </c>
-      <c r="G287">
-        <v>0.185811</v>
-      </c>
-      <c r="H287">
-        <v>18.5811</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B288" s="2">
-        <v>46197</v>
-      </c>
-      <c r="C288">
-        <v>7</v>
-      </c>
-      <c r="D288">
-        <v>6.4829</v>
-      </c>
-      <c r="E288">
-        <v>0.130139</v>
-      </c>
-      <c r="F288">
-        <v>13.0139</v>
-      </c>
-      <c r="G288">
-        <v>0.138911</v>
-      </c>
-      <c r="H288">
-        <v>13.8911</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B289" s="2">
-        <v>46197</v>
-      </c>
-      <c r="C289">
-        <v>7</v>
-      </c>
-      <c r="D289">
-        <v>7.4514</v>
-      </c>
-      <c r="E289">
-        <v>0.113223</v>
-      </c>
-      <c r="F289">
-        <v>11.3223</v>
-      </c>
-      <c r="G289">
-        <v>0.120439</v>
-      </c>
-      <c r="H289">
-        <v>12.0439</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B290" s="2">
         <v>46197</v>
@@ -8071,24 +8017,24 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>7.6071</v>
+        <v>4.8743</v>
       </c>
       <c r="E290">
-        <v>0.110905</v>
+        <v>0.173086</v>
       </c>
       <c r="F290">
-        <v>11.0905</v>
+        <v>17.3086</v>
       </c>
       <c r="G290">
-        <v>0.117909</v>
+        <v>0.185811</v>
       </c>
       <c r="H290">
-        <v>11.7909</v>
+        <v>18.5811</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B291" s="2">
         <v>46197</v>
@@ -8097,24 +8043,24 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>10.8286</v>
+        <v>6.4829</v>
       </c>
       <c r="E291">
-        <v>0.077912</v>
+        <v>0.130139</v>
       </c>
       <c r="F291">
-        <v>7.7912</v>
+        <v>13.0139</v>
       </c>
       <c r="G291">
-        <v>0.081889</v>
+        <v>0.138911</v>
       </c>
       <c r="H291">
-        <v>8.1889</v>
+        <v>13.8911</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B292" s="2">
         <v>46197</v>
@@ -8123,24 +8069,24 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>14.6</v>
+        <v>7.4514</v>
       </c>
       <c r="E292">
-        <v>0.057786</v>
+        <v>0.113223</v>
       </c>
       <c r="F292">
-        <v>5.7786</v>
+        <v>11.3223</v>
       </c>
       <c r="G292">
-        <v>0.059928</v>
+        <v>0.120439</v>
       </c>
       <c r="H292">
-        <v>5.9928</v>
+        <v>12.0439</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B293" s="2">
         <v>46197</v>
@@ -8149,24 +8095,24 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>14.9429</v>
+        <v>7.6071</v>
       </c>
       <c r="E293">
-        <v>0.05646</v>
+        <v>0.110905</v>
       </c>
       <c r="F293">
-        <v>5.646</v>
+        <v>11.0905</v>
       </c>
       <c r="G293">
-        <v>0.058482</v>
+        <v>0.117909</v>
       </c>
       <c r="H293">
-        <v>5.8482</v>
+        <v>11.7909</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B294" s="2">
         <v>46197</v>
@@ -8175,24 +8121,24 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>17.2286</v>
+        <v>10.8286</v>
       </c>
       <c r="E294">
-        <v>0.048969</v>
+        <v>0.077912</v>
       </c>
       <c r="F294">
-        <v>4.8969</v>
+        <v>7.7912</v>
       </c>
       <c r="G294">
-        <v>0.050314</v>
+        <v>0.081889</v>
       </c>
       <c r="H294">
-        <v>5.0314</v>
+        <v>8.1889</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B295" s="2">
         <v>46197</v>
@@ -8201,24 +8147,24 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>32.1429</v>
+        <v>14.6</v>
       </c>
       <c r="E295">
-        <v>0.026248</v>
+        <v>0.057786</v>
       </c>
       <c r="F295">
-        <v>2.6248</v>
+        <v>5.7786</v>
       </c>
       <c r="G295">
-        <v>0.025582</v>
+        <v>0.059928</v>
       </c>
       <c r="H295">
-        <v>2.5582</v>
+        <v>5.9928</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B296" s="2">
         <v>46197</v>
@@ -8227,24 +8173,24 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>32.4286</v>
+        <v>14.9429</v>
       </c>
       <c r="E296">
-        <v>0.026016</v>
+        <v>0.05646</v>
       </c>
       <c r="F296">
-        <v>2.6016</v>
+        <v>5.646</v>
       </c>
       <c r="G296">
-        <v>0.025331</v>
+        <v>0.058482</v>
       </c>
       <c r="H296">
-        <v>2.5331</v>
+        <v>5.8482</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B297" s="2">
         <v>46197</v>
@@ -8253,24 +8199,24 @@
         <v>7</v>
       </c>
       <c r="D297">
-        <v>35.1429</v>
+        <v>17.2286</v>
       </c>
       <c r="E297">
-        <v>0.024007</v>
+        <v>0.048969</v>
       </c>
       <c r="F297">
-        <v>2.4007</v>
+        <v>4.8969</v>
       </c>
       <c r="G297">
-        <v>0.023151</v>
+        <v>0.050314</v>
       </c>
       <c r="H297">
-        <v>2.3151</v>
+        <v>5.0314</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B298" s="2">
         <v>46197</v>
@@ -8279,24 +8225,24 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>40</v>
+        <v>32.1429</v>
       </c>
       <c r="E298">
-        <v>0.021092</v>
+        <v>0.026248</v>
       </c>
       <c r="F298">
-        <v>2.1092</v>
+        <v>2.6248</v>
       </c>
       <c r="G298">
-        <v>0.019995</v>
+        <v>0.025582</v>
       </c>
       <c r="H298">
-        <v>1.9995</v>
+        <v>2.5582</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B299" s="2">
         <v>46197</v>
@@ -8305,24 +8251,24 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>47</v>
+        <v>32.4286</v>
       </c>
       <c r="E299">
-        <v>0.01795</v>
+        <v>0.026016</v>
       </c>
       <c r="F299">
-        <v>1.795</v>
+        <v>2.6016</v>
       </c>
       <c r="G299">
-        <v>0.016604</v>
+        <v>0.025331</v>
       </c>
       <c r="H299">
-        <v>1.6604</v>
+        <v>2.5331</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B300" s="2">
         <v>46197</v>
@@ -8331,24 +8277,24 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>52.5714</v>
+        <v>35.1429</v>
       </c>
       <c r="E300">
-        <v>0.016048</v>
+        <v>0.024007</v>
       </c>
       <c r="F300">
-        <v>1.6048</v>
+        <v>2.4007</v>
       </c>
       <c r="G300">
-        <v>0.014558</v>
+        <v>0.023151</v>
       </c>
       <c r="H300">
-        <v>1.4558</v>
+        <v>2.3151</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B301" s="2">
         <v>46197</v>
@@ -8357,24 +8303,24 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>52.7143</v>
+        <v>40</v>
       </c>
       <c r="E301">
-        <v>0.016005</v>
+        <v>0.021092</v>
       </c>
       <c r="F301">
-        <v>1.6005</v>
+        <v>2.1092</v>
       </c>
       <c r="G301">
-        <v>0.014511</v>
+        <v>0.019995</v>
       </c>
       <c r="H301">
-        <v>1.4511</v>
+        <v>1.9995</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B302" s="2">
         <v>46197</v>
@@ -8383,24 +8329,24 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>80.1429</v>
+        <v>47</v>
       </c>
       <c r="E302">
-        <v>0.010527</v>
+        <v>0.01795</v>
       </c>
       <c r="F302">
-        <v>1.0527</v>
+        <v>1.795</v>
       </c>
       <c r="G302">
-        <v>0.008680999999999999</v>
+        <v>0.016604</v>
       </c>
       <c r="H302">
-        <v>0.8681</v>
+        <v>1.6604</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B303" s="2">
         <v>46197</v>
@@ -8409,24 +8355,24 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>112.2857</v>
+        <v>52.5714</v>
       </c>
       <c r="E303">
-        <v>0.007514</v>
+        <v>0.016048</v>
       </c>
       <c r="F303">
-        <v>0.7514</v>
+        <v>1.6048</v>
       </c>
       <c r="G303">
-        <v>0.005562</v>
+        <v>0.014558</v>
       </c>
       <c r="H303">
-        <v>0.5562</v>
+        <v>1.4558</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B304" s="2">
         <v>46197</v>
@@ -8435,24 +8381,24 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>137.8571</v>
+        <v>52.7143</v>
       </c>
       <c r="E304">
-        <v>0.00612</v>
+        <v>0.016005</v>
       </c>
       <c r="F304">
-        <v>0.612</v>
+        <v>1.6005</v>
       </c>
       <c r="G304">
-        <v>0.004169</v>
+        <v>0.014511</v>
       </c>
       <c r="H304">
-        <v>0.4169</v>
+        <v>1.4511</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B305" s="2">
         <v>46197</v>
@@ -8461,24 +8407,24 @@
         <v>7</v>
       </c>
       <c r="D305">
-        <v>138.5714</v>
+        <v>80.1429</v>
       </c>
       <c r="E305">
-        <v>0.006088</v>
+        <v>0.010527</v>
       </c>
       <c r="F305">
-        <v>0.6088</v>
+        <v>1.0527</v>
       </c>
       <c r="G305">
-        <v>0.004138</v>
+        <v>0.008680999999999999</v>
       </c>
       <c r="H305">
-        <v>0.4138</v>
+        <v>0.8681</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B306" s="2">
         <v>46197</v>
@@ -8487,24 +8433,24 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>153.5714</v>
+        <v>112.2857</v>
       </c>
       <c r="E306">
-        <v>0.005494</v>
+        <v>0.007514</v>
       </c>
       <c r="F306">
-        <v>0.5494</v>
+        <v>0.7514</v>
       </c>
       <c r="G306">
-        <v>0.003561</v>
+        <v>0.005562</v>
       </c>
       <c r="H306">
-        <v>0.3561</v>
+        <v>0.5562</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B307" s="2">
         <v>46197</v>
@@ -8513,24 +8459,24 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>187.2857</v>
+        <v>137.8571</v>
       </c>
       <c r="E307">
-        <v>0.004505</v>
+        <v>0.00612</v>
       </c>
       <c r="F307">
-        <v>0.4505</v>
+        <v>0.612</v>
       </c>
       <c r="G307">
-        <v>0.002636</v>
+        <v>0.004169</v>
       </c>
       <c r="H307">
-        <v>0.2636</v>
+        <v>0.4169</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B308" s="2">
         <v>46197</v>
@@ -8539,24 +8485,24 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>188.2857</v>
+        <v>138.5714</v>
       </c>
       <c r="E308">
-        <v>0.004481</v>
+        <v>0.006088</v>
       </c>
       <c r="F308">
-        <v>0.4481</v>
+        <v>0.6088</v>
       </c>
       <c r="G308">
-        <v>0.002614</v>
+        <v>0.004138</v>
       </c>
       <c r="H308">
-        <v>0.2614</v>
+        <v>0.4138</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B309" s="2">
         <v>46197</v>
@@ -8565,24 +8511,24 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>190</v>
+        <v>153.5714</v>
       </c>
       <c r="E309">
-        <v>0.00444</v>
+        <v>0.005494</v>
       </c>
       <c r="F309">
-        <v>0.444</v>
+        <v>0.5494</v>
       </c>
       <c r="G309">
-        <v>0.002578</v>
+        <v>0.003561</v>
       </c>
       <c r="H309">
-        <v>0.2578</v>
+        <v>0.3561</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="A310" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B310" s="2">
         <v>46197</v>
@@ -8591,24 +8537,24 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>206.3333</v>
+        <v>187.2857</v>
       </c>
       <c r="E310">
-        <v>0.004089</v>
+        <v>0.004505</v>
       </c>
       <c r="F310">
-        <v>0.4089</v>
+        <v>0.4505</v>
       </c>
       <c r="G310">
-        <v>0.002264</v>
+        <v>0.002636</v>
       </c>
       <c r="H310">
-        <v>0.2264</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B311" s="2">
         <v>46197</v>
@@ -8617,24 +8563,24 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>232.5714</v>
+        <v>188.2857</v>
       </c>
       <c r="E311">
-        <v>0.003628</v>
+        <v>0.004481</v>
       </c>
       <c r="F311">
-        <v>0.3628</v>
+        <v>0.4481</v>
       </c>
       <c r="G311">
-        <v>0.001866</v>
+        <v>0.002614</v>
       </c>
       <c r="H311">
-        <v>0.1866</v>
+        <v>0.2614</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B312" s="2">
         <v>46197</v>
@@ -8643,24 +8589,24 @@
         <v>7</v>
       </c>
       <c r="D312">
-        <v>288</v>
+        <v>190</v>
       </c>
       <c r="E312">
-        <v>0.002929</v>
+        <v>0.00444</v>
       </c>
       <c r="F312">
-        <v>0.2929</v>
+        <v>0.444</v>
       </c>
       <c r="G312">
-        <v>0.001304</v>
+        <v>0.002578</v>
       </c>
       <c r="H312">
-        <v>0.1304</v>
+        <v>0.2578</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B313" s="2">
         <v>46197</v>
@@ -8669,24 +8615,24 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>289.2857</v>
+        <v>206.3333</v>
       </c>
       <c r="E313">
-        <v>0.002916</v>
+        <v>0.004089</v>
       </c>
       <c r="F313">
-        <v>0.2916</v>
+        <v>0.4089</v>
       </c>
       <c r="G313">
-        <v>0.001294</v>
+        <v>0.002264</v>
       </c>
       <c r="H313">
-        <v>0.1294</v>
+        <v>0.2264</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B314" s="2">
         <v>46197</v>
@@ -8695,24 +8641,24 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>314.4286</v>
+        <v>232.5714</v>
       </c>
       <c r="E314">
-        <v>0.002683</v>
+        <v>0.003628</v>
       </c>
       <c r="F314">
-        <v>0.2683</v>
+        <v>0.3628</v>
       </c>
       <c r="G314">
-        <v>0.00112</v>
+        <v>0.001866</v>
       </c>
       <c r="H314">
-        <v>0.112</v>
+        <v>0.1866</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="A315" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B315" s="2">
         <v>46197</v>
@@ -8721,24 +8667,24 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>320.1429</v>
+        <v>288</v>
       </c>
       <c r="E315">
-        <v>0.002635</v>
+        <v>0.002929</v>
       </c>
       <c r="F315">
-        <v>0.2635</v>
+        <v>0.2929</v>
       </c>
       <c r="G315">
-        <v>0.001085</v>
+        <v>0.001304</v>
       </c>
       <c r="H315">
-        <v>0.1085</v>
+        <v>0.1304</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B316" s="2">
         <v>46197</v>
@@ -8747,24 +8693,24 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>331</v>
+        <v>289.2857</v>
       </c>
       <c r="E316">
-        <v>0.002549</v>
+        <v>0.002916</v>
       </c>
       <c r="F316">
-        <v>0.2549</v>
+        <v>0.2916</v>
       </c>
       <c r="G316">
-        <v>0.001024</v>
+        <v>0.001294</v>
       </c>
       <c r="H316">
-        <v>0.1024</v>
+        <v>0.1294</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B317" s="2">
         <v>46197</v>
@@ -8773,24 +8719,24 @@
         <v>7</v>
       </c>
       <c r="D317">
-        <v>529.5714</v>
+        <v>314.4286</v>
       </c>
       <c r="E317">
-        <v>0.001593</v>
+        <v>0.002683</v>
       </c>
       <c r="F317">
-        <v>0.1593</v>
+        <v>0.2683</v>
       </c>
       <c r="G317">
-        <v>0.000434</v>
+        <v>0.00112</v>
       </c>
       <c r="H317">
-        <v>0.0434</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B318" s="2">
         <v>46197</v>
@@ -8799,24 +8745,24 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>547.8570999999999</v>
+        <v>320.1429</v>
       </c>
       <c r="E318">
-        <v>0.00154</v>
+        <v>0.002635</v>
       </c>
       <c r="F318">
-        <v>0.154</v>
+        <v>0.2635</v>
       </c>
       <c r="G318">
-        <v>0.000407</v>
+        <v>0.001085</v>
       </c>
       <c r="H318">
-        <v>0.0407</v>
+        <v>0.1085</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B319" s="2">
         <v>46197</v>
@@ -8825,24 +8771,24 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>583.5714</v>
+        <v>331</v>
       </c>
       <c r="E319">
-        <v>0.001446</v>
+        <v>0.002549</v>
       </c>
       <c r="F319">
-        <v>0.1446</v>
+        <v>0.2549</v>
       </c>
       <c r="G319">
-        <v>0.000361</v>
+        <v>0.001024</v>
       </c>
       <c r="H319">
-        <v>0.0361</v>
+        <v>0.1024</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B320" s="2">
         <v>46197</v>
@@ -8851,24 +8797,24 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>647.8570999999999</v>
+        <v>529.5714</v>
       </c>
       <c r="E320">
-        <v>0.001302</v>
+        <v>0.001593</v>
       </c>
       <c r="F320">
-        <v>0.1302</v>
+        <v>0.1593</v>
       </c>
       <c r="G320">
-        <v>0.000296</v>
+        <v>0.000434</v>
       </c>
       <c r="H320">
-        <v>0.0296</v>
+        <v>0.0434</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="A321" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B321" s="2">
         <v>46197</v>
@@ -8877,24 +8823,24 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>647.8570999999999</v>
+        <v>547.8570999999999</v>
       </c>
       <c r="E321">
-        <v>0.001302</v>
+        <v>0.00154</v>
       </c>
       <c r="F321">
-        <v>0.1302</v>
+        <v>0.154</v>
       </c>
       <c r="G321">
-        <v>0.000296</v>
+        <v>0.000407</v>
       </c>
       <c r="H321">
-        <v>0.0296</v>
+        <v>0.0407</v>
       </c>
     </row>
     <row r="322" spans="1:8">
       <c r="A322" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B322" s="2">
         <v>46197</v>
@@ -8903,24 +8849,24 @@
         <v>7</v>
       </c>
       <c r="D322">
-        <v>747.8570999999999</v>
+        <v>583.5714</v>
       </c>
       <c r="E322">
-        <v>0.001128</v>
+        <v>0.001446</v>
       </c>
       <c r="F322">
-        <v>0.1128</v>
+        <v>0.1446</v>
       </c>
       <c r="G322">
-        <v>0.000224</v>
+        <v>0.000361</v>
       </c>
       <c r="H322">
-        <v>0.0224</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B323" s="2">
         <v>46197</v>
@@ -8929,24 +8875,24 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>855</v>
+        <v>647.8570999999999</v>
       </c>
       <c r="E323">
-        <v>0.000987</v>
+        <v>0.001302</v>
       </c>
       <c r="F323">
-        <v>0.0987</v>
+        <v>0.1302</v>
       </c>
       <c r="G323">
-        <v>0.000173</v>
+        <v>0.000296</v>
       </c>
       <c r="H323">
-        <v>0.0173</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B324" s="2">
         <v>46197</v>
@@ -8955,24 +8901,24 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>890.7143</v>
+        <v>647.8570999999999</v>
       </c>
       <c r="E324">
-        <v>0.000947</v>
+        <v>0.001302</v>
       </c>
       <c r="F324">
-        <v>0.09470000000000001</v>
+        <v>0.1302</v>
       </c>
       <c r="G324">
-        <v>0.00016</v>
+        <v>0.000296</v>
       </c>
       <c r="H324">
-        <v>0.016</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B325" s="2">
         <v>46197</v>
@@ -8981,24 +8927,24 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>1212.1429</v>
+        <v>747.8570999999999</v>
       </c>
       <c r="E325">
-        <v>0.000696</v>
+        <v>0.001128</v>
       </c>
       <c r="F325">
-        <v>0.0696</v>
+        <v>0.1128</v>
       </c>
       <c r="G325">
-        <v>8.7E-05</v>
+        <v>0.000224</v>
       </c>
       <c r="H325">
-        <v>0.008699999999999999</v>
+        <v>0.0224</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B326" s="2">
         <v>46197</v>
@@ -9007,24 +8953,24 @@
         <v>7</v>
       </c>
       <c r="D326">
-        <v>1247.8571</v>
+        <v>855</v>
       </c>
       <c r="E326">
-        <v>0.000676</v>
+        <v>0.000987</v>
       </c>
       <c r="F326">
-        <v>0.06759999999999999</v>
+        <v>0.0987</v>
       </c>
       <c r="G326">
-        <v>8.2E-05</v>
+        <v>0.000173</v>
       </c>
       <c r="H326">
-        <v>0.008200000000000001</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B327" s="2">
         <v>46197</v>
@@ -9033,24 +8979,24 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>1569.2857</v>
+        <v>890.7143</v>
       </c>
       <c r="E327">
-        <v>0.000538</v>
+        <v>0.000947</v>
       </c>
       <c r="F327">
-        <v>0.0538</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G327">
-        <v>5.2E-05</v>
+        <v>0.00016</v>
       </c>
       <c r="H327">
-        <v>0.0052</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B328" s="2">
         <v>46197</v>
@@ -9059,24 +9005,24 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>1664</v>
+        <v>1212.1429</v>
       </c>
       <c r="E328">
-        <v>0.000507</v>
+        <v>0.000696</v>
       </c>
       <c r="F328">
-        <v>0.0507</v>
+        <v>0.0696</v>
       </c>
       <c r="G328">
-        <v>4.7E-05</v>
+        <v>8.7E-05</v>
       </c>
       <c r="H328">
-        <v>0.0047</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B329" s="2">
         <v>46197</v>
@@ -9085,24 +9031,24 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>1855</v>
+        <v>1247.8571</v>
       </c>
       <c r="E329">
-        <v>0.000455</v>
+        <v>0.000676</v>
       </c>
       <c r="F329">
-        <v>0.0455</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G329">
-        <v>3.7E-05</v>
+        <v>8.2E-05</v>
       </c>
       <c r="H329">
-        <v>0.0037</v>
+        <v>0.008200000000000001</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B330" s="2">
         <v>46197</v>
@@ -9111,19 +9057,1251 @@
         <v>7</v>
       </c>
       <c r="D330">
+        <v>1569.2857</v>
+      </c>
+      <c r="E330">
+        <v>0.000538</v>
+      </c>
+      <c r="F330">
+        <v>0.0538</v>
+      </c>
+      <c r="G330">
+        <v>5.2E-05</v>
+      </c>
+      <c r="H330">
+        <v>0.0052</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331" t="s">
+        <v>50</v>
+      </c>
+      <c r="B331" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C331">
+        <v>7</v>
+      </c>
+      <c r="D331">
+        <v>1664</v>
+      </c>
+      <c r="E331">
+        <v>0.000507</v>
+      </c>
+      <c r="F331">
+        <v>0.0507</v>
+      </c>
+      <c r="G331">
+        <v>4.7E-05</v>
+      </c>
+      <c r="H331">
+        <v>0.0047</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8">
+      <c r="A332" t="s">
+        <v>54</v>
+      </c>
+      <c r="B332" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C332">
+        <v>7</v>
+      </c>
+      <c r="D332">
+        <v>1855</v>
+      </c>
+      <c r="E332">
+        <v>0.000455</v>
+      </c>
+      <c r="F332">
+        <v>0.0455</v>
+      </c>
+      <c r="G332">
+        <v>3.7E-05</v>
+      </c>
+      <c r="H332">
+        <v>0.0037</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8">
+      <c r="A333" t="s">
+        <v>47</v>
+      </c>
+      <c r="B333" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C333">
+        <v>7</v>
+      </c>
+      <c r="D333">
         <v>1926.4286</v>
       </c>
-      <c r="E330">
+      <c r="E333">
         <v>0.000438</v>
       </c>
-      <c r="F330">
+      <c r="F333">
         <v>0.0438</v>
       </c>
-      <c r="G330">
+      <c r="G333">
         <v>3.5E-05</v>
       </c>
-      <c r="H330">
+      <c r="H333">
         <v>0.0035</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8">
+      <c r="A334" t="s">
+        <v>55</v>
+      </c>
+      <c r="B334" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335" t="s">
+        <v>53</v>
+      </c>
+      <c r="B335" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336" t="s">
+        <v>43</v>
+      </c>
+      <c r="B336" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8">
+      <c r="A337" t="s">
+        <v>25</v>
+      </c>
+      <c r="B337" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8">
+      <c r="A338" t="s">
+        <v>9</v>
+      </c>
+      <c r="B338" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C338">
+        <v>7</v>
+      </c>
+      <c r="D338">
+        <v>4.9586</v>
+      </c>
+      <c r="E338">
+        <v>0.173373</v>
+      </c>
+      <c r="F338">
+        <v>17.3373</v>
+      </c>
+      <c r="G338">
+        <v>0.184618</v>
+      </c>
+      <c r="H338">
+        <v>18.4618</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8">
+      <c r="A339" t="s">
+        <v>8</v>
+      </c>
+      <c r="B339" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C339">
+        <v>7</v>
+      </c>
+      <c r="D339">
+        <v>6.6257</v>
+      </c>
+      <c r="E339">
+        <v>0.12975</v>
+      </c>
+      <c r="F339">
+        <v>12.975</v>
+      </c>
+      <c r="G339">
+        <v>0.137438</v>
+      </c>
+      <c r="H339">
+        <v>13.7438</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8">
+      <c r="A340" t="s">
+        <v>13</v>
+      </c>
+      <c r="B340" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C340">
+        <v>7</v>
+      </c>
+      <c r="D340">
+        <v>7.0386</v>
+      </c>
+      <c r="E340">
+        <v>0.122139</v>
+      </c>
+      <c r="F340">
+        <v>12.2139</v>
+      </c>
+      <c r="G340">
+        <v>0.129207</v>
+      </c>
+      <c r="H340">
+        <v>12.9207</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8">
+      <c r="A341" t="s">
+        <v>10</v>
+      </c>
+      <c r="B341" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C341">
+        <v>7</v>
+      </c>
+      <c r="D341">
+        <v>8.4343</v>
+      </c>
+      <c r="E341">
+        <v>0.101927</v>
+      </c>
+      <c r="F341">
+        <v>10.1927</v>
+      </c>
+      <c r="G341">
+        <v>0.107351</v>
+      </c>
+      <c r="H341">
+        <v>10.7351</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8">
+      <c r="A342" t="s">
+        <v>11</v>
+      </c>
+      <c r="B342" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C342">
+        <v>7</v>
+      </c>
+      <c r="D342">
+        <v>10.5429</v>
+      </c>
+      <c r="E342">
+        <v>0.081542</v>
+      </c>
+      <c r="F342">
+        <v>8.154199999999999</v>
+      </c>
+      <c r="G342">
+        <v>0.08531</v>
+      </c>
+      <c r="H342">
+        <v>8.531000000000001</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8">
+      <c r="A343" t="s">
+        <v>12</v>
+      </c>
+      <c r="B343" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C343">
+        <v>7</v>
+      </c>
+      <c r="D343">
+        <v>13.3143</v>
+      </c>
+      <c r="E343">
+        <v>0.064569</v>
+      </c>
+      <c r="F343">
+        <v>6.4569</v>
+      </c>
+      <c r="G343">
+        <v>0.06696299999999999</v>
+      </c>
+      <c r="H343">
+        <v>6.6963</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" t="s">
+        <v>15</v>
+      </c>
+      <c r="B344" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C344">
+        <v>7</v>
+      </c>
+      <c r="D344">
+        <v>15.9571</v>
+      </c>
+      <c r="E344">
+        <v>0.053875</v>
+      </c>
+      <c r="F344">
+        <v>5.3875</v>
+      </c>
+      <c r="G344">
+        <v>0.055408</v>
+      </c>
+      <c r="H344">
+        <v>5.5408</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345" t="s">
+        <v>14</v>
+      </c>
+      <c r="B345" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C345">
+        <v>7</v>
+      </c>
+      <c r="D345">
+        <v>17.8</v>
+      </c>
+      <c r="E345">
+        <v>0.048297</v>
+      </c>
+      <c r="F345">
+        <v>4.8297</v>
+      </c>
+      <c r="G345">
+        <v>0.049383</v>
+      </c>
+      <c r="H345">
+        <v>4.9383</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" t="s">
+        <v>21</v>
+      </c>
+      <c r="B346" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C346">
+        <v>7</v>
+      </c>
+      <c r="D346">
+        <v>28.2857</v>
+      </c>
+      <c r="E346">
+        <v>0.030393</v>
+      </c>
+      <c r="F346">
+        <v>3.0393</v>
+      </c>
+      <c r="G346">
+        <v>0.030065</v>
+      </c>
+      <c r="H346">
+        <v>3.0065</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347" t="s">
+        <v>16</v>
+      </c>
+      <c r="B347" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C347">
+        <v>7</v>
+      </c>
+      <c r="D347">
+        <v>32.7143</v>
+      </c>
+      <c r="E347">
+        <v>0.026279</v>
+      </c>
+      <c r="F347">
+        <v>2.6279</v>
+      </c>
+      <c r="G347">
+        <v>0.025635</v>
+      </c>
+      <c r="H347">
+        <v>2.5635</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348" t="s">
+        <v>19</v>
+      </c>
+      <c r="B348" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C348">
+        <v>7</v>
+      </c>
+      <c r="D348">
+        <v>43.1429</v>
+      </c>
+      <c r="E348">
+        <v>0.019926</v>
+      </c>
+      <c r="F348">
+        <v>1.9926</v>
+      </c>
+      <c r="G348">
+        <v>0.018812</v>
+      </c>
+      <c r="H348">
+        <v>1.8812</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349" t="s">
+        <v>22</v>
+      </c>
+      <c r="B349" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C349">
+        <v>7</v>
+      </c>
+      <c r="D349">
+        <v>45.7143</v>
+      </c>
+      <c r="E349">
+        <v>0.018806</v>
+      </c>
+      <c r="F349">
+        <v>1.8806</v>
+      </c>
+      <c r="G349">
+        <v>0.017611</v>
+      </c>
+      <c r="H349">
+        <v>1.7611</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8">
+      <c r="A350" t="s">
+        <v>20</v>
+      </c>
+      <c r="B350" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C350">
+        <v>7</v>
+      </c>
+      <c r="D350">
+        <v>49.8571</v>
+      </c>
+      <c r="E350">
+        <v>0.017243</v>
+      </c>
+      <c r="F350">
+        <v>1.7243</v>
+      </c>
+      <c r="G350">
+        <v>0.01594</v>
+      </c>
+      <c r="H350">
+        <v>1.594</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351" t="s">
+        <v>18</v>
+      </c>
+      <c r="B351" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C351">
+        <v>7</v>
+      </c>
+      <c r="D351">
+        <v>53.4286</v>
+      </c>
+      <c r="E351">
+        <v>0.01609</v>
+      </c>
+      <c r="F351">
+        <v>1.609</v>
+      </c>
+      <c r="G351">
+        <v>0.014709</v>
+      </c>
+      <c r="H351">
+        <v>1.4709</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8">
+      <c r="A352" t="s">
+        <v>17</v>
+      </c>
+      <c r="B352" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C352">
+        <v>7</v>
+      </c>
+      <c r="D352">
+        <v>54.1429</v>
+      </c>
+      <c r="E352">
+        <v>0.015878</v>
+      </c>
+      <c r="F352">
+        <v>1.5878</v>
+      </c>
+      <c r="G352">
+        <v>0.014483</v>
+      </c>
+      <c r="H352">
+        <v>1.4483</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353" t="s">
+        <v>24</v>
+      </c>
+      <c r="B353" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C353">
+        <v>7</v>
+      </c>
+      <c r="D353">
+        <v>76.4286</v>
+      </c>
+      <c r="E353">
+        <v>0.011248</v>
+      </c>
+      <c r="F353">
+        <v>1.1248</v>
+      </c>
+      <c r="G353">
+        <v>0.009575</v>
+      </c>
+      <c r="H353">
+        <v>0.9575</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="A354" t="s">
+        <v>27</v>
+      </c>
+      <c r="B354" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C354">
+        <v>7</v>
+      </c>
+      <c r="D354">
+        <v>123.8571</v>
+      </c>
+      <c r="E354">
+        <v>0.006941</v>
+      </c>
+      <c r="F354">
+        <v>0.6941000000000001</v>
+      </c>
+      <c r="G354">
+        <v>0.005121</v>
+      </c>
+      <c r="H354">
+        <v>0.5121</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" t="s">
+        <v>26</v>
+      </c>
+      <c r="B355" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C355">
+        <v>7</v>
+      </c>
+      <c r="D355">
+        <v>132.2857</v>
+      </c>
+      <c r="E355">
+        <v>0.006499</v>
+      </c>
+      <c r="F355">
+        <v>0.6499</v>
+      </c>
+      <c r="G355">
+        <v>0.004678</v>
+      </c>
+      <c r="H355">
+        <v>0.4678</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356" t="s">
+        <v>34</v>
+      </c>
+      <c r="B356" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C356">
+        <v>7</v>
+      </c>
+      <c r="D356">
+        <v>150.5714</v>
+      </c>
+      <c r="E356">
+        <v>0.005709</v>
+      </c>
+      <c r="F356">
+        <v>0.5709</v>
+      </c>
+      <c r="G356">
+        <v>0.003899</v>
+      </c>
+      <c r="H356">
+        <v>0.3899</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8">
+      <c r="A357" t="s">
+        <v>28</v>
+      </c>
+      <c r="B357" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C357">
+        <v>7</v>
+      </c>
+      <c r="D357">
+        <v>165.7143</v>
+      </c>
+      <c r="E357">
+        <v>0.005188</v>
+      </c>
+      <c r="F357">
+        <v>0.5188</v>
+      </c>
+      <c r="G357">
+        <v>0.003394</v>
+      </c>
+      <c r="H357">
+        <v>0.3394</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8">
+      <c r="A358" t="s">
+        <v>31</v>
+      </c>
+      <c r="B358" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C358">
+        <v>7</v>
+      </c>
+      <c r="D358">
+        <v>180.5714</v>
+      </c>
+      <c r="E358">
+        <v>0.004761</v>
+      </c>
+      <c r="F358">
+        <v>0.4761</v>
+      </c>
+      <c r="G358">
+        <v>0.002989</v>
+      </c>
+      <c r="H358">
+        <v>0.2989</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" t="s">
+        <v>30</v>
+      </c>
+      <c r="B359" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C359">
+        <v>7</v>
+      </c>
+      <c r="D359">
+        <v>181.1429</v>
+      </c>
+      <c r="E359">
+        <v>0.004746</v>
+      </c>
+      <c r="F359">
+        <v>0.4746</v>
+      </c>
+      <c r="G359">
+        <v>0.002975</v>
+      </c>
+      <c r="H359">
+        <v>0.2975</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" t="s">
+        <v>40</v>
+      </c>
+      <c r="B360" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C360">
+        <v>7</v>
+      </c>
+      <c r="D360">
+        <v>199.8333</v>
+      </c>
+      <c r="E360">
+        <v>0.004302</v>
+      </c>
+      <c r="F360">
+        <v>0.4302</v>
+      </c>
+      <c r="G360">
+        <v>0.002563</v>
+      </c>
+      <c r="H360">
+        <v>0.2563</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" t="s">
+        <v>29</v>
+      </c>
+      <c r="B361" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C361">
+        <v>7</v>
+      </c>
+      <c r="D361">
+        <v>205.4286</v>
+      </c>
+      <c r="E361">
+        <v>0.004185</v>
+      </c>
+      <c r="F361">
+        <v>0.4185</v>
+      </c>
+      <c r="G361">
+        <v>0.002456</v>
+      </c>
+      <c r="H361">
+        <v>0.2456</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" t="s">
+        <v>23</v>
+      </c>
+      <c r="B362" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C362">
+        <v>7</v>
+      </c>
+      <c r="D362">
+        <v>216.5714</v>
+      </c>
+      <c r="E362">
+        <v>0.00397</v>
+      </c>
+      <c r="F362">
+        <v>0.397</v>
+      </c>
+      <c r="G362">
+        <v>0.002263</v>
+      </c>
+      <c r="H362">
+        <v>0.2263</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" t="s">
+        <v>36</v>
+      </c>
+      <c r="B363" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C363">
+        <v>7</v>
+      </c>
+      <c r="D363">
+        <v>260.7143</v>
+      </c>
+      <c r="E363">
+        <v>0.003297</v>
+      </c>
+      <c r="F363">
+        <v>0.3297</v>
+      </c>
+      <c r="G363">
+        <v>0.001681</v>
+      </c>
+      <c r="H363">
+        <v>0.1681</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" t="s">
+        <v>32</v>
+      </c>
+      <c r="B364" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C364">
+        <v>7</v>
+      </c>
+      <c r="D364">
+        <v>327.1429</v>
+      </c>
+      <c r="E364">
+        <v>0.002628</v>
+      </c>
+      <c r="F364">
+        <v>0.2628</v>
+      </c>
+      <c r="G364">
+        <v>0.001149</v>
+      </c>
+      <c r="H364">
+        <v>0.1149</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" t="s">
+        <v>41</v>
+      </c>
+      <c r="B365" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C365">
+        <v>7</v>
+      </c>
+      <c r="D365">
+        <v>337.7143</v>
+      </c>
+      <c r="E365">
+        <v>0.002546</v>
+      </c>
+      <c r="F365">
+        <v>0.2546</v>
+      </c>
+      <c r="G365">
+        <v>0.001087</v>
+      </c>
+      <c r="H365">
+        <v>0.1087</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" t="s">
+        <v>38</v>
+      </c>
+      <c r="B366" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C366">
+        <v>7</v>
+      </c>
+      <c r="D366">
+        <v>509.4286</v>
+      </c>
+      <c r="E366">
+        <v>0.001688</v>
+      </c>
+      <c r="F366">
+        <v>0.1688</v>
+      </c>
+      <c r="G366">
+        <v>0.00052</v>
+      </c>
+      <c r="H366">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" t="s">
+        <v>46</v>
+      </c>
+      <c r="B367" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C367">
+        <v>7</v>
+      </c>
+      <c r="D367">
+        <v>569.2857</v>
+      </c>
+      <c r="E367">
+        <v>0.00151</v>
+      </c>
+      <c r="F367">
+        <v>0.151</v>
+      </c>
+      <c r="G367">
+        <v>0.000423</v>
+      </c>
+      <c r="H367">
+        <v>0.0423</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" t="s">
+        <v>39</v>
+      </c>
+      <c r="B368" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C368">
+        <v>7</v>
+      </c>
+      <c r="D368">
+        <v>570</v>
+      </c>
+      <c r="E368">
+        <v>0.001508</v>
+      </c>
+      <c r="F368">
+        <v>0.1508</v>
+      </c>
+      <c r="G368">
+        <v>0.000422</v>
+      </c>
+      <c r="H368">
+        <v>0.0422</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
+      <c r="A369" t="s">
+        <v>37</v>
+      </c>
+      <c r="B369" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C369">
+        <v>7</v>
+      </c>
+      <c r="D369">
+        <v>576.4286</v>
+      </c>
+      <c r="E369">
+        <v>0.001491</v>
+      </c>
+      <c r="F369">
+        <v>0.1491</v>
+      </c>
+      <c r="G369">
+        <v>0.000413</v>
+      </c>
+      <c r="H369">
+        <v>0.0413</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
+      <c r="A370" t="s">
+        <v>44</v>
+      </c>
+      <c r="B370" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C370">
+        <v>7</v>
+      </c>
+      <c r="D370">
+        <v>647.8570999999999</v>
+      </c>
+      <c r="E370">
+        <v>0.001327</v>
+      </c>
+      <c r="F370">
+        <v>0.1327</v>
+      </c>
+      <c r="G370">
+        <v>0.000331</v>
+      </c>
+      <c r="H370">
+        <v>0.0331</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
+      <c r="A371" t="s">
+        <v>42</v>
+      </c>
+      <c r="B371" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C371">
+        <v>7</v>
+      </c>
+      <c r="D371">
+        <v>647.8570999999999</v>
+      </c>
+      <c r="E371">
+        <v>0.001327</v>
+      </c>
+      <c r="F371">
+        <v>0.1327</v>
+      </c>
+      <c r="G371">
+        <v>0.000331</v>
+      </c>
+      <c r="H371">
+        <v>0.0331</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" t="s">
+        <v>52</v>
+      </c>
+      <c r="B372" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C372">
+        <v>7</v>
+      </c>
+      <c r="D372">
+        <v>783.5714</v>
+      </c>
+      <c r="E372">
+        <v>0.001097</v>
+      </c>
+      <c r="F372">
+        <v>0.1097</v>
+      </c>
+      <c r="G372">
+        <v>0.00023</v>
+      </c>
+      <c r="H372">
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" t="s">
+        <v>45</v>
+      </c>
+      <c r="B373" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C373">
+        <v>7</v>
+      </c>
+      <c r="D373">
+        <v>855</v>
+      </c>
+      <c r="E373">
+        <v>0.001005</v>
+      </c>
+      <c r="F373">
+        <v>0.1005</v>
+      </c>
+      <c r="G373">
+        <v>0.000195</v>
+      </c>
+      <c r="H373">
+        <v>0.0195</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" t="s">
+        <v>49</v>
+      </c>
+      <c r="B374" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C374">
+        <v>7</v>
+      </c>
+      <c r="D374">
+        <v>926.4286</v>
+      </c>
+      <c r="E374">
+        <v>0.000928</v>
+      </c>
+      <c r="F374">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="G374">
+        <v>0.000166</v>
+      </c>
+      <c r="H374">
+        <v>0.0166</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" t="s">
+        <v>51</v>
+      </c>
+      <c r="B375" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C375">
+        <v>7</v>
+      </c>
+      <c r="D375">
+        <v>1355</v>
+      </c>
+      <c r="E375">
+        <v>0.000634</v>
+      </c>
+      <c r="F375">
+        <v>0.0634</v>
+      </c>
+      <c r="G375">
+        <v>7.9E-05</v>
+      </c>
+      <c r="H375">
+        <v>0.007900000000000001</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" t="s">
+        <v>33</v>
+      </c>
+      <c r="B376" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C376">
+        <v>7</v>
+      </c>
+      <c r="D376">
+        <v>1569.2857</v>
+      </c>
+      <c r="E376">
+        <v>0.000548</v>
+      </c>
+      <c r="F376">
+        <v>0.0548</v>
+      </c>
+      <c r="G376">
+        <v>5.9E-05</v>
+      </c>
+      <c r="H376">
+        <v>0.0059</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" t="s">
+        <v>54</v>
+      </c>
+      <c r="B377" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C377">
+        <v>7</v>
+      </c>
+      <c r="D377">
+        <v>2001</v>
+      </c>
+      <c r="E377">
+        <v>0.00043</v>
+      </c>
+      <c r="F377">
+        <v>0.043</v>
+      </c>
+      <c r="G377">
+        <v>3.6E-05</v>
+      </c>
+      <c r="H377">
+        <v>0.0036</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" t="s">
+        <v>48</v>
+      </c>
+      <c r="B378" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C378">
+        <v>7</v>
+      </c>
+      <c r="D378">
+        <v>2140.7143</v>
+      </c>
+      <c r="E378">
+        <v>0.000402</v>
+      </c>
+      <c r="F378">
+        <v>0.0402</v>
+      </c>
+      <c r="G378">
+        <v>3.2E-05</v>
+      </c>
+      <c r="H378">
+        <v>0.0032</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" t="s">
+        <v>55</v>
+      </c>
+      <c r="B379" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" t="s">
+        <v>53</v>
+      </c>
+      <c r="B380" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" t="s">
+        <v>47</v>
+      </c>
+      <c r="B381" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" t="s">
+        <v>50</v>
+      </c>
+      <c r="B382" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" t="s">
+        <v>35</v>
+      </c>
+      <c r="B383" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
+      <c r="A384" t="s">
+        <v>43</v>
+      </c>
+      <c r="B384" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" t="s">
+        <v>25</v>
+      </c>
+      <c r="B385" s="2">
+        <v>46199</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -10296,12 +10296,1062 @@
         <v>46199</v>
       </c>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" spans="1:8">
       <c r="A385" t="s">
         <v>25</v>
       </c>
       <c r="B385" s="2">
         <v>46199</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" t="s">
+        <v>9</v>
+      </c>
+      <c r="B386" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C386">
+        <v>7</v>
+      </c>
+      <c r="D386">
+        <v>4.3374</v>
+      </c>
+      <c r="E386">
+        <v>0.197828</v>
+      </c>
+      <c r="F386">
+        <v>19.7828</v>
+      </c>
+      <c r="G386">
+        <v>0.210975</v>
+      </c>
+      <c r="H386">
+        <v>21.0975</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8">
+      <c r="A387" t="s">
+        <v>13</v>
+      </c>
+      <c r="B387" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C387">
+        <v>7</v>
+      </c>
+      <c r="D387">
+        <v>5.2029</v>
+      </c>
+      <c r="E387">
+        <v>0.164919</v>
+      </c>
+      <c r="F387">
+        <v>16.4919</v>
+      </c>
+      <c r="G387">
+        <v>0.175335</v>
+      </c>
+      <c r="H387">
+        <v>17.5335</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8">
+      <c r="A388" t="s">
+        <v>8</v>
+      </c>
+      <c r="B388" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C388">
+        <v>7</v>
+      </c>
+      <c r="D388">
+        <v>8.02</v>
+      </c>
+      <c r="E388">
+        <v>0.106989</v>
+      </c>
+      <c r="F388">
+        <v>10.6989</v>
+      </c>
+      <c r="G388">
+        <v>0.112605</v>
+      </c>
+      <c r="H388">
+        <v>11.2605</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" t="s">
+        <v>10</v>
+      </c>
+      <c r="B389" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C389">
+        <v>7</v>
+      </c>
+      <c r="D389">
+        <v>8.1914</v>
+      </c>
+      <c r="E389">
+        <v>0.10475</v>
+      </c>
+      <c r="F389">
+        <v>10.475</v>
+      </c>
+      <c r="G389">
+        <v>0.110181</v>
+      </c>
+      <c r="H389">
+        <v>11.0181</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" t="s">
+        <v>11</v>
+      </c>
+      <c r="B390" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C390">
+        <v>7</v>
+      </c>
+      <c r="D390">
+        <v>13.3857</v>
+      </c>
+      <c r="E390">
+        <v>0.06410200000000001</v>
+      </c>
+      <c r="F390">
+        <v>6.4102</v>
+      </c>
+      <c r="G390">
+        <v>0.06618499999999999</v>
+      </c>
+      <c r="H390">
+        <v>6.6185</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" t="s">
+        <v>12</v>
+      </c>
+      <c r="B391" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C391">
+        <v>7</v>
+      </c>
+      <c r="D391">
+        <v>13.8143</v>
+      </c>
+      <c r="E391">
+        <v>0.062113</v>
+      </c>
+      <c r="F391">
+        <v>6.2113</v>
+      </c>
+      <c r="G391">
+        <v>0.06403399999999999</v>
+      </c>
+      <c r="H391">
+        <v>6.4034</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" t="s">
+        <v>15</v>
+      </c>
+      <c r="B392" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C392">
+        <v>7</v>
+      </c>
+      <c r="D392">
+        <v>17.4286</v>
+      </c>
+      <c r="E392">
+        <v>0.049232</v>
+      </c>
+      <c r="F392">
+        <v>4.9232</v>
+      </c>
+      <c r="G392">
+        <v>0.050103</v>
+      </c>
+      <c r="H392">
+        <v>5.0103</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" t="s">
+        <v>14</v>
+      </c>
+      <c r="B393" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C393">
+        <v>7</v>
+      </c>
+      <c r="D393">
+        <v>21.1429</v>
+      </c>
+      <c r="E393">
+        <v>0.040583</v>
+      </c>
+      <c r="F393">
+        <v>4.0583</v>
+      </c>
+      <c r="G393">
+        <v>0.040757</v>
+      </c>
+      <c r="H393">
+        <v>4.0757</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" t="s">
+        <v>21</v>
+      </c>
+      <c r="B394" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C394">
+        <v>7</v>
+      </c>
+      <c r="D394">
+        <v>31</v>
+      </c>
+      <c r="E394">
+        <v>0.027679</v>
+      </c>
+      <c r="F394">
+        <v>2.7679</v>
+      </c>
+      <c r="G394">
+        <v>0.026838</v>
+      </c>
+      <c r="H394">
+        <v>2.6838</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" t="s">
+        <v>16</v>
+      </c>
+      <c r="B395" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C395">
+        <v>7</v>
+      </c>
+      <c r="D395">
+        <v>35.7143</v>
+      </c>
+      <c r="E395">
+        <v>0.024025</v>
+      </c>
+      <c r="F395">
+        <v>2.4025</v>
+      </c>
+      <c r="G395">
+        <v>0.022909</v>
+      </c>
+      <c r="H395">
+        <v>2.2909</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" t="s">
+        <v>18</v>
+      </c>
+      <c r="B396" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C396">
+        <v>7</v>
+      </c>
+      <c r="D396">
+        <v>37.2857</v>
+      </c>
+      <c r="E396">
+        <v>0.023013</v>
+      </c>
+      <c r="F396">
+        <v>2.3013</v>
+      </c>
+      <c r="G396">
+        <v>0.021821</v>
+      </c>
+      <c r="H396">
+        <v>2.1821</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8">
+      <c r="A397" t="s">
+        <v>17</v>
+      </c>
+      <c r="B397" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C397">
+        <v>7</v>
+      </c>
+      <c r="D397">
+        <v>49.1429</v>
+      </c>
+      <c r="E397">
+        <v>0.01746</v>
+      </c>
+      <c r="F397">
+        <v>1.746</v>
+      </c>
+      <c r="G397">
+        <v>0.015876</v>
+      </c>
+      <c r="H397">
+        <v>1.5876</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8">
+      <c r="A398" t="s">
+        <v>22</v>
+      </c>
+      <c r="B398" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C398">
+        <v>7</v>
+      </c>
+      <c r="D398">
+        <v>50.5714</v>
+      </c>
+      <c r="E398">
+        <v>0.016967</v>
+      </c>
+      <c r="F398">
+        <v>1.6967</v>
+      </c>
+      <c r="G398">
+        <v>0.01535</v>
+      </c>
+      <c r="H398">
+        <v>1.535</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8">
+      <c r="A399" t="s">
+        <v>19</v>
+      </c>
+      <c r="B399" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C399">
+        <v>7</v>
+      </c>
+      <c r="D399">
+        <v>51.2857</v>
+      </c>
+      <c r="E399">
+        <v>0.016731</v>
+      </c>
+      <c r="F399">
+        <v>1.6731</v>
+      </c>
+      <c r="G399">
+        <v>0.015099</v>
+      </c>
+      <c r="H399">
+        <v>1.5099</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8">
+      <c r="A400" t="s">
+        <v>20</v>
+      </c>
+      <c r="B400" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C400">
+        <v>7</v>
+      </c>
+      <c r="D400">
+        <v>58</v>
+      </c>
+      <c r="E400">
+        <v>0.014794</v>
+      </c>
+      <c r="F400">
+        <v>1.4794</v>
+      </c>
+      <c r="G400">
+        <v>0.01304</v>
+      </c>
+      <c r="H400">
+        <v>1.304</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8">
+      <c r="A401" t="s">
+        <v>24</v>
+      </c>
+      <c r="B401" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C401">
+        <v>7</v>
+      </c>
+      <c r="D401">
+        <v>73.71429999999999</v>
+      </c>
+      <c r="E401">
+        <v>0.01164</v>
+      </c>
+      <c r="F401">
+        <v>1.164</v>
+      </c>
+      <c r="G401">
+        <v>0.009714</v>
+      </c>
+      <c r="H401">
+        <v>0.9714</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8">
+      <c r="A402" t="s">
+        <v>28</v>
+      </c>
+      <c r="B402" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C402">
+        <v>7</v>
+      </c>
+      <c r="D402">
+        <v>120.2857</v>
+      </c>
+      <c r="E402">
+        <v>0.007133</v>
+      </c>
+      <c r="F402">
+        <v>0.7133</v>
+      </c>
+      <c r="G402">
+        <v>0.005086</v>
+      </c>
+      <c r="H402">
+        <v>0.5086000000000001</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8">
+      <c r="A403" t="s">
+        <v>27</v>
+      </c>
+      <c r="B403" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C403">
+        <v>7</v>
+      </c>
+      <c r="D403">
+        <v>127.4286</v>
+      </c>
+      <c r="E403">
+        <v>0.006734</v>
+      </c>
+      <c r="F403">
+        <v>0.6734</v>
+      </c>
+      <c r="G403">
+        <v>0.00469</v>
+      </c>
+      <c r="H403">
+        <v>0.469</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8">
+      <c r="A404" t="s">
+        <v>26</v>
+      </c>
+      <c r="B404" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C404">
+        <v>7</v>
+      </c>
+      <c r="D404">
+        <v>144.6429</v>
+      </c>
+      <c r="E404">
+        <v>0.005932</v>
+      </c>
+      <c r="F404">
+        <v>0.5931999999999999</v>
+      </c>
+      <c r="G404">
+        <v>0.003909</v>
+      </c>
+      <c r="H404">
+        <v>0.3909</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8">
+      <c r="A405" t="s">
+        <v>34</v>
+      </c>
+      <c r="B405" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C405">
+        <v>7</v>
+      </c>
+      <c r="D405">
+        <v>174.8571</v>
+      </c>
+      <c r="E405">
+        <v>0.004907</v>
+      </c>
+      <c r="F405">
+        <v>0.4907</v>
+      </c>
+      <c r="G405">
+        <v>0.002944</v>
+      </c>
+      <c r="H405">
+        <v>0.2944</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8">
+      <c r="A406" t="s">
+        <v>31</v>
+      </c>
+      <c r="B406" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C406">
+        <v>7</v>
+      </c>
+      <c r="D406">
+        <v>189.0714</v>
+      </c>
+      <c r="E406">
+        <v>0.004538</v>
+      </c>
+      <c r="F406">
+        <v>0.4538</v>
+      </c>
+      <c r="G406">
+        <v>0.002609</v>
+      </c>
+      <c r="H406">
+        <v>0.2609</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8">
+      <c r="A407" t="s">
+        <v>40</v>
+      </c>
+      <c r="B407" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C407">
+        <v>7</v>
+      </c>
+      <c r="D407">
+        <v>249.1429</v>
+      </c>
+      <c r="E407">
+        <v>0.003444</v>
+      </c>
+      <c r="F407">
+        <v>0.3444</v>
+      </c>
+      <c r="G407">
+        <v>0.001672</v>
+      </c>
+      <c r="H407">
+        <v>0.1672</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8">
+      <c r="A408" t="s">
+        <v>29</v>
+      </c>
+      <c r="B408" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C408">
+        <v>7</v>
+      </c>
+      <c r="D408">
+        <v>260.7143</v>
+      </c>
+      <c r="E408">
+        <v>0.003291</v>
+      </c>
+      <c r="F408">
+        <v>0.3291</v>
+      </c>
+      <c r="G408">
+        <v>0.00155</v>
+      </c>
+      <c r="H408">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8">
+      <c r="A409" t="s">
+        <v>30</v>
+      </c>
+      <c r="B409" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C409">
+        <v>7</v>
+      </c>
+      <c r="D409">
+        <v>272.2857</v>
+      </c>
+      <c r="E409">
+        <v>0.003151</v>
+      </c>
+      <c r="F409">
+        <v>0.3151</v>
+      </c>
+      <c r="G409">
+        <v>0.00144</v>
+      </c>
+      <c r="H409">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8">
+      <c r="A410" t="s">
+        <v>36</v>
+      </c>
+      <c r="B410" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C410">
+        <v>7</v>
+      </c>
+      <c r="D410">
+        <v>273.5714</v>
+      </c>
+      <c r="E410">
+        <v>0.003136</v>
+      </c>
+      <c r="F410">
+        <v>0.3136</v>
+      </c>
+      <c r="G410">
+        <v>0.001428</v>
+      </c>
+      <c r="H410">
+        <v>0.1428</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8">
+      <c r="A411" t="s">
+        <v>41</v>
+      </c>
+      <c r="B411" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C411">
+        <v>7</v>
+      </c>
+      <c r="D411">
+        <v>373.7143</v>
+      </c>
+      <c r="E411">
+        <v>0.002296</v>
+      </c>
+      <c r="F411">
+        <v>0.2296</v>
+      </c>
+      <c r="G411">
+        <v>0.000827</v>
+      </c>
+      <c r="H411">
+        <v>0.0827</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8">
+      <c r="A412" t="s">
+        <v>32</v>
+      </c>
+      <c r="B412" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C412">
+        <v>7</v>
+      </c>
+      <c r="D412">
+        <v>448.1429</v>
+      </c>
+      <c r="E412">
+        <v>0.001915</v>
+      </c>
+      <c r="F412">
+        <v>0.1915</v>
+      </c>
+      <c r="G412">
+        <v>0.000594</v>
+      </c>
+      <c r="H412">
+        <v>0.0594</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8">
+      <c r="A413" t="s">
+        <v>37</v>
+      </c>
+      <c r="B413" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C413">
+        <v>7</v>
+      </c>
+      <c r="D413">
+        <v>458.7143</v>
+      </c>
+      <c r="E413">
+        <v>0.001871</v>
+      </c>
+      <c r="F413">
+        <v>0.1871</v>
+      </c>
+      <c r="G413">
+        <v>0.000569</v>
+      </c>
+      <c r="H413">
+        <v>0.0569</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8">
+      <c r="A414" t="s">
+        <v>38</v>
+      </c>
+      <c r="B414" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C414">
+        <v>7</v>
+      </c>
+      <c r="D414">
+        <v>503.7143</v>
+      </c>
+      <c r="E414">
+        <v>0.001703</v>
+      </c>
+      <c r="F414">
+        <v>0.1703</v>
+      </c>
+      <c r="G414">
+        <v>0.000478</v>
+      </c>
+      <c r="H414">
+        <v>0.0478</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8">
+      <c r="A415" t="s">
+        <v>52</v>
+      </c>
+      <c r="B415" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C415">
+        <v>7</v>
+      </c>
+      <c r="D415">
+        <v>526.4286</v>
+      </c>
+      <c r="E415">
+        <v>0.00163</v>
+      </c>
+      <c r="F415">
+        <v>0.163</v>
+      </c>
+      <c r="G415">
+        <v>0.00044</v>
+      </c>
+      <c r="H415">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8">
+      <c r="A416" t="s">
+        <v>44</v>
+      </c>
+      <c r="B416" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C416">
+        <v>7</v>
+      </c>
+      <c r="D416">
+        <v>612.1429000000001</v>
+      </c>
+      <c r="E416">
+        <v>0.001402</v>
+      </c>
+      <c r="F416">
+        <v>0.1402</v>
+      </c>
+      <c r="G416">
+        <v>0.00033</v>
+      </c>
+      <c r="H416">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8">
+      <c r="A417" t="s">
+        <v>46</v>
+      </c>
+      <c r="B417" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C417">
+        <v>7</v>
+      </c>
+      <c r="D417">
+        <v>630</v>
+      </c>
+      <c r="E417">
+        <v>0.001362</v>
+      </c>
+      <c r="F417">
+        <v>0.1362</v>
+      </c>
+      <c r="G417">
+        <v>0.000313</v>
+      </c>
+      <c r="H417">
+        <v>0.0313</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8">
+      <c r="A418" t="s">
+        <v>39</v>
+      </c>
+      <c r="B418" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C418">
+        <v>7</v>
+      </c>
+      <c r="D418">
+        <v>964</v>
+      </c>
+      <c r="E418">
+        <v>0.0008899999999999999</v>
+      </c>
+      <c r="F418">
+        <v>0.089</v>
+      </c>
+      <c r="G418">
+        <v>0.000137</v>
+      </c>
+      <c r="H418">
+        <v>0.0137</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8">
+      <c r="A419" t="s">
+        <v>42</v>
+      </c>
+      <c r="B419" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C419">
+        <v>7</v>
+      </c>
+      <c r="D419">
+        <v>1219.2857</v>
+      </c>
+      <c r="E419">
+        <v>0.000704</v>
+      </c>
+      <c r="F419">
+        <v>0.0704</v>
+      </c>
+      <c r="G419">
+        <v>8.6E-05</v>
+      </c>
+      <c r="H419">
+        <v>0.0086</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8">
+      <c r="A420" t="s">
+        <v>48</v>
+      </c>
+      <c r="B420" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C420">
+        <v>7</v>
+      </c>
+      <c r="D420">
+        <v>2001</v>
+      </c>
+      <c r="E420">
+        <v>0.000429</v>
+      </c>
+      <c r="F420">
+        <v>0.0429</v>
+      </c>
+      <c r="G420">
+        <v>3.2E-05</v>
+      </c>
+      <c r="H420">
+        <v>0.0032</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8">
+      <c r="A421" t="s">
+        <v>51</v>
+      </c>
+      <c r="B421" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C421">
+        <v>7</v>
+      </c>
+      <c r="D421">
+        <v>2330.6667</v>
+      </c>
+      <c r="E421">
+        <v>0.000368</v>
+      </c>
+      <c r="F421">
+        <v>0.0368</v>
+      </c>
+      <c r="G421">
+        <v>2.4E-05</v>
+      </c>
+      <c r="H421">
+        <v>0.0024</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8">
+      <c r="A422" t="s">
+        <v>33</v>
+      </c>
+      <c r="B422" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C422">
+        <v>7</v>
+      </c>
+      <c r="D422">
+        <v>2539</v>
+      </c>
+      <c r="E422">
+        <v>0.000338</v>
+      </c>
+      <c r="F422">
+        <v>0.0338</v>
+      </c>
+      <c r="G422">
+        <v>2E-05</v>
+      </c>
+      <c r="H422">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8">
+      <c r="A423" t="s">
+        <v>54</v>
+      </c>
+      <c r="B423" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8">
+      <c r="A424" t="s">
+        <v>55</v>
+      </c>
+      <c r="B424" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8">
+      <c r="A425" t="s">
+        <v>53</v>
+      </c>
+      <c r="B425" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8">
+      <c r="A426" t="s">
+        <v>47</v>
+      </c>
+      <c r="B426" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8">
+      <c r="A427" t="s">
+        <v>49</v>
+      </c>
+      <c r="B427" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8">
+      <c r="A428" t="s">
+        <v>50</v>
+      </c>
+      <c r="B428" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8">
+      <c r="A429" t="s">
+        <v>45</v>
+      </c>
+      <c r="B429" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8">
+      <c r="A430" t="s">
+        <v>35</v>
+      </c>
+      <c r="B430" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8">
+      <c r="A431" t="s">
+        <v>43</v>
+      </c>
+      <c r="B431" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8">
+      <c r="A432" t="s">
+        <v>25</v>
+      </c>
+      <c r="B432" s="2">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" t="s">
+        <v>23</v>
+      </c>
+      <c r="B433" s="2">
+        <v>46201</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -11346,12 +11346,954 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="433" spans="1:2">
+    <row r="433" spans="1:8">
       <c r="A433" t="s">
         <v>23</v>
       </c>
       <c r="B433" s="2">
         <v>46201</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8">
+      <c r="A434" t="s">
+        <v>9</v>
+      </c>
+      <c r="B434" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C434">
+        <v>7</v>
+      </c>
+      <c r="D434">
+        <v>3.62</v>
+      </c>
+      <c r="E434">
+        <v>0.223354</v>
+      </c>
+      <c r="F434">
+        <v>22.3354</v>
+      </c>
+      <c r="G434">
+        <v>0.244072</v>
+      </c>
+      <c r="H434">
+        <v>24.4072</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8">
+      <c r="A435" t="s">
+        <v>13</v>
+      </c>
+      <c r="B435" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C435">
+        <v>7</v>
+      </c>
+      <c r="D435">
+        <v>4.8386</v>
+      </c>
+      <c r="E435">
+        <v>0.167103</v>
+      </c>
+      <c r="F435">
+        <v>16.7103</v>
+      </c>
+      <c r="G435">
+        <v>0.181173</v>
+      </c>
+      <c r="H435">
+        <v>18.1173</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8">
+      <c r="A436" t="s">
+        <v>8</v>
+      </c>
+      <c r="B436" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C436">
+        <v>7</v>
+      </c>
+      <c r="D436">
+        <v>8.1357</v>
+      </c>
+      <c r="E436">
+        <v>0.099382</v>
+      </c>
+      <c r="F436">
+        <v>9.9382</v>
+      </c>
+      <c r="G436">
+        <v>0.105483</v>
+      </c>
+      <c r="H436">
+        <v>10.5483</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8">
+      <c r="A437" t="s">
+        <v>10</v>
+      </c>
+      <c r="B437" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C437">
+        <v>7</v>
+      </c>
+      <c r="D437">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E437">
+        <v>0.09836300000000001</v>
+      </c>
+      <c r="F437">
+        <v>9.8363</v>
+      </c>
+      <c r="G437">
+        <v>0.104345</v>
+      </c>
+      <c r="H437">
+        <v>10.4345</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8">
+      <c r="A438" t="s">
+        <v>12</v>
+      </c>
+      <c r="B438" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C438">
+        <v>7</v>
+      </c>
+      <c r="D438">
+        <v>11.4714</v>
+      </c>
+      <c r="E438">
+        <v>0.070483</v>
+      </c>
+      <c r="F438">
+        <v>7.0483</v>
+      </c>
+      <c r="G438">
+        <v>0.07321999999999999</v>
+      </c>
+      <c r="H438">
+        <v>7.322</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8">
+      <c r="A439" t="s">
+        <v>11</v>
+      </c>
+      <c r="B439" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C439">
+        <v>7</v>
+      </c>
+      <c r="D439">
+        <v>13.6</v>
+      </c>
+      <c r="E439">
+        <v>0.059452</v>
+      </c>
+      <c r="F439">
+        <v>5.9452</v>
+      </c>
+      <c r="G439">
+        <v>0.06092</v>
+      </c>
+      <c r="H439">
+        <v>6.092</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8">
+      <c r="A440" t="s">
+        <v>15</v>
+      </c>
+      <c r="B440" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C440">
+        <v>7</v>
+      </c>
+      <c r="D440">
+        <v>17</v>
+      </c>
+      <c r="E440">
+        <v>0.047561</v>
+      </c>
+      <c r="F440">
+        <v>4.7561</v>
+      </c>
+      <c r="G440">
+        <v>0.047683</v>
+      </c>
+      <c r="H440">
+        <v>4.7683</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8">
+      <c r="A441" t="s">
+        <v>19</v>
+      </c>
+      <c r="B441" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C441">
+        <v>7</v>
+      </c>
+      <c r="D441">
+        <v>21.5714</v>
+      </c>
+      <c r="E441">
+        <v>0.037482</v>
+      </c>
+      <c r="F441">
+        <v>3.7482</v>
+      </c>
+      <c r="G441">
+        <v>0.036494</v>
+      </c>
+      <c r="H441">
+        <v>3.6494</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8">
+      <c r="A442" t="s">
+        <v>14</v>
+      </c>
+      <c r="B442" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C442">
+        <v>7</v>
+      </c>
+      <c r="D442">
+        <v>26</v>
+      </c>
+      <c r="E442">
+        <v>0.031098</v>
+      </c>
+      <c r="F442">
+        <v>3.1098</v>
+      </c>
+      <c r="G442">
+        <v>0.029435</v>
+      </c>
+      <c r="H442">
+        <v>2.9435</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8">
+      <c r="A443" t="s">
+        <v>18</v>
+      </c>
+      <c r="B443" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C443">
+        <v>7</v>
+      </c>
+      <c r="D443">
+        <v>31.8571</v>
+      </c>
+      <c r="E443">
+        <v>0.02538</v>
+      </c>
+      <c r="F443">
+        <v>2.538</v>
+      </c>
+      <c r="G443">
+        <v>0.023147</v>
+      </c>
+      <c r="H443">
+        <v>2.3147</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8">
+      <c r="A444" t="s">
+        <v>21</v>
+      </c>
+      <c r="B444" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C444">
+        <v>7</v>
+      </c>
+      <c r="D444">
+        <v>32.5714</v>
+      </c>
+      <c r="E444">
+        <v>0.024824</v>
+      </c>
+      <c r="F444">
+        <v>2.4824</v>
+      </c>
+      <c r="G444">
+        <v>0.022537</v>
+      </c>
+      <c r="H444">
+        <v>2.2537</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8">
+      <c r="A445" t="s">
+        <v>16</v>
+      </c>
+      <c r="B445" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C445">
+        <v>7</v>
+      </c>
+      <c r="D445">
+        <v>37.7143</v>
+      </c>
+      <c r="E445">
+        <v>0.021439</v>
+      </c>
+      <c r="F445">
+        <v>2.1439</v>
+      </c>
+      <c r="G445">
+        <v>0.018844</v>
+      </c>
+      <c r="H445">
+        <v>1.8844</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8">
+      <c r="A446" t="s">
+        <v>22</v>
+      </c>
+      <c r="B446" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C446">
+        <v>7</v>
+      </c>
+      <c r="D446">
+        <v>50.2857</v>
+      </c>
+      <c r="E446">
+        <v>0.016079</v>
+      </c>
+      <c r="F446">
+        <v>1.6079</v>
+      </c>
+      <c r="G446">
+        <v>0.013072</v>
+      </c>
+      <c r="H446">
+        <v>1.3072</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8">
+      <c r="A447" t="s">
+        <v>17</v>
+      </c>
+      <c r="B447" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C447">
+        <v>7</v>
+      </c>
+      <c r="D447">
+        <v>52</v>
+      </c>
+      <c r="E447">
+        <v>0.015549</v>
+      </c>
+      <c r="F447">
+        <v>1.5549</v>
+      </c>
+      <c r="G447">
+        <v>0.012509</v>
+      </c>
+      <c r="H447">
+        <v>1.2509</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8">
+      <c r="A448" t="s">
+        <v>24</v>
+      </c>
+      <c r="B448" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C448">
+        <v>7</v>
+      </c>
+      <c r="D448">
+        <v>78.71429999999999</v>
+      </c>
+      <c r="E448">
+        <v>0.010272</v>
+      </c>
+      <c r="F448">
+        <v>1.0272</v>
+      </c>
+      <c r="G448">
+        <v>0.00705</v>
+      </c>
+      <c r="H448">
+        <v>0.705</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8">
+      <c r="A449" t="s">
+        <v>28</v>
+      </c>
+      <c r="B449" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C449">
+        <v>7</v>
+      </c>
+      <c r="D449">
+        <v>121.7143</v>
+      </c>
+      <c r="E449">
+        <v>0.006643</v>
+      </c>
+      <c r="F449">
+        <v>0.6643</v>
+      </c>
+      <c r="G449">
+        <v>0.003612</v>
+      </c>
+      <c r="H449">
+        <v>0.3612</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8">
+      <c r="A450" t="s">
+        <v>27</v>
+      </c>
+      <c r="B450" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C450">
+        <v>7</v>
+      </c>
+      <c r="D450">
+        <v>129.5714</v>
+      </c>
+      <c r="E450">
+        <v>0.00624</v>
+      </c>
+      <c r="F450">
+        <v>0.624</v>
+      </c>
+      <c r="G450">
+        <v>0.003262</v>
+      </c>
+      <c r="H450">
+        <v>0.3262</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8">
+      <c r="A451" t="s">
+        <v>26</v>
+      </c>
+      <c r="B451" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C451">
+        <v>7</v>
+      </c>
+      <c r="D451">
+        <v>146.0714</v>
+      </c>
+      <c r="E451">
+        <v>0.005535</v>
+      </c>
+      <c r="F451">
+        <v>0.5535</v>
+      </c>
+      <c r="G451">
+        <v>0.002672</v>
+      </c>
+      <c r="H451">
+        <v>0.2672</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8">
+      <c r="A452" t="s">
+        <v>31</v>
+      </c>
+      <c r="B452" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C452">
+        <v>7</v>
+      </c>
+      <c r="D452">
+        <v>165.3571</v>
+      </c>
+      <c r="E452">
+        <v>0.00489</v>
+      </c>
+      <c r="F452">
+        <v>0.489</v>
+      </c>
+      <c r="G452">
+        <v>0.002162</v>
+      </c>
+      <c r="H452">
+        <v>0.2162</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8">
+      <c r="A453" t="s">
+        <v>34</v>
+      </c>
+      <c r="B453" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C453">
+        <v>7</v>
+      </c>
+      <c r="D453">
+        <v>179.2857</v>
+      </c>
+      <c r="E453">
+        <v>0.00451</v>
+      </c>
+      <c r="F453">
+        <v>0.451</v>
+      </c>
+      <c r="G453">
+        <v>0.001878</v>
+      </c>
+      <c r="H453">
+        <v>0.1878</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8">
+      <c r="A454" t="s">
+        <v>32</v>
+      </c>
+      <c r="B454" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C454">
+        <v>7</v>
+      </c>
+      <c r="D454">
+        <v>212.5714</v>
+      </c>
+      <c r="E454">
+        <v>0.003804</v>
+      </c>
+      <c r="F454">
+        <v>0.3804</v>
+      </c>
+      <c r="G454">
+        <v>0.001386</v>
+      </c>
+      <c r="H454">
+        <v>0.1386</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8">
+      <c r="A455" t="s">
+        <v>29</v>
+      </c>
+      <c r="B455" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C455">
+        <v>7</v>
+      </c>
+      <c r="D455">
+        <v>229.7143</v>
+      </c>
+      <c r="E455">
+        <v>0.00352</v>
+      </c>
+      <c r="F455">
+        <v>0.352</v>
+      </c>
+      <c r="G455">
+        <v>0.001204</v>
+      </c>
+      <c r="H455">
+        <v>0.1204</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8">
+      <c r="A456" t="s">
+        <v>30</v>
+      </c>
+      <c r="B456" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C456">
+        <v>7</v>
+      </c>
+      <c r="D456">
+        <v>284.8571</v>
+      </c>
+      <c r="E456">
+        <v>0.002838</v>
+      </c>
+      <c r="F456">
+        <v>0.2838</v>
+      </c>
+      <c r="G456">
+        <v>0.000808</v>
+      </c>
+      <c r="H456">
+        <v>0.0808</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8">
+      <c r="A457" t="s">
+        <v>36</v>
+      </c>
+      <c r="B457" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C457">
+        <v>7</v>
+      </c>
+      <c r="D457">
+        <v>287.8571</v>
+      </c>
+      <c r="E457">
+        <v>0.002809</v>
+      </c>
+      <c r="F457">
+        <v>0.2809</v>
+      </c>
+      <c r="G457">
+        <v>0.000792</v>
+      </c>
+      <c r="H457">
+        <v>0.07920000000000001</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8">
+      <c r="A458" t="s">
+        <v>40</v>
+      </c>
+      <c r="B458" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C458">
+        <v>7</v>
+      </c>
+      <c r="D458">
+        <v>290.5714</v>
+      </c>
+      <c r="E458">
+        <v>0.002783</v>
+      </c>
+      <c r="F458">
+        <v>0.2783</v>
+      </c>
+      <c r="G458">
+        <v>0.000778</v>
+      </c>
+      <c r="H458">
+        <v>0.07779999999999999</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8">
+      <c r="A459" t="s">
+        <v>37</v>
+      </c>
+      <c r="B459" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C459">
+        <v>7</v>
+      </c>
+      <c r="D459">
+        <v>391.2857</v>
+      </c>
+      <c r="E459">
+        <v>0.002066</v>
+      </c>
+      <c r="F459">
+        <v>0.2066</v>
+      </c>
+      <c r="G459">
+        <v>0.000441</v>
+      </c>
+      <c r="H459">
+        <v>0.0441</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8">
+      <c r="A460" t="s">
+        <v>41</v>
+      </c>
+      <c r="B460" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C460">
+        <v>7</v>
+      </c>
+      <c r="D460">
+        <v>429.4286</v>
+      </c>
+      <c r="E460">
+        <v>0.001883</v>
+      </c>
+      <c r="F460">
+        <v>0.1883</v>
+      </c>
+      <c r="G460">
+        <v>0.000368</v>
+      </c>
+      <c r="H460">
+        <v>0.0368</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8">
+      <c r="A461" t="s">
+        <v>44</v>
+      </c>
+      <c r="B461" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C461">
+        <v>7</v>
+      </c>
+      <c r="D461">
+        <v>551</v>
+      </c>
+      <c r="E461">
+        <v>0.001467</v>
+      </c>
+      <c r="F461">
+        <v>0.1467</v>
+      </c>
+      <c r="G461">
+        <v>0.000226</v>
+      </c>
+      <c r="H461">
+        <v>0.0226</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8">
+      <c r="A462" t="s">
+        <v>38</v>
+      </c>
+      <c r="B462" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C462">
+        <v>7</v>
+      </c>
+      <c r="D462">
+        <v>576.4286</v>
+      </c>
+      <c r="E462">
+        <v>0.001403</v>
+      </c>
+      <c r="F462">
+        <v>0.1403</v>
+      </c>
+      <c r="G462">
+        <v>0.000207</v>
+      </c>
+      <c r="H462">
+        <v>0.0207</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8">
+      <c r="A463" t="s">
+        <v>52</v>
+      </c>
+      <c r="B463" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C463">
+        <v>7</v>
+      </c>
+      <c r="D463">
+        <v>583.5714</v>
+      </c>
+      <c r="E463">
+        <v>0.001386</v>
+      </c>
+      <c r="F463">
+        <v>0.1386</v>
+      </c>
+      <c r="G463">
+        <v>0.000202</v>
+      </c>
+      <c r="H463">
+        <v>0.0202</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8">
+      <c r="A464" t="s">
+        <v>48</v>
+      </c>
+      <c r="B464" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C464">
+        <v>7</v>
+      </c>
+      <c r="D464">
+        <v>2001</v>
+      </c>
+      <c r="E464">
+        <v>0.000404</v>
+      </c>
+      <c r="F464">
+        <v>0.0404</v>
+      </c>
+      <c r="G464">
+        <v>1.7E-05</v>
+      </c>
+      <c r="H464">
+        <v>0.0017</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" t="s">
+        <v>54</v>
+      </c>
+      <c r="B465" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" t="s">
+        <v>55</v>
+      </c>
+      <c r="B466" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" t="s">
+        <v>42</v>
+      </c>
+      <c r="B467" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" t="s">
+        <v>20</v>
+      </c>
+      <c r="B468" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" t="s">
+        <v>53</v>
+      </c>
+      <c r="B469" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" t="s">
+        <v>47</v>
+      </c>
+      <c r="B470" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" t="s">
+        <v>49</v>
+      </c>
+      <c r="B471" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" t="s">
+        <v>50</v>
+      </c>
+      <c r="B472" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" t="s">
+        <v>45</v>
+      </c>
+      <c r="B473" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" t="s">
+        <v>33</v>
+      </c>
+      <c r="B474" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" t="s">
+        <v>46</v>
+      </c>
+      <c r="B475" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" t="s">
+        <v>39</v>
+      </c>
+      <c r="B476" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" t="s">
+        <v>35</v>
+      </c>
+      <c r="B477" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" t="s">
+        <v>43</v>
+      </c>
+      <c r="B478" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" t="s">
+        <v>25</v>
+      </c>
+      <c r="B479" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" t="s">
+        <v>23</v>
+      </c>
+      <c r="B480" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" t="s">
+        <v>51</v>
+      </c>
+      <c r="B481" s="2">
+        <v>46203</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H481"/>
+  <dimension ref="A1:H529"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -12288,12 +12288,792 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="481" spans="1:2">
+    <row r="481" spans="1:8">
       <c r="A481" t="s">
         <v>51</v>
       </c>
       <c r="B481" s="2">
         <v>46203</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8">
+      <c r="A482" t="s">
+        <v>9</v>
+      </c>
+      <c r="B482" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C482">
+        <v>6</v>
+      </c>
+      <c r="D482">
+        <v>2.8562</v>
+      </c>
+      <c r="E482">
+        <v>0.306719</v>
+      </c>
+      <c r="F482">
+        <v>30.6719</v>
+      </c>
+      <c r="G482">
+        <v>0.324692</v>
+      </c>
+      <c r="H482">
+        <v>32.4692</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8">
+      <c r="A483" t="s">
+        <v>13</v>
+      </c>
+      <c r="B483" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C483">
+        <v>6</v>
+      </c>
+      <c r="D483">
+        <v>5.11</v>
+      </c>
+      <c r="E483">
+        <v>0.171442</v>
+      </c>
+      <c r="F483">
+        <v>17.1442</v>
+      </c>
+      <c r="G483">
+        <v>0.179536</v>
+      </c>
+      <c r="H483">
+        <v>17.9536</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8">
+      <c r="A484" t="s">
+        <v>8</v>
+      </c>
+      <c r="B484" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C484">
+        <v>6</v>
+      </c>
+      <c r="D484">
+        <v>8.59</v>
+      </c>
+      <c r="E484">
+        <v>0.101987</v>
+      </c>
+      <c r="F484">
+        <v>10.1987</v>
+      </c>
+      <c r="G484">
+        <v>0.105035</v>
+      </c>
+      <c r="H484">
+        <v>10.5035</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8">
+      <c r="A485" t="s">
+        <v>10</v>
+      </c>
+      <c r="B485" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C485">
+        <v>6</v>
+      </c>
+      <c r="D485">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E485">
+        <v>0.089395</v>
+      </c>
+      <c r="F485">
+        <v>8.939500000000001</v>
+      </c>
+      <c r="G485">
+        <v>0.091534</v>
+      </c>
+      <c r="H485">
+        <v>9.1534</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8">
+      <c r="A486" t="s">
+        <v>12</v>
+      </c>
+      <c r="B486" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C486">
+        <v>6</v>
+      </c>
+      <c r="D486">
+        <v>12.2833</v>
+      </c>
+      <c r="E486">
+        <v>0.071322</v>
+      </c>
+      <c r="F486">
+        <v>7.1322</v>
+      </c>
+      <c r="G486">
+        <v>0.07216500000000001</v>
+      </c>
+      <c r="H486">
+        <v>7.2165</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8">
+      <c r="A487" t="s">
+        <v>11</v>
+      </c>
+      <c r="B487" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C487">
+        <v>6</v>
+      </c>
+      <c r="D487">
+        <v>15.5167</v>
+      </c>
+      <c r="E487">
+        <v>0.05646</v>
+      </c>
+      <c r="F487">
+        <v>5.646</v>
+      </c>
+      <c r="G487">
+        <v>0.05625</v>
+      </c>
+      <c r="H487">
+        <v>5.625</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8">
+      <c r="A488" t="s">
+        <v>19</v>
+      </c>
+      <c r="B488" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C488">
+        <v>6</v>
+      </c>
+      <c r="D488">
+        <v>27.3333</v>
+      </c>
+      <c r="E488">
+        <v>0.032051</v>
+      </c>
+      <c r="F488">
+        <v>3.2051</v>
+      </c>
+      <c r="G488">
+        <v>0.030182</v>
+      </c>
+      <c r="H488">
+        <v>3.0182</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8">
+      <c r="A489" t="s">
+        <v>22</v>
+      </c>
+      <c r="B489" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C489">
+        <v>6</v>
+      </c>
+      <c r="D489">
+        <v>28.3333</v>
+      </c>
+      <c r="E489">
+        <v>0.03092</v>
+      </c>
+      <c r="F489">
+        <v>3.092</v>
+      </c>
+      <c r="G489">
+        <v>0.028978</v>
+      </c>
+      <c r="H489">
+        <v>2.8978</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8">
+      <c r="A490" t="s">
+        <v>21</v>
+      </c>
+      <c r="B490" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C490">
+        <v>6</v>
+      </c>
+      <c r="D490">
+        <v>29.1667</v>
+      </c>
+      <c r="E490">
+        <v>0.030037</v>
+      </c>
+      <c r="F490">
+        <v>3.0037</v>
+      </c>
+      <c r="G490">
+        <v>0.028039</v>
+      </c>
+      <c r="H490">
+        <v>2.8039</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8">
+      <c r="A491" t="s">
+        <v>18</v>
+      </c>
+      <c r="B491" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C491">
+        <v>6</v>
+      </c>
+      <c r="D491">
+        <v>29.3333</v>
+      </c>
+      <c r="E491">
+        <v>0.029866</v>
+      </c>
+      <c r="F491">
+        <v>2.9866</v>
+      </c>
+      <c r="G491">
+        <v>0.027858</v>
+      </c>
+      <c r="H491">
+        <v>2.7858</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8">
+      <c r="A492" t="s">
+        <v>16</v>
+      </c>
+      <c r="B492" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C492">
+        <v>6</v>
+      </c>
+      <c r="D492">
+        <v>37</v>
+      </c>
+      <c r="E492">
+        <v>0.023677</v>
+      </c>
+      <c r="F492">
+        <v>2.3677</v>
+      </c>
+      <c r="G492">
+        <v>0.021298</v>
+      </c>
+      <c r="H492">
+        <v>2.1298</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8">
+      <c r="A493" t="s">
+        <v>17</v>
+      </c>
+      <c r="B493" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C493">
+        <v>6</v>
+      </c>
+      <c r="D493">
+        <v>41.8333</v>
+      </c>
+      <c r="E493">
+        <v>0.020942</v>
+      </c>
+      <c r="F493">
+        <v>2.0942</v>
+      </c>
+      <c r="G493">
+        <v>0.018413</v>
+      </c>
+      <c r="H493">
+        <v>1.8413</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8">
+      <c r="A494" t="s">
+        <v>24</v>
+      </c>
+      <c r="B494" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C494">
+        <v>6</v>
+      </c>
+      <c r="D494">
+        <v>86.33329999999999</v>
+      </c>
+      <c r="E494">
+        <v>0.010147</v>
+      </c>
+      <c r="F494">
+        <v>1.0147</v>
+      </c>
+      <c r="G494">
+        <v>0.007277</v>
+      </c>
+      <c r="H494">
+        <v>0.7277</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8">
+      <c r="A495" t="s">
+        <v>26</v>
+      </c>
+      <c r="B495" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C495">
+        <v>6</v>
+      </c>
+      <c r="D495">
+        <v>173</v>
+      </c>
+      <c r="E495">
+        <v>0.005064</v>
+      </c>
+      <c r="F495">
+        <v>0.5064</v>
+      </c>
+      <c r="G495">
+        <v>0.002552</v>
+      </c>
+      <c r="H495">
+        <v>0.2552</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8">
+      <c r="A496" t="s">
+        <v>31</v>
+      </c>
+      <c r="B496" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C496">
+        <v>6</v>
+      </c>
+      <c r="D496">
+        <v>238.3333</v>
+      </c>
+      <c r="E496">
+        <v>0.003676</v>
+      </c>
+      <c r="F496">
+        <v>0.3676</v>
+      </c>
+      <c r="G496">
+        <v>0.001482</v>
+      </c>
+      <c r="H496">
+        <v>0.1482</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8">
+      <c r="A497" t="s">
+        <v>36</v>
+      </c>
+      <c r="B497" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C497">
+        <v>6</v>
+      </c>
+      <c r="D497">
+        <v>300.5</v>
+      </c>
+      <c r="E497">
+        <v>0.002915</v>
+      </c>
+      <c r="F497">
+        <v>0.2915</v>
+      </c>
+      <c r="G497">
+        <v>0.0009790000000000001</v>
+      </c>
+      <c r="H497">
+        <v>0.0979</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8">
+      <c r="A498" t="s">
+        <v>32</v>
+      </c>
+      <c r="B498" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C498">
+        <v>6</v>
+      </c>
+      <c r="D498">
+        <v>302.1667</v>
+      </c>
+      <c r="E498">
+        <v>0.002899</v>
+      </c>
+      <c r="F498">
+        <v>0.2899</v>
+      </c>
+      <c r="G498">
+        <v>0.000969</v>
+      </c>
+      <c r="H498">
+        <v>0.0969</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8">
+      <c r="A499" t="s">
+        <v>40</v>
+      </c>
+      <c r="B499" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C499">
+        <v>6</v>
+      </c>
+      <c r="D499">
+        <v>333.6667</v>
+      </c>
+      <c r="E499">
+        <v>0.002626</v>
+      </c>
+      <c r="F499">
+        <v>0.2626</v>
+      </c>
+      <c r="G499">
+        <v>0.000808</v>
+      </c>
+      <c r="H499">
+        <v>0.0808</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8">
+      <c r="A500" t="s">
+        <v>30</v>
+      </c>
+      <c r="B500" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C500">
+        <v>6</v>
+      </c>
+      <c r="D500">
+        <v>333.6667</v>
+      </c>
+      <c r="E500">
+        <v>0.002626</v>
+      </c>
+      <c r="F500">
+        <v>0.2626</v>
+      </c>
+      <c r="G500">
+        <v>0.000808</v>
+      </c>
+      <c r="H500">
+        <v>0.0808</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8">
+      <c r="A501" t="s">
+        <v>37</v>
+      </c>
+      <c r="B501" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C501">
+        <v>6</v>
+      </c>
+      <c r="D501">
+        <v>437.8333</v>
+      </c>
+      <c r="E501">
+        <v>0.002001</v>
+      </c>
+      <c r="F501">
+        <v>0.2001</v>
+      </c>
+      <c r="G501">
+        <v>0.000485</v>
+      </c>
+      <c r="H501">
+        <v>0.0485</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8">
+      <c r="A502" t="s">
+        <v>41</v>
+      </c>
+      <c r="B502" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C502">
+        <v>6</v>
+      </c>
+      <c r="D502">
+        <v>458.5</v>
+      </c>
+      <c r="E502">
+        <v>0.001911</v>
+      </c>
+      <c r="F502">
+        <v>0.1911</v>
+      </c>
+      <c r="G502">
+        <v>0.000444</v>
+      </c>
+      <c r="H502">
+        <v>0.0444</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8">
+      <c r="A503" t="s">
+        <v>52</v>
+      </c>
+      <c r="B503" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C503">
+        <v>6</v>
+      </c>
+      <c r="D503">
+        <v>664</v>
+      </c>
+      <c r="E503">
+        <v>0.001319</v>
+      </c>
+      <c r="F503">
+        <v>0.1319</v>
+      </c>
+      <c r="G503">
+        <v>0.000217</v>
+      </c>
+      <c r="H503">
+        <v>0.0217</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8">
+      <c r="A504" t="s">
+        <v>38</v>
+      </c>
+      <c r="B504" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8">
+      <c r="A505" t="s">
+        <v>54</v>
+      </c>
+      <c r="B505" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8">
+      <c r="A506" t="s">
+        <v>44</v>
+      </c>
+      <c r="B506" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8">
+      <c r="A507" t="s">
+        <v>14</v>
+      </c>
+      <c r="B507" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8">
+      <c r="A508" t="s">
+        <v>27</v>
+      </c>
+      <c r="B508" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8">
+      <c r="A509" t="s">
+        <v>34</v>
+      </c>
+      <c r="B509" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8">
+      <c r="A510" t="s">
+        <v>55</v>
+      </c>
+      <c r="B510" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8">
+      <c r="A511" t="s">
+        <v>48</v>
+      </c>
+      <c r="B511" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8">
+      <c r="A512" t="s">
+        <v>42</v>
+      </c>
+      <c r="B512" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" t="s">
+        <v>20</v>
+      </c>
+      <c r="B513" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" t="s">
+        <v>53</v>
+      </c>
+      <c r="B514" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" t="s">
+        <v>47</v>
+      </c>
+      <c r="B515" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" t="s">
+        <v>49</v>
+      </c>
+      <c r="B516" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" t="s">
+        <v>15</v>
+      </c>
+      <c r="B517" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" t="s">
+        <v>50</v>
+      </c>
+      <c r="B518" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" t="s">
+        <v>45</v>
+      </c>
+      <c r="B519" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" t="s">
+        <v>33</v>
+      </c>
+      <c r="B520" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" t="s">
+        <v>29</v>
+      </c>
+      <c r="B521" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" t="s">
+        <v>28</v>
+      </c>
+      <c r="B522" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" t="s">
+        <v>46</v>
+      </c>
+      <c r="B523" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" t="s">
+        <v>39</v>
+      </c>
+      <c r="B524" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" t="s">
+        <v>35</v>
+      </c>
+      <c r="B525" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" t="s">
+        <v>43</v>
+      </c>
+      <c r="B526" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" t="s">
+        <v>25</v>
+      </c>
+      <c r="B527" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" t="s">
+        <v>23</v>
+      </c>
+      <c r="B528" s="2">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" t="s">
+        <v>51</v>
+      </c>
+      <c r="B529" s="2">
+        <v>46205</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H529"/>
+  <dimension ref="A1:H577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -13068,12 +13068,684 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="529" spans="1:2">
+    <row r="529" spans="1:8">
       <c r="A529" t="s">
         <v>51</v>
       </c>
       <c r="B529" s="2">
         <v>46205</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8">
+      <c r="A530" t="s">
+        <v>9</v>
+      </c>
+      <c r="B530" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C530">
+        <v>6</v>
+      </c>
+      <c r="D530">
+        <v>2.8779</v>
+      </c>
+      <c r="E530">
+        <v>0.307604</v>
+      </c>
+      <c r="F530">
+        <v>30.7604</v>
+      </c>
+      <c r="G530">
+        <v>0.323569</v>
+      </c>
+      <c r="H530">
+        <v>32.3569</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8">
+      <c r="A531" t="s">
+        <v>13</v>
+      </c>
+      <c r="B531" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C531">
+        <v>6</v>
+      </c>
+      <c r="D531">
+        <v>5.31</v>
+      </c>
+      <c r="E531">
+        <v>0.166715</v>
+      </c>
+      <c r="F531">
+        <v>16.6715</v>
+      </c>
+      <c r="G531">
+        <v>0.173107</v>
+      </c>
+      <c r="H531">
+        <v>17.3107</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8">
+      <c r="A532" t="s">
+        <v>8</v>
+      </c>
+      <c r="B532" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C532">
+        <v>6</v>
+      </c>
+      <c r="D532">
+        <v>7.045</v>
+      </c>
+      <c r="E532">
+        <v>0.125658</v>
+      </c>
+      <c r="F532">
+        <v>12.5658</v>
+      </c>
+      <c r="G532">
+        <v>0.129274</v>
+      </c>
+      <c r="H532">
+        <v>12.9274</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8">
+      <c r="A533" t="s">
+        <v>10</v>
+      </c>
+      <c r="B533" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C533">
+        <v>6</v>
+      </c>
+      <c r="D533">
+        <v>11.05</v>
+      </c>
+      <c r="E533">
+        <v>0.080114</v>
+      </c>
+      <c r="F533">
+        <v>8.0114</v>
+      </c>
+      <c r="G533">
+        <v>0.080678</v>
+      </c>
+      <c r="H533">
+        <v>8.0678</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8">
+      <c r="A534" t="s">
+        <v>12</v>
+      </c>
+      <c r="B534" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C534">
+        <v>6</v>
+      </c>
+      <c r="D534">
+        <v>12.7</v>
+      </c>
+      <c r="E534">
+        <v>0.069705</v>
+      </c>
+      <c r="F534">
+        <v>6.9705</v>
+      </c>
+      <c r="G534">
+        <v>0.069582</v>
+      </c>
+      <c r="H534">
+        <v>6.9582</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8">
+      <c r="A535" t="s">
+        <v>11</v>
+      </c>
+      <c r="B535" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C535">
+        <v>6</v>
+      </c>
+      <c r="D535">
+        <v>13.95</v>
+      </c>
+      <c r="E535">
+        <v>0.063459</v>
+      </c>
+      <c r="F535">
+        <v>6.3459</v>
+      </c>
+      <c r="G535">
+        <v>0.062927</v>
+      </c>
+      <c r="H535">
+        <v>6.2927</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8">
+      <c r="A536" t="s">
+        <v>18</v>
+      </c>
+      <c r="B536" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C536">
+        <v>6</v>
+      </c>
+      <c r="D536">
+        <v>25.5</v>
+      </c>
+      <c r="E536">
+        <v>0.034716</v>
+      </c>
+      <c r="F536">
+        <v>3.4716</v>
+      </c>
+      <c r="G536">
+        <v>0.032378</v>
+      </c>
+      <c r="H536">
+        <v>3.2378</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8">
+      <c r="A537" t="s">
+        <v>22</v>
+      </c>
+      <c r="B537" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C537">
+        <v>6</v>
+      </c>
+      <c r="D537">
+        <v>28.8333</v>
+      </c>
+      <c r="E537">
+        <v>0.030703</v>
+      </c>
+      <c r="F537">
+        <v>3.0703</v>
+      </c>
+      <c r="G537">
+        <v>0.028135</v>
+      </c>
+      <c r="H537">
+        <v>2.8135</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8">
+      <c r="A538" t="s">
+        <v>21</v>
+      </c>
+      <c r="B538" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C538">
+        <v>6</v>
+      </c>
+      <c r="D538">
+        <v>29.8333</v>
+      </c>
+      <c r="E538">
+        <v>0.029673</v>
+      </c>
+      <c r="F538">
+        <v>2.9673</v>
+      </c>
+      <c r="G538">
+        <v>0.027049</v>
+      </c>
+      <c r="H538">
+        <v>2.7049</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8">
+      <c r="A539" t="s">
+        <v>19</v>
+      </c>
+      <c r="B539" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C539">
+        <v>6</v>
+      </c>
+      <c r="D539">
+        <v>31.8333</v>
+      </c>
+      <c r="E539">
+        <v>0.027809</v>
+      </c>
+      <c r="F539">
+        <v>2.7809</v>
+      </c>
+      <c r="G539">
+        <v>0.025084</v>
+      </c>
+      <c r="H539">
+        <v>2.5084</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8">
+      <c r="A540" t="s">
+        <v>16</v>
+      </c>
+      <c r="B540" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C540">
+        <v>6</v>
+      </c>
+      <c r="D540">
+        <v>38.5</v>
+      </c>
+      <c r="E540">
+        <v>0.022994</v>
+      </c>
+      <c r="F540">
+        <v>2.2994</v>
+      </c>
+      <c r="G540">
+        <v>0.020028</v>
+      </c>
+      <c r="H540">
+        <v>2.0028</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8">
+      <c r="A541" t="s">
+        <v>17</v>
+      </c>
+      <c r="B541" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C541">
+        <v>6</v>
+      </c>
+      <c r="D541">
+        <v>48.5</v>
+      </c>
+      <c r="E541">
+        <v>0.018253</v>
+      </c>
+      <c r="F541">
+        <v>1.8253</v>
+      </c>
+      <c r="G541">
+        <v>0.015093</v>
+      </c>
+      <c r="H541">
+        <v>1.5093</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8">
+      <c r="A542" t="s">
+        <v>24</v>
+      </c>
+      <c r="B542" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C542">
+        <v>6</v>
+      </c>
+      <c r="D542">
+        <v>66</v>
+      </c>
+      <c r="E542">
+        <v>0.013413</v>
+      </c>
+      <c r="F542">
+        <v>1.3413</v>
+      </c>
+      <c r="G542">
+        <v>0.010144</v>
+      </c>
+      <c r="H542">
+        <v>1.0144</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8">
+      <c r="A543" t="s">
+        <v>31</v>
+      </c>
+      <c r="B543" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C543">
+        <v>6</v>
+      </c>
+      <c r="D543">
+        <v>249.8333</v>
+      </c>
+      <c r="E543">
+        <v>0.003543</v>
+      </c>
+      <c r="F543">
+        <v>0.3543</v>
+      </c>
+      <c r="G543">
+        <v>0.001262</v>
+      </c>
+      <c r="H543">
+        <v>0.1262</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8">
+      <c r="A544" t="s">
+        <v>36</v>
+      </c>
+      <c r="B544" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C544">
+        <v>6</v>
+      </c>
+      <c r="D544">
+        <v>272.3333</v>
+      </c>
+      <c r="E544">
+        <v>0.003251</v>
+      </c>
+      <c r="F544">
+        <v>0.3251</v>
+      </c>
+      <c r="G544">
+        <v>0.001079</v>
+      </c>
+      <c r="H544">
+        <v>0.1079</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8">
+      <c r="A545" t="s">
+        <v>32</v>
+      </c>
+      <c r="B545" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C545">
+        <v>6</v>
+      </c>
+      <c r="D545">
+        <v>370.3333</v>
+      </c>
+      <c r="E545">
+        <v>0.00239</v>
+      </c>
+      <c r="F545">
+        <v>0.239</v>
+      </c>
+      <c r="G545">
+        <v>0.0006089999999999999</v>
+      </c>
+      <c r="H545">
+        <v>0.0609</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8">
+      <c r="A546" t="s">
+        <v>37</v>
+      </c>
+      <c r="B546" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8">
+      <c r="A547" t="s">
+        <v>40</v>
+      </c>
+      <c r="B547" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8">
+      <c r="A548" t="s">
+        <v>38</v>
+      </c>
+      <c r="B548" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8">
+      <c r="A549" t="s">
+        <v>54</v>
+      </c>
+      <c r="B549" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8">
+      <c r="A550" t="s">
+        <v>44</v>
+      </c>
+      <c r="B550" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8">
+      <c r="A551" t="s">
+        <v>14</v>
+      </c>
+      <c r="B551" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8">
+      <c r="A552" t="s">
+        <v>27</v>
+      </c>
+      <c r="B552" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8">
+      <c r="A553" t="s">
+        <v>34</v>
+      </c>
+      <c r="B553" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8">
+      <c r="A554" t="s">
+        <v>41</v>
+      </c>
+      <c r="B554" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8">
+      <c r="A555" t="s">
+        <v>55</v>
+      </c>
+      <c r="B555" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8">
+      <c r="A556" t="s">
+        <v>48</v>
+      </c>
+      <c r="B556" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8">
+      <c r="A557" t="s">
+        <v>42</v>
+      </c>
+      <c r="B557" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8">
+      <c r="A558" t="s">
+        <v>20</v>
+      </c>
+      <c r="B558" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8">
+      <c r="A559" t="s">
+        <v>53</v>
+      </c>
+      <c r="B559" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8">
+      <c r="A560" t="s">
+        <v>52</v>
+      </c>
+      <c r="B560" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" t="s">
+        <v>47</v>
+      </c>
+      <c r="B561" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" t="s">
+        <v>26</v>
+      </c>
+      <c r="B562" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" t="s">
+        <v>49</v>
+      </c>
+      <c r="B563" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" t="s">
+        <v>15</v>
+      </c>
+      <c r="B564" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" t="s">
+        <v>50</v>
+      </c>
+      <c r="B565" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" t="s">
+        <v>45</v>
+      </c>
+      <c r="B566" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" t="s">
+        <v>33</v>
+      </c>
+      <c r="B567" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" t="s">
+        <v>29</v>
+      </c>
+      <c r="B568" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" t="s">
+        <v>28</v>
+      </c>
+      <c r="B569" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" t="s">
+        <v>46</v>
+      </c>
+      <c r="B570" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" t="s">
+        <v>39</v>
+      </c>
+      <c r="B571" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" t="s">
+        <v>35</v>
+      </c>
+      <c r="B572" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" t="s">
+        <v>43</v>
+      </c>
+      <c r="B573" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" t="s">
+        <v>25</v>
+      </c>
+      <c r="B574" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" t="s">
+        <v>23</v>
+      </c>
+      <c r="B575" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" t="s">
+        <v>51</v>
+      </c>
+      <c r="B576" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" t="s">
+        <v>30</v>
+      </c>
+      <c r="B577" s="2">
+        <v>46207</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H577"/>
+  <dimension ref="A1:H625"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -13740,12 +13740,630 @@
         <v>46207</v>
       </c>
     </row>
-    <row r="577" spans="1:2">
+    <row r="577" spans="1:8">
       <c r="A577" t="s">
         <v>30</v>
       </c>
       <c r="B577" s="2">
         <v>46207</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8">
+      <c r="A578" t="s">
+        <v>9</v>
+      </c>
+      <c r="B578" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C578">
+        <v>6</v>
+      </c>
+      <c r="D578">
+        <v>2.79</v>
+      </c>
+      <c r="E578">
+        <v>0.325574</v>
+      </c>
+      <c r="F578">
+        <v>32.5574</v>
+      </c>
+      <c r="G578">
+        <v>0.338611</v>
+      </c>
+      <c r="H578">
+        <v>33.8611</v>
+      </c>
+    </row>
+    <row r="579" spans="1:8">
+      <c r="A579" t="s">
+        <v>13</v>
+      </c>
+      <c r="B579" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C579">
+        <v>6</v>
+      </c>
+      <c r="D579">
+        <v>5.5333</v>
+      </c>
+      <c r="E579">
+        <v>0.16416</v>
+      </c>
+      <c r="F579">
+        <v>16.416</v>
+      </c>
+      <c r="G579">
+        <v>0.168504</v>
+      </c>
+      <c r="H579">
+        <v>16.8504</v>
+      </c>
+    </row>
+    <row r="580" spans="1:8">
+      <c r="A580" t="s">
+        <v>8</v>
+      </c>
+      <c r="B580" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C580">
+        <v>6</v>
+      </c>
+      <c r="D580">
+        <v>6.98</v>
+      </c>
+      <c r="E580">
+        <v>0.130136</v>
+      </c>
+      <c r="F580">
+        <v>13.0136</v>
+      </c>
+      <c r="G580">
+        <v>0.132658</v>
+      </c>
+      <c r="H580">
+        <v>13.2658</v>
+      </c>
+    </row>
+    <row r="581" spans="1:8">
+      <c r="A581" t="s">
+        <v>10</v>
+      </c>
+      <c r="B581" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C581">
+        <v>6</v>
+      </c>
+      <c r="D581">
+        <v>7.3967</v>
+      </c>
+      <c r="E581">
+        <v>0.122806</v>
+      </c>
+      <c r="F581">
+        <v>12.2806</v>
+      </c>
+      <c r="G581">
+        <v>0.124936</v>
+      </c>
+      <c r="H581">
+        <v>12.4936</v>
+      </c>
+    </row>
+    <row r="582" spans="1:8">
+      <c r="A582" t="s">
+        <v>11</v>
+      </c>
+      <c r="B582" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C582">
+        <v>6</v>
+      </c>
+      <c r="D582">
+        <v>14.2</v>
+      </c>
+      <c r="E582">
+        <v>0.063968</v>
+      </c>
+      <c r="F582">
+        <v>6.3968</v>
+      </c>
+      <c r="G582">
+        <v>0.06299399999999999</v>
+      </c>
+      <c r="H582">
+        <v>6.2994</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8">
+      <c r="A583" t="s">
+        <v>16</v>
+      </c>
+      <c r="B583" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C583">
+        <v>6</v>
+      </c>
+      <c r="D583">
+        <v>21</v>
+      </c>
+      <c r="E583">
+        <v>0.043255</v>
+      </c>
+      <c r="F583">
+        <v>4.3255</v>
+      </c>
+      <c r="G583">
+        <v>0.041235</v>
+      </c>
+      <c r="H583">
+        <v>4.1235</v>
+      </c>
+    </row>
+    <row r="584" spans="1:8">
+      <c r="A584" t="s">
+        <v>18</v>
+      </c>
+      <c r="B584" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C584">
+        <v>6</v>
+      </c>
+      <c r="D584">
+        <v>25</v>
+      </c>
+      <c r="E584">
+        <v>0.036334</v>
+      </c>
+      <c r="F584">
+        <v>3.6334</v>
+      </c>
+      <c r="G584">
+        <v>0.033984</v>
+      </c>
+      <c r="H584">
+        <v>3.3984</v>
+      </c>
+    </row>
+    <row r="585" spans="1:8">
+      <c r="A585" t="s">
+        <v>21</v>
+      </c>
+      <c r="B585" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C585">
+        <v>6</v>
+      </c>
+      <c r="D585">
+        <v>28.8333</v>
+      </c>
+      <c r="E585">
+        <v>0.031504</v>
+      </c>
+      <c r="F585">
+        <v>3.1504</v>
+      </c>
+      <c r="G585">
+        <v>0.028934</v>
+      </c>
+      <c r="H585">
+        <v>2.8934</v>
+      </c>
+    </row>
+    <row r="586" spans="1:8">
+      <c r="A586" t="s">
+        <v>19</v>
+      </c>
+      <c r="B586" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C586">
+        <v>6</v>
+      </c>
+      <c r="D586">
+        <v>30.5</v>
+      </c>
+      <c r="E586">
+        <v>0.029782</v>
+      </c>
+      <c r="F586">
+        <v>2.9782</v>
+      </c>
+      <c r="G586">
+        <v>0.027138</v>
+      </c>
+      <c r="H586">
+        <v>2.7138</v>
+      </c>
+    </row>
+    <row r="587" spans="1:8">
+      <c r="A587" t="s">
+        <v>17</v>
+      </c>
+      <c r="B587" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C587">
+        <v>6</v>
+      </c>
+      <c r="D587">
+        <v>49.3333</v>
+      </c>
+      <c r="E587">
+        <v>0.018413</v>
+      </c>
+      <c r="F587">
+        <v>1.8413</v>
+      </c>
+      <c r="G587">
+        <v>0.015355</v>
+      </c>
+      <c r="H587">
+        <v>1.5355</v>
+      </c>
+    </row>
+    <row r="588" spans="1:8">
+      <c r="A588" t="s">
+        <v>22</v>
+      </c>
+      <c r="B588" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C588">
+        <v>6</v>
+      </c>
+      <c r="D588">
+        <v>51</v>
+      </c>
+      <c r="E588">
+        <v>0.017811</v>
+      </c>
+      <c r="F588">
+        <v>1.7811</v>
+      </c>
+      <c r="G588">
+        <v>0.014738</v>
+      </c>
+      <c r="H588">
+        <v>1.4738</v>
+      </c>
+    </row>
+    <row r="589" spans="1:8">
+      <c r="A589" t="s">
+        <v>24</v>
+      </c>
+      <c r="B589" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C589">
+        <v>6</v>
+      </c>
+      <c r="D589">
+        <v>71.33329999999999</v>
+      </c>
+      <c r="E589">
+        <v>0.012734</v>
+      </c>
+      <c r="F589">
+        <v>1.2734</v>
+      </c>
+      <c r="G589">
+        <v>0.009597</v>
+      </c>
+      <c r="H589">
+        <v>0.9597</v>
+      </c>
+    </row>
+    <row r="590" spans="1:8">
+      <c r="A590" t="s">
+        <v>36</v>
+      </c>
+      <c r="B590" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C590">
+        <v>6</v>
+      </c>
+      <c r="D590">
+        <v>257.8333</v>
+      </c>
+      <c r="E590">
+        <v>0.003523</v>
+      </c>
+      <c r="F590">
+        <v>0.3523</v>
+      </c>
+      <c r="G590">
+        <v>0.001315</v>
+      </c>
+      <c r="H590">
+        <v>0.1315</v>
+      </c>
+    </row>
+    <row r="591" spans="1:8">
+      <c r="A591" t="s">
+        <v>37</v>
+      </c>
+      <c r="B591" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8">
+      <c r="A592" t="s">
+        <v>40</v>
+      </c>
+      <c r="B592" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" t="s">
+        <v>38</v>
+      </c>
+      <c r="B593" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" t="s">
+        <v>12</v>
+      </c>
+      <c r="B594" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" t="s">
+        <v>54</v>
+      </c>
+      <c r="B595" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" t="s">
+        <v>44</v>
+      </c>
+      <c r="B596" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" t="s">
+        <v>14</v>
+      </c>
+      <c r="B597" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" t="s">
+        <v>27</v>
+      </c>
+      <c r="B598" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" t="s">
+        <v>34</v>
+      </c>
+      <c r="B599" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" t="s">
+        <v>41</v>
+      </c>
+      <c r="B600" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" t="s">
+        <v>55</v>
+      </c>
+      <c r="B601" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" t="s">
+        <v>48</v>
+      </c>
+      <c r="B602" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" t="s">
+        <v>42</v>
+      </c>
+      <c r="B603" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" t="s">
+        <v>20</v>
+      </c>
+      <c r="B604" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" t="s">
+        <v>53</v>
+      </c>
+      <c r="B605" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" t="s">
+        <v>31</v>
+      </c>
+      <c r="B606" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" t="s">
+        <v>52</v>
+      </c>
+      <c r="B607" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" t="s">
+        <v>47</v>
+      </c>
+      <c r="B608" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" t="s">
+        <v>26</v>
+      </c>
+      <c r="B609" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" t="s">
+        <v>49</v>
+      </c>
+      <c r="B610" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" t="s">
+        <v>15</v>
+      </c>
+      <c r="B611" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" t="s">
+        <v>50</v>
+      </c>
+      <c r="B612" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" t="s">
+        <v>32</v>
+      </c>
+      <c r="B613" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" t="s">
+        <v>45</v>
+      </c>
+      <c r="B614" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" t="s">
+        <v>33</v>
+      </c>
+      <c r="B615" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" t="s">
+        <v>29</v>
+      </c>
+      <c r="B616" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" t="s">
+        <v>28</v>
+      </c>
+      <c r="B617" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" t="s">
+        <v>46</v>
+      </c>
+      <c r="B618" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" t="s">
+        <v>39</v>
+      </c>
+      <c r="B619" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620" t="s">
+        <v>35</v>
+      </c>
+      <c r="B620" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" t="s">
+        <v>43</v>
+      </c>
+      <c r="B621" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622" t="s">
+        <v>25</v>
+      </c>
+      <c r="B622" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" t="s">
+        <v>23</v>
+      </c>
+      <c r="B623" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" t="s">
+        <v>51</v>
+      </c>
+      <c r="B624" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625" t="s">
+        <v>30</v>
+      </c>
+      <c r="B625" s="2">
+        <v>46209</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H625"/>
+  <dimension ref="A1:H673"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -14358,12 +14358,540 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="625" spans="1:2">
+    <row r="625" spans="1:8">
       <c r="A625" t="s">
         <v>30</v>
       </c>
       <c r="B625" s="2">
         <v>46209</v>
+      </c>
+    </row>
+    <row r="626" spans="1:8">
+      <c r="A626" t="s">
+        <v>9</v>
+      </c>
+      <c r="B626" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C626">
+        <v>6</v>
+      </c>
+      <c r="D626">
+        <v>2.8817</v>
+      </c>
+      <c r="E626">
+        <v>0.322525</v>
+      </c>
+      <c r="F626">
+        <v>32.2525</v>
+      </c>
+      <c r="G626">
+        <v>0.330815</v>
+      </c>
+      <c r="H626">
+        <v>33.0815</v>
+      </c>
+    </row>
+    <row r="627" spans="1:8">
+      <c r="A627" t="s">
+        <v>8</v>
+      </c>
+      <c r="B627" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C627">
+        <v>6</v>
+      </c>
+      <c r="D627">
+        <v>4.7533</v>
+      </c>
+      <c r="E627">
+        <v>0.195528</v>
+      </c>
+      <c r="F627">
+        <v>19.5528</v>
+      </c>
+      <c r="G627">
+        <v>0.198369</v>
+      </c>
+      <c r="H627">
+        <v>19.8369</v>
+      </c>
+    </row>
+    <row r="628" spans="1:8">
+      <c r="A628" t="s">
+        <v>13</v>
+      </c>
+      <c r="B628" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C628">
+        <v>6</v>
+      </c>
+      <c r="D628">
+        <v>5.0517</v>
+      </c>
+      <c r="E628">
+        <v>0.183981</v>
+      </c>
+      <c r="F628">
+        <v>18.3981</v>
+      </c>
+      <c r="G628">
+        <v>0.186328</v>
+      </c>
+      <c r="H628">
+        <v>18.6328</v>
+      </c>
+    </row>
+    <row r="629" spans="1:8">
+      <c r="A629" t="s">
+        <v>10</v>
+      </c>
+      <c r="B629" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C629">
+        <v>6</v>
+      </c>
+      <c r="D629">
+        <v>5.8917</v>
+      </c>
+      <c r="E629">
+        <v>0.15775</v>
+      </c>
+      <c r="F629">
+        <v>15.775</v>
+      </c>
+      <c r="G629">
+        <v>0.158979</v>
+      </c>
+      <c r="H629">
+        <v>15.8979</v>
+      </c>
+    </row>
+    <row r="630" spans="1:8">
+      <c r="A630" t="s">
+        <v>16</v>
+      </c>
+      <c r="B630" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C630">
+        <v>6</v>
+      </c>
+      <c r="D630">
+        <v>16.2</v>
+      </c>
+      <c r="E630">
+        <v>0.057371</v>
+      </c>
+      <c r="F630">
+        <v>5.7371</v>
+      </c>
+      <c r="G630">
+        <v>0.05444</v>
+      </c>
+      <c r="H630">
+        <v>5.444</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8">
+      <c r="A631" t="s">
+        <v>19</v>
+      </c>
+      <c r="B631" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C631">
+        <v>6</v>
+      </c>
+      <c r="D631">
+        <v>31.3333</v>
+      </c>
+      <c r="E631">
+        <v>0.029662</v>
+      </c>
+      <c r="F631">
+        <v>2.9662</v>
+      </c>
+      <c r="G631">
+        <v>0.025783</v>
+      </c>
+      <c r="H631">
+        <v>2.5783</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8">
+      <c r="A632" t="s">
+        <v>17</v>
+      </c>
+      <c r="B632" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C632">
+        <v>6</v>
+      </c>
+      <c r="D632">
+        <v>32</v>
+      </c>
+      <c r="E632">
+        <v>0.029044</v>
+      </c>
+      <c r="F632">
+        <v>2.9044</v>
+      </c>
+      <c r="G632">
+        <v>0.025149</v>
+      </c>
+      <c r="H632">
+        <v>2.5149</v>
+      </c>
+    </row>
+    <row r="633" spans="1:8">
+      <c r="A633" t="s">
+        <v>24</v>
+      </c>
+      <c r="B633" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C633">
+        <v>6</v>
+      </c>
+      <c r="D633">
+        <v>38.5</v>
+      </c>
+      <c r="E633">
+        <v>0.02414</v>
+      </c>
+      <c r="F633">
+        <v>2.414</v>
+      </c>
+      <c r="G633">
+        <v>0.020138</v>
+      </c>
+      <c r="H633">
+        <v>2.0138</v>
+      </c>
+    </row>
+    <row r="634" spans="1:8">
+      <c r="A634" t="s">
+        <v>37</v>
+      </c>
+      <c r="B634" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="635" spans="1:8">
+      <c r="A635" t="s">
+        <v>40</v>
+      </c>
+      <c r="B635" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="636" spans="1:8">
+      <c r="A636" t="s">
+        <v>38</v>
+      </c>
+      <c r="B636" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="637" spans="1:8">
+      <c r="A637" t="s">
+        <v>12</v>
+      </c>
+      <c r="B637" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="638" spans="1:8">
+      <c r="A638" t="s">
+        <v>54</v>
+      </c>
+      <c r="B638" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="639" spans="1:8">
+      <c r="A639" t="s">
+        <v>44</v>
+      </c>
+      <c r="B639" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="640" spans="1:8">
+      <c r="A640" t="s">
+        <v>14</v>
+      </c>
+      <c r="B640" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641" t="s">
+        <v>27</v>
+      </c>
+      <c r="B641" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642" t="s">
+        <v>34</v>
+      </c>
+      <c r="B642" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643" t="s">
+        <v>41</v>
+      </c>
+      <c r="B643" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644" t="s">
+        <v>55</v>
+      </c>
+      <c r="B644" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645" t="s">
+        <v>48</v>
+      </c>
+      <c r="B645" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646" t="s">
+        <v>42</v>
+      </c>
+      <c r="B646" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647" t="s">
+        <v>20</v>
+      </c>
+      <c r="B647" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648" t="s">
+        <v>53</v>
+      </c>
+      <c r="B648" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649" t="s">
+        <v>31</v>
+      </c>
+      <c r="B649" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650" t="s">
+        <v>52</v>
+      </c>
+      <c r="B650" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651" t="s">
+        <v>47</v>
+      </c>
+      <c r="B651" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652" t="s">
+        <v>18</v>
+      </c>
+      <c r="B652" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653" t="s">
+        <v>26</v>
+      </c>
+      <c r="B653" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654" t="s">
+        <v>22</v>
+      </c>
+      <c r="B654" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655" t="s">
+        <v>49</v>
+      </c>
+      <c r="B655" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" t="s">
+        <v>15</v>
+      </c>
+      <c r="B656" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" t="s">
+        <v>50</v>
+      </c>
+      <c r="B657" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" t="s">
+        <v>32</v>
+      </c>
+      <c r="B658" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659" t="s">
+        <v>11</v>
+      </c>
+      <c r="B659" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" t="s">
+        <v>45</v>
+      </c>
+      <c r="B660" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661" t="s">
+        <v>33</v>
+      </c>
+      <c r="B661" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662" t="s">
+        <v>29</v>
+      </c>
+      <c r="B662" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663" t="s">
+        <v>28</v>
+      </c>
+      <c r="B663" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664" t="s">
+        <v>46</v>
+      </c>
+      <c r="B664" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665" t="s">
+        <v>39</v>
+      </c>
+      <c r="B665" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" t="s">
+        <v>35</v>
+      </c>
+      <c r="B666" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" t="s">
+        <v>43</v>
+      </c>
+      <c r="B667" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" t="s">
+        <v>25</v>
+      </c>
+      <c r="B668" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669" t="s">
+        <v>21</v>
+      </c>
+      <c r="B669" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670" t="s">
+        <v>23</v>
+      </c>
+      <c r="B670" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671" t="s">
+        <v>51</v>
+      </c>
+      <c r="B671" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672" t="s">
+        <v>36</v>
+      </c>
+      <c r="B672" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673" t="s">
+        <v>30</v>
+      </c>
+      <c r="B673" s="2">
+        <v>46211</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H673"/>
+  <dimension ref="A1:H721"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -14886,12 +14886,522 @@
         <v>46211</v>
       </c>
     </row>
-    <row r="673" spans="1:2">
+    <row r="673" spans="1:8">
       <c r="A673" t="s">
         <v>30</v>
       </c>
       <c r="B673" s="2">
         <v>46211</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8">
+      <c r="A674" t="s">
+        <v>9</v>
+      </c>
+      <c r="B674" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C674">
+        <v>6</v>
+      </c>
+      <c r="D674">
+        <v>2.4883</v>
+      </c>
+      <c r="E674">
+        <v>0.375433</v>
+      </c>
+      <c r="F674">
+        <v>37.5433</v>
+      </c>
+      <c r="G674">
+        <v>0.38471</v>
+      </c>
+      <c r="H674">
+        <v>38.471</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8">
+      <c r="A675" t="s">
+        <v>8</v>
+      </c>
+      <c r="B675" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C675">
+        <v>6</v>
+      </c>
+      <c r="D675">
+        <v>5.2517</v>
+      </c>
+      <c r="E675">
+        <v>0.177887</v>
+      </c>
+      <c r="F675">
+        <v>17.7887</v>
+      </c>
+      <c r="G675">
+        <v>0.179126</v>
+      </c>
+      <c r="H675">
+        <v>17.9126</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8">
+      <c r="A676" t="s">
+        <v>13</v>
+      </c>
+      <c r="B676" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C676">
+        <v>6</v>
+      </c>
+      <c r="D676">
+        <v>5.335</v>
+      </c>
+      <c r="E676">
+        <v>0.175108</v>
+      </c>
+      <c r="F676">
+        <v>17.5108</v>
+      </c>
+      <c r="G676">
+        <v>0.176236</v>
+      </c>
+      <c r="H676">
+        <v>17.6236</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8">
+      <c r="A677" t="s">
+        <v>10</v>
+      </c>
+      <c r="B677" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C677">
+        <v>6</v>
+      </c>
+      <c r="D677">
+        <v>5.7333</v>
+      </c>
+      <c r="E677">
+        <v>0.162942</v>
+      </c>
+      <c r="F677">
+        <v>16.2942</v>
+      </c>
+      <c r="G677">
+        <v>0.163579</v>
+      </c>
+      <c r="H677">
+        <v>16.3579</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8">
+      <c r="A678" t="s">
+        <v>16</v>
+      </c>
+      <c r="B678" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C678">
+        <v>6</v>
+      </c>
+      <c r="D678">
+        <v>16.2833</v>
+      </c>
+      <c r="E678">
+        <v>0.057372</v>
+      </c>
+      <c r="F678">
+        <v>5.7372</v>
+      </c>
+      <c r="G678">
+        <v>0.053889</v>
+      </c>
+      <c r="H678">
+        <v>5.3889</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8">
+      <c r="A679" t="s">
+        <v>17</v>
+      </c>
+      <c r="B679" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C679">
+        <v>6</v>
+      </c>
+      <c r="D679">
+        <v>35.1667</v>
+      </c>
+      <c r="E679">
+        <v>0.026565</v>
+      </c>
+      <c r="F679">
+        <v>2.6565</v>
+      </c>
+      <c r="G679">
+        <v>0.02218</v>
+      </c>
+      <c r="H679">
+        <v>2.218</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8">
+      <c r="A680" t="s">
+        <v>24</v>
+      </c>
+      <c r="B680" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C680">
+        <v>6</v>
+      </c>
+      <c r="D680">
+        <v>37.8333</v>
+      </c>
+      <c r="E680">
+        <v>0.024693</v>
+      </c>
+      <c r="F680">
+        <v>2.4693</v>
+      </c>
+      <c r="G680">
+        <v>0.020281</v>
+      </c>
+      <c r="H680">
+        <v>2.0281</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8">
+      <c r="A681" t="s">
+        <v>37</v>
+      </c>
+      <c r="B681" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8">
+      <c r="A682" t="s">
+        <v>40</v>
+      </c>
+      <c r="B682" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" t="s">
+        <v>38</v>
+      </c>
+      <c r="B683" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" t="s">
+        <v>12</v>
+      </c>
+      <c r="B684" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8">
+      <c r="A685" t="s">
+        <v>54</v>
+      </c>
+      <c r="B685" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8">
+      <c r="A686" t="s">
+        <v>44</v>
+      </c>
+      <c r="B686" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8">
+      <c r="A687" t="s">
+        <v>14</v>
+      </c>
+      <c r="B687" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8">
+      <c r="A688" t="s">
+        <v>27</v>
+      </c>
+      <c r="B688" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689" t="s">
+        <v>34</v>
+      </c>
+      <c r="B689" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690" t="s">
+        <v>41</v>
+      </c>
+      <c r="B690" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691" t="s">
+        <v>55</v>
+      </c>
+      <c r="B691" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692" t="s">
+        <v>48</v>
+      </c>
+      <c r="B692" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693" t="s">
+        <v>42</v>
+      </c>
+      <c r="B693" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694" t="s">
+        <v>20</v>
+      </c>
+      <c r="B694" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695" t="s">
+        <v>53</v>
+      </c>
+      <c r="B695" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696" t="s">
+        <v>31</v>
+      </c>
+      <c r="B696" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697" t="s">
+        <v>52</v>
+      </c>
+      <c r="B697" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698" t="s">
+        <v>47</v>
+      </c>
+      <c r="B698" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699" t="s">
+        <v>18</v>
+      </c>
+      <c r="B699" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700" t="s">
+        <v>26</v>
+      </c>
+      <c r="B700" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701" t="s">
+        <v>19</v>
+      </c>
+      <c r="B701" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702" t="s">
+        <v>22</v>
+      </c>
+      <c r="B702" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703" t="s">
+        <v>49</v>
+      </c>
+      <c r="B703" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704" t="s">
+        <v>15</v>
+      </c>
+      <c r="B704" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705" t="s">
+        <v>50</v>
+      </c>
+      <c r="B705" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706" t="s">
+        <v>32</v>
+      </c>
+      <c r="B706" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707" t="s">
+        <v>11</v>
+      </c>
+      <c r="B707" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708" t="s">
+        <v>45</v>
+      </c>
+      <c r="B708" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709" t="s">
+        <v>33</v>
+      </c>
+      <c r="B709" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710" t="s">
+        <v>29</v>
+      </c>
+      <c r="B710" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711" t="s">
+        <v>28</v>
+      </c>
+      <c r="B711" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712" t="s">
+        <v>46</v>
+      </c>
+      <c r="B712" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713" t="s">
+        <v>39</v>
+      </c>
+      <c r="B713" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714" t="s">
+        <v>35</v>
+      </c>
+      <c r="B714" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715" t="s">
+        <v>43</v>
+      </c>
+      <c r="B715" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716" t="s">
+        <v>25</v>
+      </c>
+      <c r="B716" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717" t="s">
+        <v>21</v>
+      </c>
+      <c r="B717" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718" t="s">
+        <v>23</v>
+      </c>
+      <c r="B718" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719" t="s">
+        <v>51</v>
+      </c>
+      <c r="B719" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720" t="s">
+        <v>36</v>
+      </c>
+      <c r="B720" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721" t="s">
+        <v>30</v>
+      </c>
+      <c r="B721" s="2">
+        <v>46213</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H721"/>
+  <dimension ref="A1:H769"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -15396,12 +15396,468 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="721" spans="1:2">
+    <row r="721" spans="1:8">
       <c r="A721" t="s">
         <v>30</v>
       </c>
       <c r="B721" s="2">
         <v>46213</v>
+      </c>
+    </row>
+    <row r="722" spans="1:8">
+      <c r="A722" t="s">
+        <v>9</v>
+      </c>
+      <c r="B722" s="2">
+        <v>46215</v>
+      </c>
+      <c r="C722">
+        <v>6</v>
+      </c>
+      <c r="D722">
+        <v>2.5083</v>
+      </c>
+      <c r="E722">
+        <v>0.377824</v>
+      </c>
+      <c r="F722">
+        <v>37.7824</v>
+      </c>
+      <c r="G722">
+        <v>0.38246</v>
+      </c>
+      <c r="H722">
+        <v>38.246</v>
+      </c>
+    </row>
+    <row r="723" spans="1:8">
+      <c r="A723" t="s">
+        <v>8</v>
+      </c>
+      <c r="B723" s="2">
+        <v>46215</v>
+      </c>
+      <c r="C723">
+        <v>6</v>
+      </c>
+      <c r="D723">
+        <v>4.3619</v>
+      </c>
+      <c r="E723">
+        <v>0.217269</v>
+      </c>
+      <c r="F723">
+        <v>21.7269</v>
+      </c>
+      <c r="G723">
+        <v>0.216077</v>
+      </c>
+      <c r="H723">
+        <v>21.6077</v>
+      </c>
+    </row>
+    <row r="724" spans="1:8">
+      <c r="A724" t="s">
+        <v>10</v>
+      </c>
+      <c r="B724" s="2">
+        <v>46215</v>
+      </c>
+      <c r="C724">
+        <v>6</v>
+      </c>
+      <c r="D724">
+        <v>4.4319</v>
+      </c>
+      <c r="E724">
+        <v>0.213837</v>
+      </c>
+      <c r="F724">
+        <v>21.3837</v>
+      </c>
+      <c r="G724">
+        <v>0.212522</v>
+      </c>
+      <c r="H724">
+        <v>21.2522</v>
+      </c>
+    </row>
+    <row r="725" spans="1:8">
+      <c r="A725" t="s">
+        <v>13</v>
+      </c>
+      <c r="B725" s="2">
+        <v>46215</v>
+      </c>
+      <c r="C725">
+        <v>6</v>
+      </c>
+      <c r="D725">
+        <v>4.96</v>
+      </c>
+      <c r="E725">
+        <v>0.19107</v>
+      </c>
+      <c r="F725">
+        <v>19.107</v>
+      </c>
+      <c r="G725">
+        <v>0.188941</v>
+      </c>
+      <c r="H725">
+        <v>18.8941</v>
+      </c>
+    </row>
+    <row r="726" spans="1:8">
+      <c r="A726" t="s">
+        <v>37</v>
+      </c>
+      <c r="B726" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="727" spans="1:8">
+      <c r="A727" t="s">
+        <v>40</v>
+      </c>
+      <c r="B727" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="728" spans="1:8">
+      <c r="A728" t="s">
+        <v>17</v>
+      </c>
+      <c r="B728" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="729" spans="1:8">
+      <c r="A729" t="s">
+        <v>38</v>
+      </c>
+      <c r="B729" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="730" spans="1:8">
+      <c r="A730" t="s">
+        <v>12</v>
+      </c>
+      <c r="B730" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="731" spans="1:8">
+      <c r="A731" t="s">
+        <v>54</v>
+      </c>
+      <c r="B731" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="732" spans="1:8">
+      <c r="A732" t="s">
+        <v>44</v>
+      </c>
+      <c r="B732" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="733" spans="1:8">
+      <c r="A733" t="s">
+        <v>14</v>
+      </c>
+      <c r="B733" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="734" spans="1:8">
+      <c r="A734" t="s">
+        <v>27</v>
+      </c>
+      <c r="B734" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8">
+      <c r="A735" t="s">
+        <v>34</v>
+      </c>
+      <c r="B735" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" t="s">
+        <v>41</v>
+      </c>
+      <c r="B736" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737" t="s">
+        <v>55</v>
+      </c>
+      <c r="B737" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738" t="s">
+        <v>48</v>
+      </c>
+      <c r="B738" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739" t="s">
+        <v>42</v>
+      </c>
+      <c r="B739" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740" t="s">
+        <v>20</v>
+      </c>
+      <c r="B740" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741" t="s">
+        <v>53</v>
+      </c>
+      <c r="B741" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742" t="s">
+        <v>31</v>
+      </c>
+      <c r="B742" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743" t="s">
+        <v>52</v>
+      </c>
+      <c r="B743" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744" t="s">
+        <v>47</v>
+      </c>
+      <c r="B744" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745" t="s">
+        <v>18</v>
+      </c>
+      <c r="B745" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746" t="s">
+        <v>26</v>
+      </c>
+      <c r="B746" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747" t="s">
+        <v>19</v>
+      </c>
+      <c r="B747" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748" t="s">
+        <v>22</v>
+      </c>
+      <c r="B748" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749" t="s">
+        <v>49</v>
+      </c>
+      <c r="B749" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750" t="s">
+        <v>15</v>
+      </c>
+      <c r="B750" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751" t="s">
+        <v>16</v>
+      </c>
+      <c r="B751" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752" t="s">
+        <v>50</v>
+      </c>
+      <c r="B752" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753" t="s">
+        <v>32</v>
+      </c>
+      <c r="B753" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754" t="s">
+        <v>11</v>
+      </c>
+      <c r="B754" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755" t="s">
+        <v>45</v>
+      </c>
+      <c r="B755" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756" t="s">
+        <v>33</v>
+      </c>
+      <c r="B756" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757" t="s">
+        <v>29</v>
+      </c>
+      <c r="B757" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758" t="s">
+        <v>24</v>
+      </c>
+      <c r="B758" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759" t="s">
+        <v>28</v>
+      </c>
+      <c r="B759" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760" t="s">
+        <v>46</v>
+      </c>
+      <c r="B760" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761" t="s">
+        <v>39</v>
+      </c>
+      <c r="B761" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762" t="s">
+        <v>35</v>
+      </c>
+      <c r="B762" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763" t="s">
+        <v>43</v>
+      </c>
+      <c r="B763" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764" t="s">
+        <v>25</v>
+      </c>
+      <c r="B764" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765" t="s">
+        <v>21</v>
+      </c>
+      <c r="B765" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766" t="s">
+        <v>23</v>
+      </c>
+      <c r="B766" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767" t="s">
+        <v>51</v>
+      </c>
+      <c r="B767" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768" t="s">
+        <v>36</v>
+      </c>
+      <c r="B768" s="2">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769" t="s">
+        <v>30</v>
+      </c>
+      <c r="B769" s="2">
+        <v>46215</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H769"/>
+  <dimension ref="A1:H817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -15852,12 +15852,468 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="769" spans="1:2">
+    <row r="769" spans="1:8">
       <c r="A769" t="s">
         <v>30</v>
       </c>
       <c r="B769" s="2">
         <v>46215</v>
+      </c>
+    </row>
+    <row r="770" spans="1:8">
+      <c r="A770" t="s">
+        <v>9</v>
+      </c>
+      <c r="B770" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C770">
+        <v>6</v>
+      </c>
+      <c r="D770">
+        <v>2.4312</v>
+      </c>
+      <c r="E770">
+        <v>0.389318</v>
+      </c>
+      <c r="F770">
+        <v>38.9318</v>
+      </c>
+      <c r="G770">
+        <v>0.39449</v>
+      </c>
+      <c r="H770">
+        <v>39.449</v>
+      </c>
+    </row>
+    <row r="771" spans="1:8">
+      <c r="A771" t="s">
+        <v>8</v>
+      </c>
+      <c r="B771" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C771">
+        <v>6</v>
+      </c>
+      <c r="D771">
+        <v>4.3286</v>
+      </c>
+      <c r="E771">
+        <v>0.21867</v>
+      </c>
+      <c r="F771">
+        <v>21.867</v>
+      </c>
+      <c r="G771">
+        <v>0.217498</v>
+      </c>
+      <c r="H771">
+        <v>21.7498</v>
+      </c>
+    </row>
+    <row r="772" spans="1:8">
+      <c r="A772" t="s">
+        <v>10</v>
+      </c>
+      <c r="B772" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C772">
+        <v>6</v>
+      </c>
+      <c r="D772">
+        <v>4.3619</v>
+      </c>
+      <c r="E772">
+        <v>0.216999</v>
+      </c>
+      <c r="F772">
+        <v>21.6999</v>
+      </c>
+      <c r="G772">
+        <v>0.215765</v>
+      </c>
+      <c r="H772">
+        <v>21.5765</v>
+      </c>
+    </row>
+    <row r="773" spans="1:8">
+      <c r="A773" t="s">
+        <v>13</v>
+      </c>
+      <c r="B773" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C773">
+        <v>6</v>
+      </c>
+      <c r="D773">
+        <v>5.4083</v>
+      </c>
+      <c r="E773">
+        <v>0.175013</v>
+      </c>
+      <c r="F773">
+        <v>17.5013</v>
+      </c>
+      <c r="G773">
+        <v>0.172247</v>
+      </c>
+      <c r="H773">
+        <v>17.2247</v>
+      </c>
+    </row>
+    <row r="774" spans="1:8">
+      <c r="A774" t="s">
+        <v>37</v>
+      </c>
+      <c r="B774" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="775" spans="1:8">
+      <c r="A775" t="s">
+        <v>40</v>
+      </c>
+      <c r="B775" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="776" spans="1:8">
+      <c r="A776" t="s">
+        <v>17</v>
+      </c>
+      <c r="B776" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="777" spans="1:8">
+      <c r="A777" t="s">
+        <v>38</v>
+      </c>
+      <c r="B777" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="778" spans="1:8">
+      <c r="A778" t="s">
+        <v>12</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="779" spans="1:8">
+      <c r="A779" t="s">
+        <v>54</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="780" spans="1:8">
+      <c r="A780" t="s">
+        <v>44</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="781" spans="1:8">
+      <c r="A781" t="s">
+        <v>14</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="782" spans="1:8">
+      <c r="A782" t="s">
+        <v>27</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="783" spans="1:8">
+      <c r="A783" t="s">
+        <v>34</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="784" spans="1:8">
+      <c r="A784" t="s">
+        <v>41</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785" t="s">
+        <v>55</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786" t="s">
+        <v>48</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787" t="s">
+        <v>42</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788" t="s">
+        <v>20</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789" t="s">
+        <v>53</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790" t="s">
+        <v>31</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791" t="s">
+        <v>52</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792" t="s">
+        <v>47</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793" t="s">
+        <v>18</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794" t="s">
+        <v>26</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795" t="s">
+        <v>19</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796" t="s">
+        <v>22</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797" t="s">
+        <v>49</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798" t="s">
+        <v>15</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799" t="s">
+        <v>16</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800" t="s">
+        <v>50</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801" t="s">
+        <v>32</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802" t="s">
+        <v>11</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803" t="s">
+        <v>45</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804" t="s">
+        <v>33</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805" t="s">
+        <v>29</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806" t="s">
+        <v>24</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807" t="s">
+        <v>28</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808" t="s">
+        <v>46</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809" t="s">
+        <v>39</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810" t="s">
+        <v>35</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811" t="s">
+        <v>43</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812" t="s">
+        <v>25</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813" t="s">
+        <v>21</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814" t="s">
+        <v>23</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815" t="s">
+        <v>51</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816" t="s">
+        <v>36</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817" t="s">
+        <v>30</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46217</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_long.xlsx
+++ b/processed_data_during_wm/processed_data_long.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="56">
   <si>
     <t>Team</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H817"/>
+  <dimension ref="A1:H865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -16308,12 +16308,432 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="817" spans="1:2">
+    <row r="817" spans="1:8">
       <c r="A817" t="s">
         <v>30</v>
       </c>
       <c r="B817" s="2">
         <v>46217</v>
+      </c>
+    </row>
+    <row r="818" spans="1:8">
+      <c r="A818" t="s">
+        <v>8</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C818">
+        <v>6</v>
+      </c>
+      <c r="D818">
+        <v>1.6396</v>
+      </c>
+      <c r="E818">
+        <v>0.5806249999999999</v>
+      </c>
+      <c r="F818">
+        <v>58.0625</v>
+      </c>
+      <c r="G818">
+        <v>0.584691</v>
+      </c>
+      <c r="H818">
+        <v>58.4691</v>
+      </c>
+    </row>
+    <row r="819" spans="1:8">
+      <c r="A819" t="s">
+        <v>13</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C819">
+        <v>6</v>
+      </c>
+      <c r="D819">
+        <v>2.27</v>
+      </c>
+      <c r="E819">
+        <v>0.419375</v>
+      </c>
+      <c r="F819">
+        <v>41.9375</v>
+      </c>
+      <c r="G819">
+        <v>0.415309</v>
+      </c>
+      <c r="H819">
+        <v>41.5309</v>
+      </c>
+    </row>
+    <row r="820" spans="1:8">
+      <c r="A820" t="s">
+        <v>37</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="821" spans="1:8">
+      <c r="A821" t="s">
+        <v>40</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="822" spans="1:8">
+      <c r="A822" t="s">
+        <v>17</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="823" spans="1:8">
+      <c r="A823" t="s">
+        <v>38</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="824" spans="1:8">
+      <c r="A824" t="s">
+        <v>12</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="825" spans="1:8">
+      <c r="A825" t="s">
+        <v>54</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="826" spans="1:8">
+      <c r="A826" t="s">
+        <v>44</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="827" spans="1:8">
+      <c r="A827" t="s">
+        <v>14</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="828" spans="1:8">
+      <c r="A828" t="s">
+        <v>27</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="829" spans="1:8">
+      <c r="A829" t="s">
+        <v>34</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="830" spans="1:8">
+      <c r="A830" t="s">
+        <v>10</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="831" spans="1:8">
+      <c r="A831" t="s">
+        <v>9</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="832" spans="1:8">
+      <c r="A832" t="s">
+        <v>41</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2">
+      <c r="A833" t="s">
+        <v>55</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2">
+      <c r="A834" t="s">
+        <v>48</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2">
+      <c r="A835" t="s">
+        <v>42</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2">
+      <c r="A836" t="s">
+        <v>20</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2">
+      <c r="A837" t="s">
+        <v>53</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2">
+      <c r="A838" t="s">
+        <v>31</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2">
+      <c r="A839" t="s">
+        <v>52</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2">
+      <c r="A840" t="s">
+        <v>47</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2">
+      <c r="A841" t="s">
+        <v>18</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2">
+      <c r="A842" t="s">
+        <v>26</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2">
+      <c r="A843" t="s">
+        <v>19</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2">
+      <c r="A844" t="s">
+        <v>22</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2">
+      <c r="A845" t="s">
+        <v>49</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2">
+      <c r="A846" t="s">
+        <v>15</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2">
+      <c r="A847" t="s">
+        <v>16</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2">
+      <c r="A848" t="s">
+        <v>50</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2">
+      <c r="A849" t="s">
+        <v>32</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2">
+      <c r="A850" t="s">
+        <v>11</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2">
+      <c r="A851" t="s">
+        <v>45</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2">
+      <c r="A852" t="s">
+        <v>33</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2">
+      <c r="A853" t="s">
+        <v>29</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2">
+      <c r="A854" t="s">
+        <v>24</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2">
+      <c r="A855" t="s">
+        <v>28</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2">
+      <c r="A856" t="s">
+        <v>46</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2">
+      <c r="A857" t="s">
+        <v>39</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2">
+      <c r="A858" t="s">
+        <v>35</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2">
+      <c r="A859" t="s">
+        <v>43</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2">
+      <c r="A860" t="s">
+        <v>25</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2">
+      <c r="A861" t="s">
+        <v>21</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2">
+      <c r="A862" t="s">
+        <v>23</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2">
+      <c r="A863" t="s">
+        <v>51</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2">
+      <c r="A864" t="s">
+        <v>36</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2">
+      <c r="A865" t="s">
+        <v>30</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46219</v>
       </c>
     </row>
   </sheetData>
